--- a/PythonPlayground/PreliminaryExperimentResults.xlsx
+++ b/PythonPlayground/PreliminaryExperimentResults.xlsx
@@ -5,6 +5,9 @@
   <sheets>
     <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
     <sheet state="visible" name="Sheet2" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="Sheet3" sheetId="3" r:id="rId6"/>
+    <sheet state="visible" name="Sheet4" sheetId="4" r:id="rId7"/>
+    <sheet state="visible" name="DSIFT" sheetId="5" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -12,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="47">
   <si>
     <t>Experiment1</t>
   </si>
@@ -112,6 +115,48 @@
   <si>
     <t>NearBias</t>
   </si>
+  <si>
+    <t>WD</t>
+  </si>
+  <si>
+    <t>Photos</t>
+  </si>
+  <si>
+    <t>SIFT</t>
+  </si>
+  <si>
+    <t>DSIFT</t>
+  </si>
+  <si>
+    <t>SIFT+DSIFT</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>OffViews</t>
+  </si>
+  <si>
+    <t>Radius of SfM showed a large radius</t>
+  </si>
+  <si>
+    <t>SpiralFocus</t>
+  </si>
+  <si>
+    <t>Very litle of the surrounding scene was captured</t>
+  </si>
+  <si>
+    <t>CircularFocus</t>
+  </si>
+  <si>
+    <t>Tilt</t>
+  </si>
+  <si>
+    <t>SIFT had a pretty large Std. Dev</t>
+  </si>
+  <si>
+    <t>Photos #</t>
+  </si>
 </sst>
 </file>
 
@@ -157,21 +202,64 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7B7B7"/>
+        <bgColor rgb="FFB7B7B7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border/>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+    </border>
+    <border>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="25">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -204,6 +292,41 @@
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -393,11 +516,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="162294874"/>
-        <c:axId val="1713431489"/>
+        <c:axId val="1791946864"/>
+        <c:axId val="2081689551"/>
       </c:bar3DChart>
       <c:catAx>
-        <c:axId val="162294874"/>
+        <c:axId val="1791946864"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -449,10 +572,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1713431489"/>
+        <c:crossAx val="2081689551"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1713431489"/>
+        <c:axId val="2081689551"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -527,7 +650,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="162294874"/>
+        <c:crossAx val="1791946864"/>
         <c:crosses val="max"/>
       </c:valAx>
     </c:plotArea>
@@ -746,11 +869,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="1745710111"/>
-        <c:axId val="2070223812"/>
+        <c:axId val="1750696618"/>
+        <c:axId val="50005776"/>
       </c:bar3DChart>
       <c:catAx>
-        <c:axId val="1745710111"/>
+        <c:axId val="1750696618"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -802,10 +925,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2070223812"/>
+        <c:crossAx val="50005776"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="2070223812"/>
+        <c:axId val="50005776"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -882,7 +1005,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1745710111"/>
+        <c:crossAx val="1750696618"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -1114,11 +1237,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="542819769"/>
-        <c:axId val="241885027"/>
+        <c:axId val="1089295186"/>
+        <c:axId val="879454078"/>
       </c:bar3DChart>
       <c:catAx>
-        <c:axId val="542819769"/>
+        <c:axId val="1089295186"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1170,10 +1293,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="241885027"/>
+        <c:crossAx val="879454078"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="241885027"/>
+        <c:axId val="879454078"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1250,7 +1373,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="542819769"/>
+        <c:crossAx val="1089295186"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -1359,6 +1482,18 @@
     <xdr:clientData fLocksWithSheet="0"/>
   </xdr:oneCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11535,4 +11670,4843 @@
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="2" max="2" width="6.25"/>
+    <col customWidth="1" min="3" max="3" width="6.63"/>
+    <col customWidth="1" min="4" max="4" width="8.13"/>
+    <col customWidth="1" min="5" max="5" width="8.88"/>
+    <col customWidth="1" min="6" max="6" width="8.5"/>
+    <col customWidth="1" min="7" max="7" width="8.13"/>
+    <col customWidth="1" min="8" max="8" width="8.88"/>
+    <col customWidth="1" min="9" max="9" width="8.5"/>
+    <col customWidth="1" min="10" max="10" width="10.38"/>
+    <col customWidth="1" min="11" max="11" width="8.88"/>
+    <col customWidth="1" min="12" max="12" width="8.5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="J1" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
+      <c r="S1" s="6"/>
+      <c r="T1" s="6"/>
+      <c r="U1" s="6"/>
+      <c r="V1" s="6"/>
+      <c r="W1" s="6"/>
+      <c r="X1" s="6"/>
+      <c r="Y1" s="6"/>
+      <c r="Z1" s="6"/>
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6"/>
+      <c r="AD1" s="6"/>
+      <c r="AE1" s="6"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="15"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="17"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
+      <c r="V2" s="6"/>
+      <c r="W2" s="6"/>
+      <c r="X2" s="6"/>
+      <c r="Y2" s="6"/>
+      <c r="Z2" s="6"/>
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="6"/>
+      <c r="AD2" s="6"/>
+      <c r="AE2" s="6"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="C3" s="7">
+        <v>48.0</v>
+      </c>
+      <c r="D3" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="E3" s="7">
+        <v>0.0563419</v>
+      </c>
+      <c r="F3" s="7">
+        <v>-0.003753</v>
+      </c>
+      <c r="G3" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="H3" s="7">
+        <v>0.122002</v>
+      </c>
+      <c r="I3" s="7">
+        <v>-0.045195</v>
+      </c>
+      <c r="J3" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="K3" s="7">
+        <v>0.132857</v>
+      </c>
+      <c r="L3" s="7">
+        <v>-0.022211</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="C4" s="7">
+        <v>72.0</v>
+      </c>
+      <c r="D4" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="E4" s="7">
+        <v>0.09968</v>
+      </c>
+      <c r="F4" s="7">
+        <v>0.01147</v>
+      </c>
+      <c r="G4" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="H4" s="7">
+        <v>0.3459</v>
+      </c>
+      <c r="I4" s="7">
+        <v>0.152536</v>
+      </c>
+      <c r="J4" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="K4" s="7">
+        <v>0.140796</v>
+      </c>
+      <c r="L4" s="7">
+        <v>0.039724</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="C5" s="7">
+        <v>48.0</v>
+      </c>
+      <c r="D5" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="E5" s="7">
+        <v>0.299593</v>
+      </c>
+      <c r="F5" s="7">
+        <v>-0.094855</v>
+      </c>
+      <c r="G5" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="H5" s="7">
+        <v>0.165687</v>
+      </c>
+      <c r="I5" s="7">
+        <v>0.039983</v>
+      </c>
+      <c r="J5" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="K5" s="7">
+        <v>0.166992</v>
+      </c>
+      <c r="L5" s="7">
+        <v>0.040403</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="C6" s="7">
+        <v>72.0</v>
+      </c>
+      <c r="D6" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="E6" s="7">
+        <v>0.273452</v>
+      </c>
+      <c r="F6" s="7">
+        <v>0.095401</v>
+      </c>
+      <c r="G6" s="7">
+        <v>7.0</v>
+      </c>
+      <c r="H6" s="7">
+        <v>0.290725</v>
+      </c>
+      <c r="I6" s="7">
+        <v>-0.247398</v>
+      </c>
+      <c r="J6" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="K6" s="7">
+        <v>0.293721</v>
+      </c>
+      <c r="L6" s="7">
+        <v>-0.259891</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="C7" s="7">
+        <v>48.0</v>
+      </c>
+      <c r="D7" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.302278</v>
+      </c>
+      <c r="F7" s="7">
+        <v>0.216884</v>
+      </c>
+      <c r="G7" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="H7" s="7">
+        <v>0.57742</v>
+      </c>
+      <c r="I7" s="7">
+        <v>0.394852</v>
+      </c>
+      <c r="J7" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="K7" s="7">
+        <v>0.581207</v>
+      </c>
+      <c r="L7" s="7">
+        <v>0.448983</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="C8" s="7">
+        <v>72.0</v>
+      </c>
+      <c r="D8" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0.648478</v>
+      </c>
+      <c r="F8" s="7">
+        <v>0.415064</v>
+      </c>
+      <c r="G8" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="H8" s="7">
+        <v>0.768339</v>
+      </c>
+      <c r="I8" s="7">
+        <v>0.403431</v>
+      </c>
+      <c r="J8" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="K8" s="7">
+        <v>0.720302</v>
+      </c>
+      <c r="L8" s="7">
+        <v>0.461317</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="C9" s="7">
+        <v>48.0</v>
+      </c>
+      <c r="D9" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.439882</v>
+      </c>
+      <c r="F9" s="7">
+        <v>0.27209</v>
+      </c>
+      <c r="G9" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="H9" s="7">
+        <v>0.0798324</v>
+      </c>
+      <c r="I9" s="7">
+        <v>5.31E-4</v>
+      </c>
+      <c r="J9" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="K9" s="7">
+        <v>0.0996823</v>
+      </c>
+      <c r="L9" s="7">
+        <v>-0.017615</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="C10" s="7">
+        <v>72.0</v>
+      </c>
+      <c r="D10" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.188511</v>
+      </c>
+      <c r="F10" s="7">
+        <v>0.091326</v>
+      </c>
+      <c r="G10" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="H10" s="7">
+        <v>0.205691</v>
+      </c>
+      <c r="I10" s="7">
+        <v>0.106242</v>
+      </c>
+      <c r="J10" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="K10" s="7">
+        <v>0.166254</v>
+      </c>
+      <c r="L10" s="7">
+        <v>0.151412</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="18">
+        <v>1.5</v>
+      </c>
+      <c r="C11" s="18">
+        <v>48.0</v>
+      </c>
+      <c r="D11" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="E11" s="18">
+        <v>0.0782306</v>
+      </c>
+      <c r="F11" s="18">
+        <v>-0.021749</v>
+      </c>
+      <c r="G11" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="H11" s="18">
+        <v>0.0829006</v>
+      </c>
+      <c r="I11" s="18">
+        <v>-0.026013</v>
+      </c>
+      <c r="J11" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="K11" s="18">
+        <v>0.0471715</v>
+      </c>
+      <c r="L11" s="18">
+        <v>-0.006232</v>
+      </c>
+      <c r="M11" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="N11" s="19"/>
+      <c r="O11" s="19"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="19"/>
+      <c r="U11" s="19"/>
+      <c r="V11" s="19"/>
+      <c r="W11" s="19"/>
+      <c r="X11" s="19"/>
+      <c r="Y11" s="19"/>
+      <c r="Z11" s="19"/>
+      <c r="AA11" s="19"/>
+      <c r="AB11" s="19"/>
+      <c r="AC11" s="19"/>
+      <c r="AD11" s="19"/>
+      <c r="AE11" s="19"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="C12" s="7">
+        <v>72.0</v>
+      </c>
+      <c r="G12" s="7">
+        <v>9.0</v>
+      </c>
+      <c r="H12" s="7">
+        <v>0.0990531</v>
+      </c>
+      <c r="I12" s="7">
+        <v>0.019526</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="18">
+        <v>2.0</v>
+      </c>
+      <c r="C13" s="18">
+        <v>48.0</v>
+      </c>
+      <c r="D13" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="E13" s="18">
+        <v>0.404484</v>
+      </c>
+      <c r="F13" s="18">
+        <v>-0.251714</v>
+      </c>
+      <c r="G13" s="18">
+        <v>2.0</v>
+      </c>
+      <c r="H13" s="18">
+        <v>0.339539</v>
+      </c>
+      <c r="I13" s="18">
+        <v>-0.264361</v>
+      </c>
+      <c r="J13" s="18">
+        <v>4.0</v>
+      </c>
+      <c r="K13" s="18">
+        <v>0.31387</v>
+      </c>
+      <c r="L13" s="18">
+        <v>-0.09202</v>
+      </c>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="19"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="19"/>
+      <c r="R13" s="19"/>
+      <c r="S13" s="19"/>
+      <c r="T13" s="19"/>
+      <c r="U13" s="19"/>
+      <c r="V13" s="19"/>
+      <c r="W13" s="19"/>
+      <c r="X13" s="19"/>
+      <c r="Y13" s="19"/>
+      <c r="Z13" s="19"/>
+      <c r="AA13" s="19"/>
+      <c r="AB13" s="19"/>
+      <c r="AC13" s="19"/>
+      <c r="AD13" s="19"/>
+      <c r="AE13" s="19"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="C14" s="7">
+        <v>72.0</v>
+      </c>
+      <c r="G14" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="H14" s="7">
+        <v>0.76562</v>
+      </c>
+      <c r="I14" s="7">
+        <v>0.359441</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="C15" s="7">
+        <v>48.0</v>
+      </c>
+      <c r="G15" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="H15" s="7">
+        <v>0.0379268</v>
+      </c>
+      <c r="I15" s="7">
+        <v>0.001728</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="C16" s="7">
+        <v>72.0</v>
+      </c>
+      <c r="D16" s="7">
+        <v>9.0</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.153509</v>
+      </c>
+      <c r="F16" s="7">
+        <v>0.072291</v>
+      </c>
+      <c r="G16" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="H16" s="7">
+        <v>0.188314</v>
+      </c>
+      <c r="I16" s="7">
+        <v>-0.056644</v>
+      </c>
+      <c r="J16" s="7">
+        <v>7.0</v>
+      </c>
+      <c r="K16" s="7">
+        <v>0.128848</v>
+      </c>
+      <c r="L16" s="7">
+        <v>0.195241</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="C17" s="7">
+        <v>48.0</v>
+      </c>
+      <c r="D17" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.275252</v>
+      </c>
+      <c r="F17" s="7">
+        <v>0.144195</v>
+      </c>
+      <c r="G17" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="H17" s="7">
+        <v>0.528085</v>
+      </c>
+      <c r="I17" s="7">
+        <v>0.110889</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" s="18">
+        <v>2.0</v>
+      </c>
+      <c r="C18" s="18">
+        <v>72.0</v>
+      </c>
+      <c r="D18" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="E18" s="18">
+        <v>0.285772</v>
+      </c>
+      <c r="F18" s="18">
+        <v>0.206562</v>
+      </c>
+      <c r="G18" s="18">
+        <v>3.0</v>
+      </c>
+      <c r="H18" s="18">
+        <v>0.143423</v>
+      </c>
+      <c r="I18" s="18">
+        <v>-0.054014</v>
+      </c>
+      <c r="J18" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="K18" s="18">
+        <v>0.273543</v>
+      </c>
+      <c r="L18" s="18">
+        <v>0.159298</v>
+      </c>
+      <c r="M18" s="19"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="19"/>
+      <c r="P18" s="19"/>
+      <c r="Q18" s="19"/>
+      <c r="R18" s="19"/>
+      <c r="S18" s="19"/>
+      <c r="T18" s="19"/>
+      <c r="U18" s="19"/>
+      <c r="V18" s="19"/>
+      <c r="W18" s="19"/>
+      <c r="X18" s="19"/>
+      <c r="Y18" s="19"/>
+      <c r="Z18" s="19"/>
+      <c r="AA18" s="19"/>
+      <c r="AB18" s="19"/>
+      <c r="AC18" s="19"/>
+      <c r="AD18" s="19"/>
+      <c r="AE18" s="19"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="J1:L1"/>
+  </mergeCells>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="E1" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="K1" s="13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="I2" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="L2" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="C3" s="7">
+        <v>48.0</v>
+      </c>
+      <c r="D3" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="E3" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="F3" s="7">
+        <v>0.0563419</v>
+      </c>
+      <c r="G3" s="7">
+        <v>-0.003753</v>
+      </c>
+      <c r="H3" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="I3" s="7">
+        <v>0.122002</v>
+      </c>
+      <c r="J3" s="7">
+        <v>-0.045195</v>
+      </c>
+      <c r="K3" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="L3" s="7">
+        <v>0.132857</v>
+      </c>
+      <c r="M3" s="7">
+        <v>-0.022211</v>
+      </c>
+      <c r="N3" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="C4" s="7">
+        <v>72.0</v>
+      </c>
+      <c r="D4" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="E4" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="F4" s="7">
+        <v>0.09968</v>
+      </c>
+      <c r="G4" s="7">
+        <v>0.01147</v>
+      </c>
+      <c r="H4" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="I4" s="7">
+        <v>0.3459</v>
+      </c>
+      <c r="J4" s="7">
+        <v>0.152536</v>
+      </c>
+      <c r="K4" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="L4" s="7">
+        <v>0.140796</v>
+      </c>
+      <c r="M4" s="7">
+        <v>0.039724</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="C5" s="7">
+        <v>48.0</v>
+      </c>
+      <c r="D5" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="E5" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="F5" s="7">
+        <v>0.299593</v>
+      </c>
+      <c r="G5" s="7">
+        <v>-0.094855</v>
+      </c>
+      <c r="H5" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="I5" s="7">
+        <v>0.165687</v>
+      </c>
+      <c r="J5" s="7">
+        <v>0.039983</v>
+      </c>
+      <c r="K5" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="L5" s="7">
+        <v>0.166992</v>
+      </c>
+      <c r="M5" s="7">
+        <v>0.040403</v>
+      </c>
+      <c r="O5" s="21"/>
+      <c r="P5" s="21"/>
+      <c r="Q5" s="21"/>
+      <c r="R5" s="21"/>
+      <c r="S5" s="21"/>
+      <c r="T5" s="21"/>
+      <c r="U5" s="21"/>
+      <c r="V5" s="21"/>
+      <c r="W5" s="21"/>
+      <c r="X5" s="21"/>
+      <c r="Y5" s="21"/>
+      <c r="Z5" s="21"/>
+      <c r="AA5" s="21"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="C6" s="7">
+        <v>72.0</v>
+      </c>
+      <c r="D6" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="E6" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="F6" s="7">
+        <v>0.273452</v>
+      </c>
+      <c r="G6" s="7">
+        <v>0.095401</v>
+      </c>
+      <c r="H6" s="7">
+        <v>7.0</v>
+      </c>
+      <c r="I6" s="7">
+        <v>0.290725</v>
+      </c>
+      <c r="J6" s="7">
+        <v>-0.247398</v>
+      </c>
+      <c r="K6" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="L6" s="7">
+        <v>0.293721</v>
+      </c>
+      <c r="M6" s="7">
+        <v>-0.259891</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="C7" s="7">
+        <v>48.0</v>
+      </c>
+      <c r="D7" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="F7" s="7">
+        <v>0.302278</v>
+      </c>
+      <c r="G7" s="7">
+        <v>0.216884</v>
+      </c>
+      <c r="H7" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="I7" s="7">
+        <v>0.57742</v>
+      </c>
+      <c r="J7" s="7">
+        <v>0.394852</v>
+      </c>
+      <c r="K7" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="L7" s="7">
+        <v>0.581207</v>
+      </c>
+      <c r="M7" s="7">
+        <v>0.448983</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="C8" s="7">
+        <v>72.0</v>
+      </c>
+      <c r="D8" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="F8" s="7">
+        <v>0.648478</v>
+      </c>
+      <c r="G8" s="7">
+        <v>0.415064</v>
+      </c>
+      <c r="H8" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="I8" s="7">
+        <v>0.768339</v>
+      </c>
+      <c r="J8" s="7">
+        <v>0.403431</v>
+      </c>
+      <c r="K8" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="L8" s="7">
+        <v>0.720302</v>
+      </c>
+      <c r="M8" s="7">
+        <v>0.461317</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="C9" s="7">
+        <v>48.0</v>
+      </c>
+      <c r="D9" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="F9" s="7">
+        <v>0.439882</v>
+      </c>
+      <c r="G9" s="7">
+        <v>0.27209</v>
+      </c>
+      <c r="H9" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="I9" s="7">
+        <v>0.0798324</v>
+      </c>
+      <c r="J9" s="7">
+        <v>5.31E-4</v>
+      </c>
+      <c r="K9" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="L9" s="7">
+        <v>0.0996823</v>
+      </c>
+      <c r="M9" s="7">
+        <v>-0.017615</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="C10" s="7">
+        <v>72.0</v>
+      </c>
+      <c r="D10" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="F10" s="7">
+        <v>0.188511</v>
+      </c>
+      <c r="G10" s="7">
+        <v>0.091326</v>
+      </c>
+      <c r="H10" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="I10" s="7">
+        <v>0.205691</v>
+      </c>
+      <c r="J10" s="7">
+        <v>0.106242</v>
+      </c>
+      <c r="K10" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="L10" s="7">
+        <v>0.166254</v>
+      </c>
+      <c r="M10" s="7">
+        <v>0.151412</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="18">
+        <v>1.5</v>
+      </c>
+      <c r="C11" s="18">
+        <v>48.0</v>
+      </c>
+      <c r="D11" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="E11" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="F11" s="18">
+        <v>0.0782306</v>
+      </c>
+      <c r="G11" s="18">
+        <v>-0.021749</v>
+      </c>
+      <c r="H11" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="I11" s="18">
+        <v>0.0829006</v>
+      </c>
+      <c r="J11" s="18">
+        <v>-0.026013</v>
+      </c>
+      <c r="K11" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="L11" s="18">
+        <v>0.0471715</v>
+      </c>
+      <c r="M11" s="18">
+        <v>-0.006232</v>
+      </c>
+      <c r="N11" s="18" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="C12" s="7">
+        <v>72.0</v>
+      </c>
+      <c r="D12" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="H12" s="7">
+        <v>9.0</v>
+      </c>
+      <c r="I12" s="7">
+        <v>0.0990531</v>
+      </c>
+      <c r="J12" s="7">
+        <v>0.019526</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="18">
+        <v>2.0</v>
+      </c>
+      <c r="C13" s="18">
+        <v>48.0</v>
+      </c>
+      <c r="D13" s="20">
+        <v>1.0</v>
+      </c>
+      <c r="E13" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="F13" s="18">
+        <v>0.404484</v>
+      </c>
+      <c r="G13" s="18">
+        <v>-0.251714</v>
+      </c>
+      <c r="H13" s="18">
+        <v>2.0</v>
+      </c>
+      <c r="I13" s="18">
+        <v>0.339539</v>
+      </c>
+      <c r="J13" s="18">
+        <v>-0.264361</v>
+      </c>
+      <c r="K13" s="18">
+        <v>4.0</v>
+      </c>
+      <c r="L13" s="18">
+        <v>0.31387</v>
+      </c>
+      <c r="M13" s="18">
+        <v>-0.09202</v>
+      </c>
+      <c r="N13" s="19"/>
+      <c r="O13" s="21"/>
+      <c r="P13" s="21"/>
+      <c r="Q13" s="21"/>
+      <c r="R13" s="21"/>
+      <c r="S13" s="21"/>
+      <c r="T13" s="21"/>
+      <c r="U13" s="21"/>
+      <c r="V13" s="21"/>
+      <c r="W13" s="21"/>
+      <c r="X13" s="21"/>
+      <c r="Y13" s="21"/>
+      <c r="Z13" s="21"/>
+      <c r="AA13" s="21"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="C14" s="7">
+        <v>72.0</v>
+      </c>
+      <c r="D14" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="F14" s="7">
+        <v>0.687837</v>
+      </c>
+      <c r="G14" s="7">
+        <v>0.145153</v>
+      </c>
+      <c r="H14" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="I14" s="7">
+        <v>0.758792</v>
+      </c>
+      <c r="J14" s="7">
+        <v>0.186581</v>
+      </c>
+      <c r="K14" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="L14" s="7">
+        <v>0.12286</v>
+      </c>
+      <c r="M14" s="7">
+        <v>0.02199</v>
+      </c>
+      <c r="N14" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="C15" s="7">
+        <v>48.0</v>
+      </c>
+      <c r="D15" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="H15" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="I15" s="7">
+        <v>0.0379268</v>
+      </c>
+      <c r="J15" s="7">
+        <v>0.001728</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="C16" s="7">
+        <v>72.0</v>
+      </c>
+      <c r="D16" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="E16" s="7">
+        <v>9.0</v>
+      </c>
+      <c r="F16" s="7">
+        <v>0.153509</v>
+      </c>
+      <c r="G16" s="7">
+        <v>0.072291</v>
+      </c>
+      <c r="H16" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="I16" s="7">
+        <v>0.188314</v>
+      </c>
+      <c r="J16" s="7">
+        <v>-0.056644</v>
+      </c>
+      <c r="K16" s="7">
+        <v>7.0</v>
+      </c>
+      <c r="L16" s="7">
+        <v>0.128848</v>
+      </c>
+      <c r="M16" s="7">
+        <v>0.195241</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="C17" s="7">
+        <v>48.0</v>
+      </c>
+      <c r="D17" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="F17" s="7">
+        <v>0.275252</v>
+      </c>
+      <c r="G17" s="7">
+        <v>0.144195</v>
+      </c>
+      <c r="H17" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="I17" s="7">
+        <v>0.528085</v>
+      </c>
+      <c r="J17" s="7">
+        <v>0.110889</v>
+      </c>
+      <c r="K17" s="7">
+        <v>6.0</v>
+      </c>
+      <c r="L17" s="7">
+        <v>0.692386</v>
+      </c>
+      <c r="M17" s="7">
+        <v>0.616835</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="18">
+        <v>2.0</v>
+      </c>
+      <c r="C18" s="18">
+        <v>72.0</v>
+      </c>
+      <c r="D18" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="E18" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="F18" s="18">
+        <v>0.285772</v>
+      </c>
+      <c r="G18" s="18">
+        <v>0.206562</v>
+      </c>
+      <c r="H18" s="18">
+        <v>3.0</v>
+      </c>
+      <c r="I18" s="18">
+        <v>0.143423</v>
+      </c>
+      <c r="J18" s="18">
+        <v>-0.054014</v>
+      </c>
+      <c r="K18" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="L18" s="18">
+        <v>0.273543</v>
+      </c>
+      <c r="M18" s="18">
+        <v>0.159298</v>
+      </c>
+      <c r="N18" s="19"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:M1"/>
+  </mergeCells>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="10.25"/>
+    <col customWidth="1" min="2" max="2" width="8.25"/>
+    <col customWidth="1" min="3" max="3" width="9.13"/>
+    <col customWidth="1" min="4" max="4" width="6.25"/>
+    <col customWidth="1" min="5" max="5" width="8.13"/>
+    <col customWidth="1" min="6" max="6" width="14.63"/>
+    <col customWidth="1" min="8" max="8" width="15.75"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" s="22" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="C2" s="7">
+        <v>48.0</v>
+      </c>
+      <c r="D2" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="E2" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="F2" s="7">
+        <v>0.122002</v>
+      </c>
+      <c r="G2" s="7">
+        <v>-0.045195</v>
+      </c>
+      <c r="H2" s="23" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="C3" s="7">
+        <v>72.0</v>
+      </c>
+      <c r="D3" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="E3" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="F3" s="7">
+        <v>0.3459</v>
+      </c>
+      <c r="G3" s="7">
+        <v>0.152536</v>
+      </c>
+      <c r="H3" s="24"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="C4" s="7">
+        <v>48.0</v>
+      </c>
+      <c r="D4" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="E4" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="F4" s="7">
+        <v>0.165687</v>
+      </c>
+      <c r="G4" s="7">
+        <v>0.039983</v>
+      </c>
+      <c r="H4" s="24"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="C5" s="7">
+        <v>72.0</v>
+      </c>
+      <c r="D5" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="E5" s="7">
+        <v>7.0</v>
+      </c>
+      <c r="F5" s="7">
+        <v>0.290725</v>
+      </c>
+      <c r="G5" s="7">
+        <v>-0.247398</v>
+      </c>
+      <c r="H5" s="24"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="C6" s="7">
+        <v>48.0</v>
+      </c>
+      <c r="D6" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="E6" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="F6" s="7">
+        <v>0.57742</v>
+      </c>
+      <c r="G6" s="7">
+        <v>0.394852</v>
+      </c>
+      <c r="H6" s="24"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="C7" s="7">
+        <v>72.0</v>
+      </c>
+      <c r="D7" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="F7" s="7">
+        <v>0.768339</v>
+      </c>
+      <c r="G7" s="7">
+        <v>0.403431</v>
+      </c>
+      <c r="H7" s="24"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="C8" s="7">
+        <v>48.0</v>
+      </c>
+      <c r="D8" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="F8" s="7">
+        <v>0.0798324</v>
+      </c>
+      <c r="G8" s="7">
+        <v>5.31E-4</v>
+      </c>
+      <c r="H8" s="24"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="C9" s="7">
+        <v>72.0</v>
+      </c>
+      <c r="D9" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="F9" s="7">
+        <v>0.205691</v>
+      </c>
+      <c r="G9" s="7">
+        <v>0.106242</v>
+      </c>
+      <c r="H9" s="24"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="C10" s="7">
+        <v>48.0</v>
+      </c>
+      <c r="D10" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="F10" s="7">
+        <v>0.0829006</v>
+      </c>
+      <c r="G10" s="7">
+        <v>-0.026013</v>
+      </c>
+      <c r="H10" s="23" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="C11" s="7">
+        <v>72.0</v>
+      </c>
+      <c r="D11" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="E11" s="7">
+        <v>9.0</v>
+      </c>
+      <c r="F11" s="7">
+        <v>0.0990531</v>
+      </c>
+      <c r="G11" s="7">
+        <v>0.019526</v>
+      </c>
+      <c r="H11" s="24"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="C12" s="7">
+        <v>48.0</v>
+      </c>
+      <c r="D12" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="E12" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="F12" s="7">
+        <v>0.339539</v>
+      </c>
+      <c r="G12" s="7">
+        <v>-0.264361</v>
+      </c>
+      <c r="H12" s="24"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="C13" s="7">
+        <v>72.0</v>
+      </c>
+      <c r="D13" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="F13" s="7">
+        <v>0.76562</v>
+      </c>
+      <c r="G13" s="7">
+        <v>0.359441</v>
+      </c>
+      <c r="H13" s="24"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="C14" s="7">
+        <v>48.0</v>
+      </c>
+      <c r="D14" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="F14" s="7">
+        <v>0.0379268</v>
+      </c>
+      <c r="G14" s="7">
+        <v>0.001728</v>
+      </c>
+      <c r="H14" s="24"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="C15" s="7">
+        <v>72.0</v>
+      </c>
+      <c r="D15" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="F15" s="7">
+        <v>0.188314</v>
+      </c>
+      <c r="G15" s="7">
+        <v>-0.056644</v>
+      </c>
+      <c r="H15" s="24"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="C16" s="7">
+        <v>48.0</v>
+      </c>
+      <c r="D16" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="F16" s="7">
+        <v>0.528085</v>
+      </c>
+      <c r="G16" s="7">
+        <v>0.110889</v>
+      </c>
+      <c r="H16" s="24"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="C17" s="7">
+        <v>72.0</v>
+      </c>
+      <c r="D17" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="E17" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="F17" s="7">
+        <v>0.143423</v>
+      </c>
+      <c r="G17" s="7">
+        <v>-0.054014</v>
+      </c>
+      <c r="H17" s="24"/>
+    </row>
+    <row r="18">
+      <c r="H18" s="24"/>
+    </row>
+    <row r="19">
+      <c r="H19" s="24"/>
+    </row>
+    <row r="20">
+      <c r="H20" s="24"/>
+    </row>
+    <row r="21">
+      <c r="H21" s="24"/>
+    </row>
+    <row r="22">
+      <c r="H22" s="24"/>
+    </row>
+    <row r="23">
+      <c r="H23" s="24"/>
+    </row>
+    <row r="24">
+      <c r="H24" s="24"/>
+    </row>
+    <row r="25">
+      <c r="H25" s="24"/>
+    </row>
+    <row r="26">
+      <c r="H26" s="24"/>
+    </row>
+    <row r="27">
+      <c r="H27" s="24"/>
+    </row>
+    <row r="28">
+      <c r="H28" s="24"/>
+    </row>
+    <row r="29">
+      <c r="H29" s="24"/>
+    </row>
+    <row r="30">
+      <c r="H30" s="24"/>
+    </row>
+    <row r="31">
+      <c r="H31" s="24"/>
+    </row>
+    <row r="32">
+      <c r="H32" s="24"/>
+    </row>
+    <row r="33">
+      <c r="H33" s="24"/>
+    </row>
+    <row r="34">
+      <c r="H34" s="24"/>
+    </row>
+    <row r="35">
+      <c r="H35" s="24"/>
+    </row>
+    <row r="36">
+      <c r="H36" s="24"/>
+    </row>
+    <row r="37">
+      <c r="H37" s="24"/>
+    </row>
+    <row r="38">
+      <c r="H38" s="24"/>
+    </row>
+    <row r="39">
+      <c r="H39" s="24"/>
+    </row>
+    <row r="40">
+      <c r="H40" s="24"/>
+    </row>
+    <row r="41">
+      <c r="H41" s="24"/>
+    </row>
+    <row r="42">
+      <c r="H42" s="24"/>
+    </row>
+    <row r="43">
+      <c r="H43" s="24"/>
+    </row>
+    <row r="44">
+      <c r="H44" s="24"/>
+    </row>
+    <row r="45">
+      <c r="H45" s="24"/>
+    </row>
+    <row r="46">
+      <c r="H46" s="24"/>
+    </row>
+    <row r="47">
+      <c r="H47" s="24"/>
+    </row>
+    <row r="48">
+      <c r="H48" s="24"/>
+    </row>
+    <row r="49">
+      <c r="H49" s="24"/>
+    </row>
+    <row r="50">
+      <c r="H50" s="24"/>
+    </row>
+    <row r="51">
+      <c r="H51" s="24"/>
+    </row>
+    <row r="52">
+      <c r="H52" s="24"/>
+    </row>
+    <row r="53">
+      <c r="H53" s="24"/>
+    </row>
+    <row r="54">
+      <c r="H54" s="24"/>
+    </row>
+    <row r="55">
+      <c r="H55" s="24"/>
+    </row>
+    <row r="56">
+      <c r="H56" s="24"/>
+    </row>
+    <row r="57">
+      <c r="H57" s="24"/>
+    </row>
+    <row r="58">
+      <c r="H58" s="24"/>
+    </row>
+    <row r="59">
+      <c r="H59" s="24"/>
+    </row>
+    <row r="60">
+      <c r="H60" s="24"/>
+    </row>
+    <row r="61">
+      <c r="H61" s="24"/>
+    </row>
+    <row r="62">
+      <c r="H62" s="24"/>
+    </row>
+    <row r="63">
+      <c r="H63" s="24"/>
+    </row>
+    <row r="64">
+      <c r="H64" s="24"/>
+    </row>
+    <row r="65">
+      <c r="H65" s="24"/>
+    </row>
+    <row r="66">
+      <c r="H66" s="24"/>
+    </row>
+    <row r="67">
+      <c r="H67" s="24"/>
+    </row>
+    <row r="68">
+      <c r="H68" s="24"/>
+    </row>
+    <row r="69">
+      <c r="H69" s="24"/>
+    </row>
+    <row r="70">
+      <c r="H70" s="24"/>
+    </row>
+    <row r="71">
+      <c r="H71" s="24"/>
+    </row>
+    <row r="72">
+      <c r="H72" s="24"/>
+    </row>
+    <row r="73">
+      <c r="H73" s="24"/>
+    </row>
+    <row r="74">
+      <c r="H74" s="24"/>
+    </row>
+    <row r="75">
+      <c r="H75" s="24"/>
+    </row>
+    <row r="76">
+      <c r="H76" s="24"/>
+    </row>
+    <row r="77">
+      <c r="H77" s="24"/>
+    </row>
+    <row r="78">
+      <c r="H78" s="24"/>
+    </row>
+    <row r="79">
+      <c r="H79" s="24"/>
+    </row>
+    <row r="80">
+      <c r="H80" s="24"/>
+    </row>
+    <row r="81">
+      <c r="H81" s="24"/>
+    </row>
+    <row r="82">
+      <c r="H82" s="24"/>
+    </row>
+    <row r="83">
+      <c r="H83" s="24"/>
+    </row>
+    <row r="84">
+      <c r="H84" s="24"/>
+    </row>
+    <row r="85">
+      <c r="H85" s="24"/>
+    </row>
+    <row r="86">
+      <c r="H86" s="24"/>
+    </row>
+    <row r="87">
+      <c r="H87" s="24"/>
+    </row>
+    <row r="88">
+      <c r="H88" s="24"/>
+    </row>
+    <row r="89">
+      <c r="H89" s="24"/>
+    </row>
+    <row r="90">
+      <c r="H90" s="24"/>
+    </row>
+    <row r="91">
+      <c r="H91" s="24"/>
+    </row>
+    <row r="92">
+      <c r="H92" s="24"/>
+    </row>
+    <row r="93">
+      <c r="H93" s="24"/>
+    </row>
+    <row r="94">
+      <c r="H94" s="24"/>
+    </row>
+    <row r="95">
+      <c r="H95" s="24"/>
+    </row>
+    <row r="96">
+      <c r="H96" s="24"/>
+    </row>
+    <row r="97">
+      <c r="H97" s="24"/>
+    </row>
+    <row r="98">
+      <c r="H98" s="24"/>
+    </row>
+    <row r="99">
+      <c r="H99" s="24"/>
+    </row>
+    <row r="100">
+      <c r="H100" s="24"/>
+    </row>
+    <row r="101">
+      <c r="H101" s="24"/>
+    </row>
+    <row r="102">
+      <c r="H102" s="24"/>
+    </row>
+    <row r="103">
+      <c r="H103" s="24"/>
+    </row>
+    <row r="104">
+      <c r="H104" s="24"/>
+    </row>
+    <row r="105">
+      <c r="H105" s="24"/>
+    </row>
+    <row r="106">
+      <c r="H106" s="24"/>
+    </row>
+    <row r="107">
+      <c r="H107" s="24"/>
+    </row>
+    <row r="108">
+      <c r="H108" s="24"/>
+    </row>
+    <row r="109">
+      <c r="H109" s="24"/>
+    </row>
+    <row r="110">
+      <c r="H110" s="24"/>
+    </row>
+    <row r="111">
+      <c r="H111" s="24"/>
+    </row>
+    <row r="112">
+      <c r="H112" s="24"/>
+    </row>
+    <row r="113">
+      <c r="H113" s="24"/>
+    </row>
+    <row r="114">
+      <c r="H114" s="24"/>
+    </row>
+    <row r="115">
+      <c r="H115" s="24"/>
+    </row>
+    <row r="116">
+      <c r="H116" s="24"/>
+    </row>
+    <row r="117">
+      <c r="H117" s="24"/>
+    </row>
+    <row r="118">
+      <c r="H118" s="24"/>
+    </row>
+    <row r="119">
+      <c r="H119" s="24"/>
+    </row>
+    <row r="120">
+      <c r="H120" s="24"/>
+    </row>
+    <row r="121">
+      <c r="H121" s="24"/>
+    </row>
+    <row r="122">
+      <c r="H122" s="24"/>
+    </row>
+    <row r="123">
+      <c r="H123" s="24"/>
+    </row>
+    <row r="124">
+      <c r="H124" s="24"/>
+    </row>
+    <row r="125">
+      <c r="H125" s="24"/>
+    </row>
+    <row r="126">
+      <c r="H126" s="24"/>
+    </row>
+    <row r="127">
+      <c r="H127" s="24"/>
+    </row>
+    <row r="128">
+      <c r="H128" s="24"/>
+    </row>
+    <row r="129">
+      <c r="H129" s="24"/>
+    </row>
+    <row r="130">
+      <c r="H130" s="24"/>
+    </row>
+    <row r="131">
+      <c r="H131" s="24"/>
+    </row>
+    <row r="132">
+      <c r="H132" s="24"/>
+    </row>
+    <row r="133">
+      <c r="H133" s="24"/>
+    </row>
+    <row r="134">
+      <c r="H134" s="24"/>
+    </row>
+    <row r="135">
+      <c r="H135" s="24"/>
+    </row>
+    <row r="136">
+      <c r="H136" s="24"/>
+    </row>
+    <row r="137">
+      <c r="H137" s="24"/>
+    </row>
+    <row r="138">
+      <c r="H138" s="24"/>
+    </row>
+    <row r="139">
+      <c r="H139" s="24"/>
+    </row>
+    <row r="140">
+      <c r="H140" s="24"/>
+    </row>
+    <row r="141">
+      <c r="H141" s="24"/>
+    </row>
+    <row r="142">
+      <c r="H142" s="24"/>
+    </row>
+    <row r="143">
+      <c r="H143" s="24"/>
+    </row>
+    <row r="144">
+      <c r="H144" s="24"/>
+    </row>
+    <row r="145">
+      <c r="H145" s="24"/>
+    </row>
+    <row r="146">
+      <c r="H146" s="24"/>
+    </row>
+    <row r="147">
+      <c r="H147" s="24"/>
+    </row>
+    <row r="148">
+      <c r="H148" s="24"/>
+    </row>
+    <row r="149">
+      <c r="H149" s="24"/>
+    </row>
+    <row r="150">
+      <c r="H150" s="24"/>
+    </row>
+    <row r="151">
+      <c r="H151" s="24"/>
+    </row>
+    <row r="152">
+      <c r="H152" s="24"/>
+    </row>
+    <row r="153">
+      <c r="H153" s="24"/>
+    </row>
+    <row r="154">
+      <c r="H154" s="24"/>
+    </row>
+    <row r="155">
+      <c r="H155" s="24"/>
+    </row>
+    <row r="156">
+      <c r="H156" s="24"/>
+    </row>
+    <row r="157">
+      <c r="H157" s="24"/>
+    </row>
+    <row r="158">
+      <c r="H158" s="24"/>
+    </row>
+    <row r="159">
+      <c r="H159" s="24"/>
+    </row>
+    <row r="160">
+      <c r="H160" s="24"/>
+    </row>
+    <row r="161">
+      <c r="H161" s="24"/>
+    </row>
+    <row r="162">
+      <c r="H162" s="24"/>
+    </row>
+    <row r="163">
+      <c r="H163" s="24"/>
+    </row>
+    <row r="164">
+      <c r="H164" s="24"/>
+    </row>
+    <row r="165">
+      <c r="H165" s="24"/>
+    </row>
+    <row r="166">
+      <c r="H166" s="24"/>
+    </row>
+    <row r="167">
+      <c r="H167" s="24"/>
+    </row>
+    <row r="168">
+      <c r="H168" s="24"/>
+    </row>
+    <row r="169">
+      <c r="H169" s="24"/>
+    </row>
+    <row r="170">
+      <c r="H170" s="24"/>
+    </row>
+    <row r="171">
+      <c r="H171" s="24"/>
+    </row>
+    <row r="172">
+      <c r="H172" s="24"/>
+    </row>
+    <row r="173">
+      <c r="H173" s="24"/>
+    </row>
+    <row r="174">
+      <c r="H174" s="24"/>
+    </row>
+    <row r="175">
+      <c r="H175" s="24"/>
+    </row>
+    <row r="176">
+      <c r="H176" s="24"/>
+    </row>
+    <row r="177">
+      <c r="H177" s="24"/>
+    </row>
+    <row r="178">
+      <c r="H178" s="24"/>
+    </row>
+    <row r="179">
+      <c r="H179" s="24"/>
+    </row>
+    <row r="180">
+      <c r="H180" s="24"/>
+    </row>
+    <row r="181">
+      <c r="H181" s="24"/>
+    </row>
+    <row r="182">
+      <c r="H182" s="24"/>
+    </row>
+    <row r="183">
+      <c r="H183" s="24"/>
+    </row>
+    <row r="184">
+      <c r="H184" s="24"/>
+    </row>
+    <row r="185">
+      <c r="H185" s="24"/>
+    </row>
+    <row r="186">
+      <c r="H186" s="24"/>
+    </row>
+    <row r="187">
+      <c r="H187" s="24"/>
+    </row>
+    <row r="188">
+      <c r="H188" s="24"/>
+    </row>
+    <row r="189">
+      <c r="H189" s="24"/>
+    </row>
+    <row r="190">
+      <c r="H190" s="24"/>
+    </row>
+    <row r="191">
+      <c r="H191" s="24"/>
+    </row>
+    <row r="192">
+      <c r="H192" s="24"/>
+    </row>
+    <row r="193">
+      <c r="H193" s="24"/>
+    </row>
+    <row r="194">
+      <c r="H194" s="24"/>
+    </row>
+    <row r="195">
+      <c r="H195" s="24"/>
+    </row>
+    <row r="196">
+      <c r="H196" s="24"/>
+    </row>
+    <row r="197">
+      <c r="H197" s="24"/>
+    </row>
+    <row r="198">
+      <c r="H198" s="24"/>
+    </row>
+    <row r="199">
+      <c r="H199" s="24"/>
+    </row>
+    <row r="200">
+      <c r="H200" s="24"/>
+    </row>
+    <row r="201">
+      <c r="H201" s="24"/>
+    </row>
+    <row r="202">
+      <c r="H202" s="24"/>
+    </row>
+    <row r="203">
+      <c r="H203" s="24"/>
+    </row>
+    <row r="204">
+      <c r="H204" s="24"/>
+    </row>
+    <row r="205">
+      <c r="H205" s="24"/>
+    </row>
+    <row r="206">
+      <c r="H206" s="24"/>
+    </row>
+    <row r="207">
+      <c r="H207" s="24"/>
+    </row>
+    <row r="208">
+      <c r="H208" s="24"/>
+    </row>
+    <row r="209">
+      <c r="H209" s="24"/>
+    </row>
+    <row r="210">
+      <c r="H210" s="24"/>
+    </row>
+    <row r="211">
+      <c r="H211" s="24"/>
+    </row>
+    <row r="212">
+      <c r="H212" s="24"/>
+    </row>
+    <row r="213">
+      <c r="H213" s="24"/>
+    </row>
+    <row r="214">
+      <c r="H214" s="24"/>
+    </row>
+    <row r="215">
+      <c r="H215" s="24"/>
+    </row>
+    <row r="216">
+      <c r="H216" s="24"/>
+    </row>
+    <row r="217">
+      <c r="H217" s="24"/>
+    </row>
+    <row r="218">
+      <c r="H218" s="24"/>
+    </row>
+    <row r="219">
+      <c r="H219" s="24"/>
+    </row>
+    <row r="220">
+      <c r="H220" s="24"/>
+    </row>
+    <row r="221">
+      <c r="H221" s="24"/>
+    </row>
+    <row r="222">
+      <c r="H222" s="24"/>
+    </row>
+    <row r="223">
+      <c r="H223" s="24"/>
+    </row>
+    <row r="224">
+      <c r="H224" s="24"/>
+    </row>
+    <row r="225">
+      <c r="H225" s="24"/>
+    </row>
+    <row r="226">
+      <c r="H226" s="24"/>
+    </row>
+    <row r="227">
+      <c r="H227" s="24"/>
+    </row>
+    <row r="228">
+      <c r="H228" s="24"/>
+    </row>
+    <row r="229">
+      <c r="H229" s="24"/>
+    </row>
+    <row r="230">
+      <c r="H230" s="24"/>
+    </row>
+    <row r="231">
+      <c r="H231" s="24"/>
+    </row>
+    <row r="232">
+      <c r="H232" s="24"/>
+    </row>
+    <row r="233">
+      <c r="H233" s="24"/>
+    </row>
+    <row r="234">
+      <c r="H234" s="24"/>
+    </row>
+    <row r="235">
+      <c r="H235" s="24"/>
+    </row>
+    <row r="236">
+      <c r="H236" s="24"/>
+    </row>
+    <row r="237">
+      <c r="H237" s="24"/>
+    </row>
+    <row r="238">
+      <c r="H238" s="24"/>
+    </row>
+    <row r="239">
+      <c r="H239" s="24"/>
+    </row>
+    <row r="240">
+      <c r="H240" s="24"/>
+    </row>
+    <row r="241">
+      <c r="H241" s="24"/>
+    </row>
+    <row r="242">
+      <c r="H242" s="24"/>
+    </row>
+    <row r="243">
+      <c r="H243" s="24"/>
+    </row>
+    <row r="244">
+      <c r="H244" s="24"/>
+    </row>
+    <row r="245">
+      <c r="H245" s="24"/>
+    </row>
+    <row r="246">
+      <c r="H246" s="24"/>
+    </row>
+    <row r="247">
+      <c r="H247" s="24"/>
+    </row>
+    <row r="248">
+      <c r="H248" s="24"/>
+    </row>
+    <row r="249">
+      <c r="H249" s="24"/>
+    </row>
+    <row r="250">
+      <c r="H250" s="24"/>
+    </row>
+    <row r="251">
+      <c r="H251" s="24"/>
+    </row>
+    <row r="252">
+      <c r="H252" s="24"/>
+    </row>
+    <row r="253">
+      <c r="H253" s="24"/>
+    </row>
+    <row r="254">
+      <c r="H254" s="24"/>
+    </row>
+    <row r="255">
+      <c r="H255" s="24"/>
+    </row>
+    <row r="256">
+      <c r="H256" s="24"/>
+    </row>
+    <row r="257">
+      <c r="H257" s="24"/>
+    </row>
+    <row r="258">
+      <c r="H258" s="24"/>
+    </row>
+    <row r="259">
+      <c r="H259" s="24"/>
+    </row>
+    <row r="260">
+      <c r="H260" s="24"/>
+    </row>
+    <row r="261">
+      <c r="H261" s="24"/>
+    </row>
+    <row r="262">
+      <c r="H262" s="24"/>
+    </row>
+    <row r="263">
+      <c r="H263" s="24"/>
+    </row>
+    <row r="264">
+      <c r="H264" s="24"/>
+    </row>
+    <row r="265">
+      <c r="H265" s="24"/>
+    </row>
+    <row r="266">
+      <c r="H266" s="24"/>
+    </row>
+    <row r="267">
+      <c r="H267" s="24"/>
+    </row>
+    <row r="268">
+      <c r="H268" s="24"/>
+    </row>
+    <row r="269">
+      <c r="H269" s="24"/>
+    </row>
+    <row r="270">
+      <c r="H270" s="24"/>
+    </row>
+    <row r="271">
+      <c r="H271" s="24"/>
+    </row>
+    <row r="272">
+      <c r="H272" s="24"/>
+    </row>
+    <row r="273">
+      <c r="H273" s="24"/>
+    </row>
+    <row r="274">
+      <c r="H274" s="24"/>
+    </row>
+    <row r="275">
+      <c r="H275" s="24"/>
+    </row>
+    <row r="276">
+      <c r="H276" s="24"/>
+    </row>
+    <row r="277">
+      <c r="H277" s="24"/>
+    </row>
+    <row r="278">
+      <c r="H278" s="24"/>
+    </row>
+    <row r="279">
+      <c r="H279" s="24"/>
+    </row>
+    <row r="280">
+      <c r="H280" s="24"/>
+    </row>
+    <row r="281">
+      <c r="H281" s="24"/>
+    </row>
+    <row r="282">
+      <c r="H282" s="24"/>
+    </row>
+    <row r="283">
+      <c r="H283" s="24"/>
+    </row>
+    <row r="284">
+      <c r="H284" s="24"/>
+    </row>
+    <row r="285">
+      <c r="H285" s="24"/>
+    </row>
+    <row r="286">
+      <c r="H286" s="24"/>
+    </row>
+    <row r="287">
+      <c r="H287" s="24"/>
+    </row>
+    <row r="288">
+      <c r="H288" s="24"/>
+    </row>
+    <row r="289">
+      <c r="H289" s="24"/>
+    </row>
+    <row r="290">
+      <c r="H290" s="24"/>
+    </row>
+    <row r="291">
+      <c r="H291" s="24"/>
+    </row>
+    <row r="292">
+      <c r="H292" s="24"/>
+    </row>
+    <row r="293">
+      <c r="H293" s="24"/>
+    </row>
+    <row r="294">
+      <c r="H294" s="24"/>
+    </row>
+    <row r="295">
+      <c r="H295" s="24"/>
+    </row>
+    <row r="296">
+      <c r="H296" s="24"/>
+    </row>
+    <row r="297">
+      <c r="H297" s="24"/>
+    </row>
+    <row r="298">
+      <c r="H298" s="24"/>
+    </row>
+    <row r="299">
+      <c r="H299" s="24"/>
+    </row>
+    <row r="300">
+      <c r="H300" s="24"/>
+    </row>
+    <row r="301">
+      <c r="H301" s="24"/>
+    </row>
+    <row r="302">
+      <c r="H302" s="24"/>
+    </row>
+    <row r="303">
+      <c r="H303" s="24"/>
+    </row>
+    <row r="304">
+      <c r="H304" s="24"/>
+    </row>
+    <row r="305">
+      <c r="H305" s="24"/>
+    </row>
+    <row r="306">
+      <c r="H306" s="24"/>
+    </row>
+    <row r="307">
+      <c r="H307" s="24"/>
+    </row>
+    <row r="308">
+      <c r="H308" s="24"/>
+    </row>
+    <row r="309">
+      <c r="H309" s="24"/>
+    </row>
+    <row r="310">
+      <c r="H310" s="24"/>
+    </row>
+    <row r="311">
+      <c r="H311" s="24"/>
+    </row>
+    <row r="312">
+      <c r="H312" s="24"/>
+    </row>
+    <row r="313">
+      <c r="H313" s="24"/>
+    </row>
+    <row r="314">
+      <c r="H314" s="24"/>
+    </row>
+    <row r="315">
+      <c r="H315" s="24"/>
+    </row>
+    <row r="316">
+      <c r="H316" s="24"/>
+    </row>
+    <row r="317">
+      <c r="H317" s="24"/>
+    </row>
+    <row r="318">
+      <c r="H318" s="24"/>
+    </row>
+    <row r="319">
+      <c r="H319" s="24"/>
+    </row>
+    <row r="320">
+      <c r="H320" s="24"/>
+    </row>
+    <row r="321">
+      <c r="H321" s="24"/>
+    </row>
+    <row r="322">
+      <c r="H322" s="24"/>
+    </row>
+    <row r="323">
+      <c r="H323" s="24"/>
+    </row>
+    <row r="324">
+      <c r="H324" s="24"/>
+    </row>
+    <row r="325">
+      <c r="H325" s="24"/>
+    </row>
+    <row r="326">
+      <c r="H326" s="24"/>
+    </row>
+    <row r="327">
+      <c r="H327" s="24"/>
+    </row>
+    <row r="328">
+      <c r="H328" s="24"/>
+    </row>
+    <row r="329">
+      <c r="H329" s="24"/>
+    </row>
+    <row r="330">
+      <c r="H330" s="24"/>
+    </row>
+    <row r="331">
+      <c r="H331" s="24"/>
+    </row>
+    <row r="332">
+      <c r="H332" s="24"/>
+    </row>
+    <row r="333">
+      <c r="H333" s="24"/>
+    </row>
+    <row r="334">
+      <c r="H334" s="24"/>
+    </row>
+    <row r="335">
+      <c r="H335" s="24"/>
+    </row>
+    <row r="336">
+      <c r="H336" s="24"/>
+    </row>
+    <row r="337">
+      <c r="H337" s="24"/>
+    </row>
+    <row r="338">
+      <c r="H338" s="24"/>
+    </row>
+    <row r="339">
+      <c r="H339" s="24"/>
+    </row>
+    <row r="340">
+      <c r="H340" s="24"/>
+    </row>
+    <row r="341">
+      <c r="H341" s="24"/>
+    </row>
+    <row r="342">
+      <c r="H342" s="24"/>
+    </row>
+    <row r="343">
+      <c r="H343" s="24"/>
+    </row>
+    <row r="344">
+      <c r="H344" s="24"/>
+    </row>
+    <row r="345">
+      <c r="H345" s="24"/>
+    </row>
+    <row r="346">
+      <c r="H346" s="24"/>
+    </row>
+    <row r="347">
+      <c r="H347" s="24"/>
+    </row>
+    <row r="348">
+      <c r="H348" s="24"/>
+    </row>
+    <row r="349">
+      <c r="H349" s="24"/>
+    </row>
+    <row r="350">
+      <c r="H350" s="24"/>
+    </row>
+    <row r="351">
+      <c r="H351" s="24"/>
+    </row>
+    <row r="352">
+      <c r="H352" s="24"/>
+    </row>
+    <row r="353">
+      <c r="H353" s="24"/>
+    </row>
+    <row r="354">
+      <c r="H354" s="24"/>
+    </row>
+    <row r="355">
+      <c r="H355" s="24"/>
+    </row>
+    <row r="356">
+      <c r="H356" s="24"/>
+    </row>
+    <row r="357">
+      <c r="H357" s="24"/>
+    </row>
+    <row r="358">
+      <c r="H358" s="24"/>
+    </row>
+    <row r="359">
+      <c r="H359" s="24"/>
+    </row>
+    <row r="360">
+      <c r="H360" s="24"/>
+    </row>
+    <row r="361">
+      <c r="H361" s="24"/>
+    </row>
+    <row r="362">
+      <c r="H362" s="24"/>
+    </row>
+    <row r="363">
+      <c r="H363" s="24"/>
+    </row>
+    <row r="364">
+      <c r="H364" s="24"/>
+    </row>
+    <row r="365">
+      <c r="H365" s="24"/>
+    </row>
+    <row r="366">
+      <c r="H366" s="24"/>
+    </row>
+    <row r="367">
+      <c r="H367" s="24"/>
+    </row>
+    <row r="368">
+      <c r="H368" s="24"/>
+    </row>
+    <row r="369">
+      <c r="H369" s="24"/>
+    </row>
+    <row r="370">
+      <c r="H370" s="24"/>
+    </row>
+    <row r="371">
+      <c r="H371" s="24"/>
+    </row>
+    <row r="372">
+      <c r="H372" s="24"/>
+    </row>
+    <row r="373">
+      <c r="H373" s="24"/>
+    </row>
+    <row r="374">
+      <c r="H374" s="24"/>
+    </row>
+    <row r="375">
+      <c r="H375" s="24"/>
+    </row>
+    <row r="376">
+      <c r="H376" s="24"/>
+    </row>
+    <row r="377">
+      <c r="H377" s="24"/>
+    </row>
+    <row r="378">
+      <c r="H378" s="24"/>
+    </row>
+    <row r="379">
+      <c r="H379" s="24"/>
+    </row>
+    <row r="380">
+      <c r="H380" s="24"/>
+    </row>
+    <row r="381">
+      <c r="H381" s="24"/>
+    </row>
+    <row r="382">
+      <c r="H382" s="24"/>
+    </row>
+    <row r="383">
+      <c r="H383" s="24"/>
+    </row>
+    <row r="384">
+      <c r="H384" s="24"/>
+    </row>
+    <row r="385">
+      <c r="H385" s="24"/>
+    </row>
+    <row r="386">
+      <c r="H386" s="24"/>
+    </row>
+    <row r="387">
+      <c r="H387" s="24"/>
+    </row>
+    <row r="388">
+      <c r="H388" s="24"/>
+    </row>
+    <row r="389">
+      <c r="H389" s="24"/>
+    </row>
+    <row r="390">
+      <c r="H390" s="24"/>
+    </row>
+    <row r="391">
+      <c r="H391" s="24"/>
+    </row>
+    <row r="392">
+      <c r="H392" s="24"/>
+    </row>
+    <row r="393">
+      <c r="H393" s="24"/>
+    </row>
+    <row r="394">
+      <c r="H394" s="24"/>
+    </row>
+    <row r="395">
+      <c r="H395" s="24"/>
+    </row>
+    <row r="396">
+      <c r="H396" s="24"/>
+    </row>
+    <row r="397">
+      <c r="H397" s="24"/>
+    </row>
+    <row r="398">
+      <c r="H398" s="24"/>
+    </row>
+    <row r="399">
+      <c r="H399" s="24"/>
+    </row>
+    <row r="400">
+      <c r="H400" s="24"/>
+    </row>
+    <row r="401">
+      <c r="H401" s="24"/>
+    </row>
+    <row r="402">
+      <c r="H402" s="24"/>
+    </row>
+    <row r="403">
+      <c r="H403" s="24"/>
+    </row>
+    <row r="404">
+      <c r="H404" s="24"/>
+    </row>
+    <row r="405">
+      <c r="H405" s="24"/>
+    </row>
+    <row r="406">
+      <c r="H406" s="24"/>
+    </row>
+    <row r="407">
+      <c r="H407" s="24"/>
+    </row>
+    <row r="408">
+      <c r="H408" s="24"/>
+    </row>
+    <row r="409">
+      <c r="H409" s="24"/>
+    </row>
+    <row r="410">
+      <c r="H410" s="24"/>
+    </row>
+    <row r="411">
+      <c r="H411" s="24"/>
+    </row>
+    <row r="412">
+      <c r="H412" s="24"/>
+    </row>
+    <row r="413">
+      <c r="H413" s="24"/>
+    </row>
+    <row r="414">
+      <c r="H414" s="24"/>
+    </row>
+    <row r="415">
+      <c r="H415" s="24"/>
+    </row>
+    <row r="416">
+      <c r="H416" s="24"/>
+    </row>
+    <row r="417">
+      <c r="H417" s="24"/>
+    </row>
+    <row r="418">
+      <c r="H418" s="24"/>
+    </row>
+    <row r="419">
+      <c r="H419" s="24"/>
+    </row>
+    <row r="420">
+      <c r="H420" s="24"/>
+    </row>
+    <row r="421">
+      <c r="H421" s="24"/>
+    </row>
+    <row r="422">
+      <c r="H422" s="24"/>
+    </row>
+    <row r="423">
+      <c r="H423" s="24"/>
+    </row>
+    <row r="424">
+      <c r="H424" s="24"/>
+    </row>
+    <row r="425">
+      <c r="H425" s="24"/>
+    </row>
+    <row r="426">
+      <c r="H426" s="24"/>
+    </row>
+    <row r="427">
+      <c r="H427" s="24"/>
+    </row>
+    <row r="428">
+      <c r="H428" s="24"/>
+    </row>
+    <row r="429">
+      <c r="H429" s="24"/>
+    </row>
+    <row r="430">
+      <c r="H430" s="24"/>
+    </row>
+    <row r="431">
+      <c r="H431" s="24"/>
+    </row>
+    <row r="432">
+      <c r="H432" s="24"/>
+    </row>
+    <row r="433">
+      <c r="H433" s="24"/>
+    </row>
+    <row r="434">
+      <c r="H434" s="24"/>
+    </row>
+    <row r="435">
+      <c r="H435" s="24"/>
+    </row>
+    <row r="436">
+      <c r="H436" s="24"/>
+    </row>
+    <row r="437">
+      <c r="H437" s="24"/>
+    </row>
+    <row r="438">
+      <c r="H438" s="24"/>
+    </row>
+    <row r="439">
+      <c r="H439" s="24"/>
+    </row>
+    <row r="440">
+      <c r="H440" s="24"/>
+    </row>
+    <row r="441">
+      <c r="H441" s="24"/>
+    </row>
+    <row r="442">
+      <c r="H442" s="24"/>
+    </row>
+    <row r="443">
+      <c r="H443" s="24"/>
+    </row>
+    <row r="444">
+      <c r="H444" s="24"/>
+    </row>
+    <row r="445">
+      <c r="H445" s="24"/>
+    </row>
+    <row r="446">
+      <c r="H446" s="24"/>
+    </row>
+    <row r="447">
+      <c r="H447" s="24"/>
+    </row>
+    <row r="448">
+      <c r="H448" s="24"/>
+    </row>
+    <row r="449">
+      <c r="H449" s="24"/>
+    </row>
+    <row r="450">
+      <c r="H450" s="24"/>
+    </row>
+    <row r="451">
+      <c r="H451" s="24"/>
+    </row>
+    <row r="452">
+      <c r="H452" s="24"/>
+    </row>
+    <row r="453">
+      <c r="H453" s="24"/>
+    </row>
+    <row r="454">
+      <c r="H454" s="24"/>
+    </row>
+    <row r="455">
+      <c r="H455" s="24"/>
+    </row>
+    <row r="456">
+      <c r="H456" s="24"/>
+    </row>
+    <row r="457">
+      <c r="H457" s="24"/>
+    </row>
+    <row r="458">
+      <c r="H458" s="24"/>
+    </row>
+    <row r="459">
+      <c r="H459" s="24"/>
+    </row>
+    <row r="460">
+      <c r="H460" s="24"/>
+    </row>
+    <row r="461">
+      <c r="H461" s="24"/>
+    </row>
+    <row r="462">
+      <c r="H462" s="24"/>
+    </row>
+    <row r="463">
+      <c r="H463" s="24"/>
+    </row>
+    <row r="464">
+      <c r="H464" s="24"/>
+    </row>
+    <row r="465">
+      <c r="H465" s="24"/>
+    </row>
+    <row r="466">
+      <c r="H466" s="24"/>
+    </row>
+    <row r="467">
+      <c r="H467" s="24"/>
+    </row>
+    <row r="468">
+      <c r="H468" s="24"/>
+    </row>
+    <row r="469">
+      <c r="H469" s="24"/>
+    </row>
+    <row r="470">
+      <c r="H470" s="24"/>
+    </row>
+    <row r="471">
+      <c r="H471" s="24"/>
+    </row>
+    <row r="472">
+      <c r="H472" s="24"/>
+    </row>
+    <row r="473">
+      <c r="H473" s="24"/>
+    </row>
+    <row r="474">
+      <c r="H474" s="24"/>
+    </row>
+    <row r="475">
+      <c r="H475" s="24"/>
+    </row>
+    <row r="476">
+      <c r="H476" s="24"/>
+    </row>
+    <row r="477">
+      <c r="H477" s="24"/>
+    </row>
+    <row r="478">
+      <c r="H478" s="24"/>
+    </row>
+    <row r="479">
+      <c r="H479" s="24"/>
+    </row>
+    <row r="480">
+      <c r="H480" s="24"/>
+    </row>
+    <row r="481">
+      <c r="H481" s="24"/>
+    </row>
+    <row r="482">
+      <c r="H482" s="24"/>
+    </row>
+    <row r="483">
+      <c r="H483" s="24"/>
+    </row>
+    <row r="484">
+      <c r="H484" s="24"/>
+    </row>
+    <row r="485">
+      <c r="H485" s="24"/>
+    </row>
+    <row r="486">
+      <c r="H486" s="24"/>
+    </row>
+    <row r="487">
+      <c r="H487" s="24"/>
+    </row>
+    <row r="488">
+      <c r="H488" s="24"/>
+    </row>
+    <row r="489">
+      <c r="H489" s="24"/>
+    </row>
+    <row r="490">
+      <c r="H490" s="24"/>
+    </row>
+    <row r="491">
+      <c r="H491" s="24"/>
+    </row>
+    <row r="492">
+      <c r="H492" s="24"/>
+    </row>
+    <row r="493">
+      <c r="H493" s="24"/>
+    </row>
+    <row r="494">
+      <c r="H494" s="24"/>
+    </row>
+    <row r="495">
+      <c r="H495" s="24"/>
+    </row>
+    <row r="496">
+      <c r="H496" s="24"/>
+    </row>
+    <row r="497">
+      <c r="H497" s="24"/>
+    </row>
+    <row r="498">
+      <c r="H498" s="24"/>
+    </row>
+    <row r="499">
+      <c r="H499" s="24"/>
+    </row>
+    <row r="500">
+      <c r="H500" s="24"/>
+    </row>
+    <row r="501">
+      <c r="H501" s="24"/>
+    </row>
+    <row r="502">
+      <c r="H502" s="24"/>
+    </row>
+    <row r="503">
+      <c r="H503" s="24"/>
+    </row>
+    <row r="504">
+      <c r="H504" s="24"/>
+    </row>
+    <row r="505">
+      <c r="H505" s="24"/>
+    </row>
+    <row r="506">
+      <c r="H506" s="24"/>
+    </row>
+    <row r="507">
+      <c r="H507" s="24"/>
+    </row>
+    <row r="508">
+      <c r="H508" s="24"/>
+    </row>
+    <row r="509">
+      <c r="H509" s="24"/>
+    </row>
+    <row r="510">
+      <c r="H510" s="24"/>
+    </row>
+    <row r="511">
+      <c r="H511" s="24"/>
+    </row>
+    <row r="512">
+      <c r="H512" s="24"/>
+    </row>
+    <row r="513">
+      <c r="H513" s="24"/>
+    </row>
+    <row r="514">
+      <c r="H514" s="24"/>
+    </row>
+    <row r="515">
+      <c r="H515" s="24"/>
+    </row>
+    <row r="516">
+      <c r="H516" s="24"/>
+    </row>
+    <row r="517">
+      <c r="H517" s="24"/>
+    </row>
+    <row r="518">
+      <c r="H518" s="24"/>
+    </row>
+    <row r="519">
+      <c r="H519" s="24"/>
+    </row>
+    <row r="520">
+      <c r="H520" s="24"/>
+    </row>
+    <row r="521">
+      <c r="H521" s="24"/>
+    </row>
+    <row r="522">
+      <c r="H522" s="24"/>
+    </row>
+    <row r="523">
+      <c r="H523" s="24"/>
+    </row>
+    <row r="524">
+      <c r="H524" s="24"/>
+    </row>
+    <row r="525">
+      <c r="H525" s="24"/>
+    </row>
+    <row r="526">
+      <c r="H526" s="24"/>
+    </row>
+    <row r="527">
+      <c r="H527" s="24"/>
+    </row>
+    <row r="528">
+      <c r="H528" s="24"/>
+    </row>
+    <row r="529">
+      <c r="H529" s="24"/>
+    </row>
+    <row r="530">
+      <c r="H530" s="24"/>
+    </row>
+    <row r="531">
+      <c r="H531" s="24"/>
+    </row>
+    <row r="532">
+      <c r="H532" s="24"/>
+    </row>
+    <row r="533">
+      <c r="H533" s="24"/>
+    </row>
+    <row r="534">
+      <c r="H534" s="24"/>
+    </row>
+    <row r="535">
+      <c r="H535" s="24"/>
+    </row>
+    <row r="536">
+      <c r="H536" s="24"/>
+    </row>
+    <row r="537">
+      <c r="H537" s="24"/>
+    </row>
+    <row r="538">
+      <c r="H538" s="24"/>
+    </row>
+    <row r="539">
+      <c r="H539" s="24"/>
+    </row>
+    <row r="540">
+      <c r="H540" s="24"/>
+    </row>
+    <row r="541">
+      <c r="H541" s="24"/>
+    </row>
+    <row r="542">
+      <c r="H542" s="24"/>
+    </row>
+    <row r="543">
+      <c r="H543" s="24"/>
+    </row>
+    <row r="544">
+      <c r="H544" s="24"/>
+    </row>
+    <row r="545">
+      <c r="H545" s="24"/>
+    </row>
+    <row r="546">
+      <c r="H546" s="24"/>
+    </row>
+    <row r="547">
+      <c r="H547" s="24"/>
+    </row>
+    <row r="548">
+      <c r="H548" s="24"/>
+    </row>
+    <row r="549">
+      <c r="H549" s="24"/>
+    </row>
+    <row r="550">
+      <c r="H550" s="24"/>
+    </row>
+    <row r="551">
+      <c r="H551" s="24"/>
+    </row>
+    <row r="552">
+      <c r="H552" s="24"/>
+    </row>
+    <row r="553">
+      <c r="H553" s="24"/>
+    </row>
+    <row r="554">
+      <c r="H554" s="24"/>
+    </row>
+    <row r="555">
+      <c r="H555" s="24"/>
+    </row>
+    <row r="556">
+      <c r="H556" s="24"/>
+    </row>
+    <row r="557">
+      <c r="H557" s="24"/>
+    </row>
+    <row r="558">
+      <c r="H558" s="24"/>
+    </row>
+    <row r="559">
+      <c r="H559" s="24"/>
+    </row>
+    <row r="560">
+      <c r="H560" s="24"/>
+    </row>
+    <row r="561">
+      <c r="H561" s="24"/>
+    </row>
+    <row r="562">
+      <c r="H562" s="24"/>
+    </row>
+    <row r="563">
+      <c r="H563" s="24"/>
+    </row>
+    <row r="564">
+      <c r="H564" s="24"/>
+    </row>
+    <row r="565">
+      <c r="H565" s="24"/>
+    </row>
+    <row r="566">
+      <c r="H566" s="24"/>
+    </row>
+    <row r="567">
+      <c r="H567" s="24"/>
+    </row>
+    <row r="568">
+      <c r="H568" s="24"/>
+    </row>
+    <row r="569">
+      <c r="H569" s="24"/>
+    </row>
+    <row r="570">
+      <c r="H570" s="24"/>
+    </row>
+    <row r="571">
+      <c r="H571" s="24"/>
+    </row>
+    <row r="572">
+      <c r="H572" s="24"/>
+    </row>
+    <row r="573">
+      <c r="H573" s="24"/>
+    </row>
+    <row r="574">
+      <c r="H574" s="24"/>
+    </row>
+    <row r="575">
+      <c r="H575" s="24"/>
+    </row>
+    <row r="576">
+      <c r="H576" s="24"/>
+    </row>
+    <row r="577">
+      <c r="H577" s="24"/>
+    </row>
+    <row r="578">
+      <c r="H578" s="24"/>
+    </row>
+    <row r="579">
+      <c r="H579" s="24"/>
+    </row>
+    <row r="580">
+      <c r="H580" s="24"/>
+    </row>
+    <row r="581">
+      <c r="H581" s="24"/>
+    </row>
+    <row r="582">
+      <c r="H582" s="24"/>
+    </row>
+    <row r="583">
+      <c r="H583" s="24"/>
+    </row>
+    <row r="584">
+      <c r="H584" s="24"/>
+    </row>
+    <row r="585">
+      <c r="H585" s="24"/>
+    </row>
+    <row r="586">
+      <c r="H586" s="24"/>
+    </row>
+    <row r="587">
+      <c r="H587" s="24"/>
+    </row>
+    <row r="588">
+      <c r="H588" s="24"/>
+    </row>
+    <row r="589">
+      <c r="H589" s="24"/>
+    </row>
+    <row r="590">
+      <c r="H590" s="24"/>
+    </row>
+    <row r="591">
+      <c r="H591" s="24"/>
+    </row>
+    <row r="592">
+      <c r="H592" s="24"/>
+    </row>
+    <row r="593">
+      <c r="H593" s="24"/>
+    </row>
+    <row r="594">
+      <c r="H594" s="24"/>
+    </row>
+    <row r="595">
+      <c r="H595" s="24"/>
+    </row>
+    <row r="596">
+      <c r="H596" s="24"/>
+    </row>
+    <row r="597">
+      <c r="H597" s="24"/>
+    </row>
+    <row r="598">
+      <c r="H598" s="24"/>
+    </row>
+    <row r="599">
+      <c r="H599" s="24"/>
+    </row>
+    <row r="600">
+      <c r="H600" s="24"/>
+    </row>
+    <row r="601">
+      <c r="H601" s="24"/>
+    </row>
+    <row r="602">
+      <c r="H602" s="24"/>
+    </row>
+    <row r="603">
+      <c r="H603" s="24"/>
+    </row>
+    <row r="604">
+      <c r="H604" s="24"/>
+    </row>
+    <row r="605">
+      <c r="H605" s="24"/>
+    </row>
+    <row r="606">
+      <c r="H606" s="24"/>
+    </row>
+    <row r="607">
+      <c r="H607" s="24"/>
+    </row>
+    <row r="608">
+      <c r="H608" s="24"/>
+    </row>
+    <row r="609">
+      <c r="H609" s="24"/>
+    </row>
+    <row r="610">
+      <c r="H610" s="24"/>
+    </row>
+    <row r="611">
+      <c r="H611" s="24"/>
+    </row>
+    <row r="612">
+      <c r="H612" s="24"/>
+    </row>
+    <row r="613">
+      <c r="H613" s="24"/>
+    </row>
+    <row r="614">
+      <c r="H614" s="24"/>
+    </row>
+    <row r="615">
+      <c r="H615" s="24"/>
+    </row>
+    <row r="616">
+      <c r="H616" s="24"/>
+    </row>
+    <row r="617">
+      <c r="H617" s="24"/>
+    </row>
+    <row r="618">
+      <c r="H618" s="24"/>
+    </row>
+    <row r="619">
+      <c r="H619" s="24"/>
+    </row>
+    <row r="620">
+      <c r="H620" s="24"/>
+    </row>
+    <row r="621">
+      <c r="H621" s="24"/>
+    </row>
+    <row r="622">
+      <c r="H622" s="24"/>
+    </row>
+    <row r="623">
+      <c r="H623" s="24"/>
+    </row>
+    <row r="624">
+      <c r="H624" s="24"/>
+    </row>
+    <row r="625">
+      <c r="H625" s="24"/>
+    </row>
+    <row r="626">
+      <c r="H626" s="24"/>
+    </row>
+    <row r="627">
+      <c r="H627" s="24"/>
+    </row>
+    <row r="628">
+      <c r="H628" s="24"/>
+    </row>
+    <row r="629">
+      <c r="H629" s="24"/>
+    </row>
+    <row r="630">
+      <c r="H630" s="24"/>
+    </row>
+    <row r="631">
+      <c r="H631" s="24"/>
+    </row>
+    <row r="632">
+      <c r="H632" s="24"/>
+    </row>
+    <row r="633">
+      <c r="H633" s="24"/>
+    </row>
+    <row r="634">
+      <c r="H634" s="24"/>
+    </row>
+    <row r="635">
+      <c r="H635" s="24"/>
+    </row>
+    <row r="636">
+      <c r="H636" s="24"/>
+    </row>
+    <row r="637">
+      <c r="H637" s="24"/>
+    </row>
+    <row r="638">
+      <c r="H638" s="24"/>
+    </row>
+    <row r="639">
+      <c r="H639" s="24"/>
+    </row>
+    <row r="640">
+      <c r="H640" s="24"/>
+    </row>
+    <row r="641">
+      <c r="H641" s="24"/>
+    </row>
+    <row r="642">
+      <c r="H642" s="24"/>
+    </row>
+    <row r="643">
+      <c r="H643" s="24"/>
+    </row>
+    <row r="644">
+      <c r="H644" s="24"/>
+    </row>
+    <row r="645">
+      <c r="H645" s="24"/>
+    </row>
+    <row r="646">
+      <c r="H646" s="24"/>
+    </row>
+    <row r="647">
+      <c r="H647" s="24"/>
+    </row>
+    <row r="648">
+      <c r="H648" s="24"/>
+    </row>
+    <row r="649">
+      <c r="H649" s="24"/>
+    </row>
+    <row r="650">
+      <c r="H650" s="24"/>
+    </row>
+    <row r="651">
+      <c r="H651" s="24"/>
+    </row>
+    <row r="652">
+      <c r="H652" s="24"/>
+    </row>
+    <row r="653">
+      <c r="H653" s="24"/>
+    </row>
+    <row r="654">
+      <c r="H654" s="24"/>
+    </row>
+    <row r="655">
+      <c r="H655" s="24"/>
+    </row>
+    <row r="656">
+      <c r="H656" s="24"/>
+    </row>
+    <row r="657">
+      <c r="H657" s="24"/>
+    </row>
+    <row r="658">
+      <c r="H658" s="24"/>
+    </row>
+    <row r="659">
+      <c r="H659" s="24"/>
+    </row>
+    <row r="660">
+      <c r="H660" s="24"/>
+    </row>
+    <row r="661">
+      <c r="H661" s="24"/>
+    </row>
+    <row r="662">
+      <c r="H662" s="24"/>
+    </row>
+    <row r="663">
+      <c r="H663" s="24"/>
+    </row>
+    <row r="664">
+      <c r="H664" s="24"/>
+    </row>
+    <row r="665">
+      <c r="H665" s="24"/>
+    </row>
+    <row r="666">
+      <c r="H666" s="24"/>
+    </row>
+    <row r="667">
+      <c r="H667" s="24"/>
+    </row>
+    <row r="668">
+      <c r="H668" s="24"/>
+    </row>
+    <row r="669">
+      <c r="H669" s="24"/>
+    </row>
+    <row r="670">
+      <c r="H670" s="24"/>
+    </row>
+    <row r="671">
+      <c r="H671" s="24"/>
+    </row>
+    <row r="672">
+      <c r="H672" s="24"/>
+    </row>
+    <row r="673">
+      <c r="H673" s="24"/>
+    </row>
+    <row r="674">
+      <c r="H674" s="24"/>
+    </row>
+    <row r="675">
+      <c r="H675" s="24"/>
+    </row>
+    <row r="676">
+      <c r="H676" s="24"/>
+    </row>
+    <row r="677">
+      <c r="H677" s="24"/>
+    </row>
+    <row r="678">
+      <c r="H678" s="24"/>
+    </row>
+    <row r="679">
+      <c r="H679" s="24"/>
+    </row>
+    <row r="680">
+      <c r="H680" s="24"/>
+    </row>
+    <row r="681">
+      <c r="H681" s="24"/>
+    </row>
+    <row r="682">
+      <c r="H682" s="24"/>
+    </row>
+    <row r="683">
+      <c r="H683" s="24"/>
+    </row>
+    <row r="684">
+      <c r="H684" s="24"/>
+    </row>
+    <row r="685">
+      <c r="H685" s="24"/>
+    </row>
+    <row r="686">
+      <c r="H686" s="24"/>
+    </row>
+    <row r="687">
+      <c r="H687" s="24"/>
+    </row>
+    <row r="688">
+      <c r="H688" s="24"/>
+    </row>
+    <row r="689">
+      <c r="H689" s="24"/>
+    </row>
+    <row r="690">
+      <c r="H690" s="24"/>
+    </row>
+    <row r="691">
+      <c r="H691" s="24"/>
+    </row>
+    <row r="692">
+      <c r="H692" s="24"/>
+    </row>
+    <row r="693">
+      <c r="H693" s="24"/>
+    </row>
+    <row r="694">
+      <c r="H694" s="24"/>
+    </row>
+    <row r="695">
+      <c r="H695" s="24"/>
+    </row>
+    <row r="696">
+      <c r="H696" s="24"/>
+    </row>
+    <row r="697">
+      <c r="H697" s="24"/>
+    </row>
+    <row r="698">
+      <c r="H698" s="24"/>
+    </row>
+    <row r="699">
+      <c r="H699" s="24"/>
+    </row>
+    <row r="700">
+      <c r="H700" s="24"/>
+    </row>
+    <row r="701">
+      <c r="H701" s="24"/>
+    </row>
+    <row r="702">
+      <c r="H702" s="24"/>
+    </row>
+    <row r="703">
+      <c r="H703" s="24"/>
+    </row>
+    <row r="704">
+      <c r="H704" s="24"/>
+    </row>
+    <row r="705">
+      <c r="H705" s="24"/>
+    </row>
+    <row r="706">
+      <c r="H706" s="24"/>
+    </row>
+    <row r="707">
+      <c r="H707" s="24"/>
+    </row>
+    <row r="708">
+      <c r="H708" s="24"/>
+    </row>
+    <row r="709">
+      <c r="H709" s="24"/>
+    </row>
+    <row r="710">
+      <c r="H710" s="24"/>
+    </row>
+    <row r="711">
+      <c r="H711" s="24"/>
+    </row>
+    <row r="712">
+      <c r="H712" s="24"/>
+    </row>
+    <row r="713">
+      <c r="H713" s="24"/>
+    </row>
+    <row r="714">
+      <c r="H714" s="24"/>
+    </row>
+    <row r="715">
+      <c r="H715" s="24"/>
+    </row>
+    <row r="716">
+      <c r="H716" s="24"/>
+    </row>
+    <row r="717">
+      <c r="H717" s="24"/>
+    </row>
+    <row r="718">
+      <c r="H718" s="24"/>
+    </row>
+    <row r="719">
+      <c r="H719" s="24"/>
+    </row>
+    <row r="720">
+      <c r="H720" s="24"/>
+    </row>
+    <row r="721">
+      <c r="H721" s="24"/>
+    </row>
+    <row r="722">
+      <c r="H722" s="24"/>
+    </row>
+    <row r="723">
+      <c r="H723" s="24"/>
+    </row>
+    <row r="724">
+      <c r="H724" s="24"/>
+    </row>
+    <row r="725">
+      <c r="H725" s="24"/>
+    </row>
+    <row r="726">
+      <c r="H726" s="24"/>
+    </row>
+    <row r="727">
+      <c r="H727" s="24"/>
+    </row>
+    <row r="728">
+      <c r="H728" s="24"/>
+    </row>
+    <row r="729">
+      <c r="H729" s="24"/>
+    </row>
+    <row r="730">
+      <c r="H730" s="24"/>
+    </row>
+    <row r="731">
+      <c r="H731" s="24"/>
+    </row>
+    <row r="732">
+      <c r="H732" s="24"/>
+    </row>
+    <row r="733">
+      <c r="H733" s="24"/>
+    </row>
+    <row r="734">
+      <c r="H734" s="24"/>
+    </row>
+    <row r="735">
+      <c r="H735" s="24"/>
+    </row>
+    <row r="736">
+      <c r="H736" s="24"/>
+    </row>
+    <row r="737">
+      <c r="H737" s="24"/>
+    </row>
+    <row r="738">
+      <c r="H738" s="24"/>
+    </row>
+    <row r="739">
+      <c r="H739" s="24"/>
+    </row>
+    <row r="740">
+      <c r="H740" s="24"/>
+    </row>
+    <row r="741">
+      <c r="H741" s="24"/>
+    </row>
+    <row r="742">
+      <c r="H742" s="24"/>
+    </row>
+    <row r="743">
+      <c r="H743" s="24"/>
+    </row>
+    <row r="744">
+      <c r="H744" s="24"/>
+    </row>
+    <row r="745">
+      <c r="H745" s="24"/>
+    </row>
+    <row r="746">
+      <c r="H746" s="24"/>
+    </row>
+    <row r="747">
+      <c r="H747" s="24"/>
+    </row>
+    <row r="748">
+      <c r="H748" s="24"/>
+    </row>
+    <row r="749">
+      <c r="H749" s="24"/>
+    </row>
+    <row r="750">
+      <c r="H750" s="24"/>
+    </row>
+    <row r="751">
+      <c r="H751" s="24"/>
+    </row>
+    <row r="752">
+      <c r="H752" s="24"/>
+    </row>
+    <row r="753">
+      <c r="H753" s="24"/>
+    </row>
+    <row r="754">
+      <c r="H754" s="24"/>
+    </row>
+    <row r="755">
+      <c r="H755" s="24"/>
+    </row>
+    <row r="756">
+      <c r="H756" s="24"/>
+    </row>
+    <row r="757">
+      <c r="H757" s="24"/>
+    </row>
+    <row r="758">
+      <c r="H758" s="24"/>
+    </row>
+    <row r="759">
+      <c r="H759" s="24"/>
+    </row>
+    <row r="760">
+      <c r="H760" s="24"/>
+    </row>
+    <row r="761">
+      <c r="H761" s="24"/>
+    </row>
+    <row r="762">
+      <c r="H762" s="24"/>
+    </row>
+    <row r="763">
+      <c r="H763" s="24"/>
+    </row>
+    <row r="764">
+      <c r="H764" s="24"/>
+    </row>
+    <row r="765">
+      <c r="H765" s="24"/>
+    </row>
+    <row r="766">
+      <c r="H766" s="24"/>
+    </row>
+    <row r="767">
+      <c r="H767" s="24"/>
+    </row>
+    <row r="768">
+      <c r="H768" s="24"/>
+    </row>
+    <row r="769">
+      <c r="H769" s="24"/>
+    </row>
+    <row r="770">
+      <c r="H770" s="24"/>
+    </row>
+    <row r="771">
+      <c r="H771" s="24"/>
+    </row>
+    <row r="772">
+      <c r="H772" s="24"/>
+    </row>
+    <row r="773">
+      <c r="H773" s="24"/>
+    </row>
+    <row r="774">
+      <c r="H774" s="24"/>
+    </row>
+    <row r="775">
+      <c r="H775" s="24"/>
+    </row>
+    <row r="776">
+      <c r="H776" s="24"/>
+    </row>
+    <row r="777">
+      <c r="H777" s="24"/>
+    </row>
+    <row r="778">
+      <c r="H778" s="24"/>
+    </row>
+    <row r="779">
+      <c r="H779" s="24"/>
+    </row>
+    <row r="780">
+      <c r="H780" s="24"/>
+    </row>
+    <row r="781">
+      <c r="H781" s="24"/>
+    </row>
+    <row r="782">
+      <c r="H782" s="24"/>
+    </row>
+    <row r="783">
+      <c r="H783" s="24"/>
+    </row>
+    <row r="784">
+      <c r="H784" s="24"/>
+    </row>
+    <row r="785">
+      <c r="H785" s="24"/>
+    </row>
+    <row r="786">
+      <c r="H786" s="24"/>
+    </row>
+    <row r="787">
+      <c r="H787" s="24"/>
+    </row>
+    <row r="788">
+      <c r="H788" s="24"/>
+    </row>
+    <row r="789">
+      <c r="H789" s="24"/>
+    </row>
+    <row r="790">
+      <c r="H790" s="24"/>
+    </row>
+    <row r="791">
+      <c r="H791" s="24"/>
+    </row>
+    <row r="792">
+      <c r="H792" s="24"/>
+    </row>
+    <row r="793">
+      <c r="H793" s="24"/>
+    </row>
+    <row r="794">
+      <c r="H794" s="24"/>
+    </row>
+    <row r="795">
+      <c r="H795" s="24"/>
+    </row>
+    <row r="796">
+      <c r="H796" s="24"/>
+    </row>
+    <row r="797">
+      <c r="H797" s="24"/>
+    </row>
+    <row r="798">
+      <c r="H798" s="24"/>
+    </row>
+    <row r="799">
+      <c r="H799" s="24"/>
+    </row>
+    <row r="800">
+      <c r="H800" s="24"/>
+    </row>
+    <row r="801">
+      <c r="H801" s="24"/>
+    </row>
+    <row r="802">
+      <c r="H802" s="24"/>
+    </row>
+    <row r="803">
+      <c r="H803" s="24"/>
+    </row>
+    <row r="804">
+      <c r="H804" s="24"/>
+    </row>
+    <row r="805">
+      <c r="H805" s="24"/>
+    </row>
+    <row r="806">
+      <c r="H806" s="24"/>
+    </row>
+    <row r="807">
+      <c r="H807" s="24"/>
+    </row>
+    <row r="808">
+      <c r="H808" s="24"/>
+    </row>
+    <row r="809">
+      <c r="H809" s="24"/>
+    </row>
+    <row r="810">
+      <c r="H810" s="24"/>
+    </row>
+    <row r="811">
+      <c r="H811" s="24"/>
+    </row>
+    <row r="812">
+      <c r="H812" s="24"/>
+    </row>
+    <row r="813">
+      <c r="H813" s="24"/>
+    </row>
+    <row r="814">
+      <c r="H814" s="24"/>
+    </row>
+    <row r="815">
+      <c r="H815" s="24"/>
+    </row>
+    <row r="816">
+      <c r="H816" s="24"/>
+    </row>
+    <row r="817">
+      <c r="H817" s="24"/>
+    </row>
+    <row r="818">
+      <c r="H818" s="24"/>
+    </row>
+    <row r="819">
+      <c r="H819" s="24"/>
+    </row>
+    <row r="820">
+      <c r="H820" s="24"/>
+    </row>
+    <row r="821">
+      <c r="H821" s="24"/>
+    </row>
+    <row r="822">
+      <c r="H822" s="24"/>
+    </row>
+    <row r="823">
+      <c r="H823" s="24"/>
+    </row>
+    <row r="824">
+      <c r="H824" s="24"/>
+    </row>
+    <row r="825">
+      <c r="H825" s="24"/>
+    </row>
+    <row r="826">
+      <c r="H826" s="24"/>
+    </row>
+    <row r="827">
+      <c r="H827" s="24"/>
+    </row>
+    <row r="828">
+      <c r="H828" s="24"/>
+    </row>
+    <row r="829">
+      <c r="H829" s="24"/>
+    </row>
+    <row r="830">
+      <c r="H830" s="24"/>
+    </row>
+    <row r="831">
+      <c r="H831" s="24"/>
+    </row>
+    <row r="832">
+      <c r="H832" s="24"/>
+    </row>
+    <row r="833">
+      <c r="H833" s="24"/>
+    </row>
+    <row r="834">
+      <c r="H834" s="24"/>
+    </row>
+    <row r="835">
+      <c r="H835" s="24"/>
+    </row>
+    <row r="836">
+      <c r="H836" s="24"/>
+    </row>
+    <row r="837">
+      <c r="H837" s="24"/>
+    </row>
+    <row r="838">
+      <c r="H838" s="24"/>
+    </row>
+    <row r="839">
+      <c r="H839" s="24"/>
+    </row>
+    <row r="840">
+      <c r="H840" s="24"/>
+    </row>
+    <row r="841">
+      <c r="H841" s="24"/>
+    </row>
+    <row r="842">
+      <c r="H842" s="24"/>
+    </row>
+    <row r="843">
+      <c r="H843" s="24"/>
+    </row>
+    <row r="844">
+      <c r="H844" s="24"/>
+    </row>
+    <row r="845">
+      <c r="H845" s="24"/>
+    </row>
+    <row r="846">
+      <c r="H846" s="24"/>
+    </row>
+    <row r="847">
+      <c r="H847" s="24"/>
+    </row>
+    <row r="848">
+      <c r="H848" s="24"/>
+    </row>
+    <row r="849">
+      <c r="H849" s="24"/>
+    </row>
+    <row r="850">
+      <c r="H850" s="24"/>
+    </row>
+    <row r="851">
+      <c r="H851" s="24"/>
+    </row>
+    <row r="852">
+      <c r="H852" s="24"/>
+    </row>
+    <row r="853">
+      <c r="H853" s="24"/>
+    </row>
+    <row r="854">
+      <c r="H854" s="24"/>
+    </row>
+    <row r="855">
+      <c r="H855" s="24"/>
+    </row>
+    <row r="856">
+      <c r="H856" s="24"/>
+    </row>
+    <row r="857">
+      <c r="H857" s="24"/>
+    </row>
+    <row r="858">
+      <c r="H858" s="24"/>
+    </row>
+    <row r="859">
+      <c r="H859" s="24"/>
+    </row>
+    <row r="860">
+      <c r="H860" s="24"/>
+    </row>
+    <row r="861">
+      <c r="H861" s="24"/>
+    </row>
+    <row r="862">
+      <c r="H862" s="24"/>
+    </row>
+    <row r="863">
+      <c r="H863" s="24"/>
+    </row>
+    <row r="864">
+      <c r="H864" s="24"/>
+    </row>
+    <row r="865">
+      <c r="H865" s="24"/>
+    </row>
+    <row r="866">
+      <c r="H866" s="24"/>
+    </row>
+    <row r="867">
+      <c r="H867" s="24"/>
+    </row>
+    <row r="868">
+      <c r="H868" s="24"/>
+    </row>
+    <row r="869">
+      <c r="H869" s="24"/>
+    </row>
+    <row r="870">
+      <c r="H870" s="24"/>
+    </row>
+    <row r="871">
+      <c r="H871" s="24"/>
+    </row>
+    <row r="872">
+      <c r="H872" s="24"/>
+    </row>
+    <row r="873">
+      <c r="H873" s="24"/>
+    </row>
+    <row r="874">
+      <c r="H874" s="24"/>
+    </row>
+    <row r="875">
+      <c r="H875" s="24"/>
+    </row>
+    <row r="876">
+      <c r="H876" s="24"/>
+    </row>
+    <row r="877">
+      <c r="H877" s="24"/>
+    </row>
+    <row r="878">
+      <c r="H878" s="24"/>
+    </row>
+    <row r="879">
+      <c r="H879" s="24"/>
+    </row>
+    <row r="880">
+      <c r="H880" s="24"/>
+    </row>
+    <row r="881">
+      <c r="H881" s="24"/>
+    </row>
+    <row r="882">
+      <c r="H882" s="24"/>
+    </row>
+    <row r="883">
+      <c r="H883" s="24"/>
+    </row>
+    <row r="884">
+      <c r="H884" s="24"/>
+    </row>
+    <row r="885">
+      <c r="H885" s="24"/>
+    </row>
+    <row r="886">
+      <c r="H886" s="24"/>
+    </row>
+    <row r="887">
+      <c r="H887" s="24"/>
+    </row>
+    <row r="888">
+      <c r="H888" s="24"/>
+    </row>
+    <row r="889">
+      <c r="H889" s="24"/>
+    </row>
+    <row r="890">
+      <c r="H890" s="24"/>
+    </row>
+    <row r="891">
+      <c r="H891" s="24"/>
+    </row>
+    <row r="892">
+      <c r="H892" s="24"/>
+    </row>
+    <row r="893">
+      <c r="H893" s="24"/>
+    </row>
+    <row r="894">
+      <c r="H894" s="24"/>
+    </row>
+    <row r="895">
+      <c r="H895" s="24"/>
+    </row>
+    <row r="896">
+      <c r="H896" s="24"/>
+    </row>
+    <row r="897">
+      <c r="H897" s="24"/>
+    </row>
+    <row r="898">
+      <c r="H898" s="24"/>
+    </row>
+    <row r="899">
+      <c r="H899" s="24"/>
+    </row>
+    <row r="900">
+      <c r="H900" s="24"/>
+    </row>
+    <row r="901">
+      <c r="H901" s="24"/>
+    </row>
+    <row r="902">
+      <c r="H902" s="24"/>
+    </row>
+    <row r="903">
+      <c r="H903" s="24"/>
+    </row>
+    <row r="904">
+      <c r="H904" s="24"/>
+    </row>
+    <row r="905">
+      <c r="H905" s="24"/>
+    </row>
+    <row r="906">
+      <c r="H906" s="24"/>
+    </row>
+    <row r="907">
+      <c r="H907" s="24"/>
+    </row>
+    <row r="908">
+      <c r="H908" s="24"/>
+    </row>
+    <row r="909">
+      <c r="H909" s="24"/>
+    </row>
+    <row r="910">
+      <c r="H910" s="24"/>
+    </row>
+    <row r="911">
+      <c r="H911" s="24"/>
+    </row>
+    <row r="912">
+      <c r="H912" s="24"/>
+    </row>
+    <row r="913">
+      <c r="H913" s="24"/>
+    </row>
+    <row r="914">
+      <c r="H914" s="24"/>
+    </row>
+    <row r="915">
+      <c r="H915" s="24"/>
+    </row>
+    <row r="916">
+      <c r="H916" s="24"/>
+    </row>
+    <row r="917">
+      <c r="H917" s="24"/>
+    </row>
+    <row r="918">
+      <c r="H918" s="24"/>
+    </row>
+    <row r="919">
+      <c r="H919" s="24"/>
+    </row>
+    <row r="920">
+      <c r="H920" s="24"/>
+    </row>
+    <row r="921">
+      <c r="H921" s="24"/>
+    </row>
+    <row r="922">
+      <c r="H922" s="24"/>
+    </row>
+    <row r="923">
+      <c r="H923" s="24"/>
+    </row>
+    <row r="924">
+      <c r="H924" s="24"/>
+    </row>
+    <row r="925">
+      <c r="H925" s="24"/>
+    </row>
+    <row r="926">
+      <c r="H926" s="24"/>
+    </row>
+    <row r="927">
+      <c r="H927" s="24"/>
+    </row>
+    <row r="928">
+      <c r="H928" s="24"/>
+    </row>
+    <row r="929">
+      <c r="H929" s="24"/>
+    </row>
+    <row r="930">
+      <c r="H930" s="24"/>
+    </row>
+    <row r="931">
+      <c r="H931" s="24"/>
+    </row>
+    <row r="932">
+      <c r="H932" s="24"/>
+    </row>
+    <row r="933">
+      <c r="H933" s="24"/>
+    </row>
+    <row r="934">
+      <c r="H934" s="24"/>
+    </row>
+    <row r="935">
+      <c r="H935" s="24"/>
+    </row>
+    <row r="936">
+      <c r="H936" s="24"/>
+    </row>
+    <row r="937">
+      <c r="H937" s="24"/>
+    </row>
+    <row r="938">
+      <c r="H938" s="24"/>
+    </row>
+    <row r="939">
+      <c r="H939" s="24"/>
+    </row>
+    <row r="940">
+      <c r="H940" s="24"/>
+    </row>
+    <row r="941">
+      <c r="H941" s="24"/>
+    </row>
+    <row r="942">
+      <c r="H942" s="24"/>
+    </row>
+    <row r="943">
+      <c r="H943" s="24"/>
+    </row>
+    <row r="944">
+      <c r="H944" s="24"/>
+    </row>
+    <row r="945">
+      <c r="H945" s="24"/>
+    </row>
+    <row r="946">
+      <c r="H946" s="24"/>
+    </row>
+    <row r="947">
+      <c r="H947" s="24"/>
+    </row>
+    <row r="948">
+      <c r="H948" s="24"/>
+    </row>
+    <row r="949">
+      <c r="H949" s="24"/>
+    </row>
+    <row r="950">
+      <c r="H950" s="24"/>
+    </row>
+    <row r="951">
+      <c r="H951" s="24"/>
+    </row>
+    <row r="952">
+      <c r="H952" s="24"/>
+    </row>
+    <row r="953">
+      <c r="H953" s="24"/>
+    </row>
+    <row r="954">
+      <c r="H954" s="24"/>
+    </row>
+    <row r="955">
+      <c r="H955" s="24"/>
+    </row>
+    <row r="956">
+      <c r="H956" s="24"/>
+    </row>
+    <row r="957">
+      <c r="H957" s="24"/>
+    </row>
+    <row r="958">
+      <c r="H958" s="24"/>
+    </row>
+    <row r="959">
+      <c r="H959" s="24"/>
+    </row>
+    <row r="960">
+      <c r="H960" s="24"/>
+    </row>
+    <row r="961">
+      <c r="H961" s="24"/>
+    </row>
+    <row r="962">
+      <c r="H962" s="24"/>
+    </row>
+    <row r="963">
+      <c r="H963" s="24"/>
+    </row>
+    <row r="964">
+      <c r="H964" s="24"/>
+    </row>
+    <row r="965">
+      <c r="H965" s="24"/>
+    </row>
+    <row r="966">
+      <c r="H966" s="24"/>
+    </row>
+    <row r="967">
+      <c r="H967" s="24"/>
+    </row>
+    <row r="968">
+      <c r="H968" s="24"/>
+    </row>
+    <row r="969">
+      <c r="H969" s="24"/>
+    </row>
+    <row r="970">
+      <c r="H970" s="24"/>
+    </row>
+    <row r="971">
+      <c r="H971" s="24"/>
+    </row>
+    <row r="972">
+      <c r="H972" s="24"/>
+    </row>
+    <row r="973">
+      <c r="H973" s="24"/>
+    </row>
+    <row r="974">
+      <c r="H974" s="24"/>
+    </row>
+    <row r="975">
+      <c r="H975" s="24"/>
+    </row>
+    <row r="976">
+      <c r="H976" s="24"/>
+    </row>
+    <row r="977">
+      <c r="H977" s="24"/>
+    </row>
+    <row r="978">
+      <c r="H978" s="24"/>
+    </row>
+    <row r="979">
+      <c r="H979" s="24"/>
+    </row>
+    <row r="980">
+      <c r="H980" s="24"/>
+    </row>
+    <row r="981">
+      <c r="H981" s="24"/>
+    </row>
+    <row r="982">
+      <c r="H982" s="24"/>
+    </row>
+    <row r="983">
+      <c r="H983" s="24"/>
+    </row>
+    <row r="984">
+      <c r="H984" s="24"/>
+    </row>
+    <row r="985">
+      <c r="H985" s="24"/>
+    </row>
+    <row r="986">
+      <c r="H986" s="24"/>
+    </row>
+    <row r="987">
+      <c r="H987" s="24"/>
+    </row>
+    <row r="988">
+      <c r="H988" s="24"/>
+    </row>
+    <row r="989">
+      <c r="H989" s="24"/>
+    </row>
+    <row r="990">
+      <c r="H990" s="24"/>
+    </row>
+    <row r="991">
+      <c r="H991" s="24"/>
+    </row>
+    <row r="992">
+      <c r="H992" s="24"/>
+    </row>
+    <row r="993">
+      <c r="H993" s="24"/>
+    </row>
+    <row r="994">
+      <c r="H994" s="24"/>
+    </row>
+    <row r="995">
+      <c r="H995" s="24"/>
+    </row>
+    <row r="996">
+      <c r="H996" s="24"/>
+    </row>
+    <row r="997">
+      <c r="H997" s="24"/>
+    </row>
+    <row r="998">
+      <c r="H998" s="24"/>
+    </row>
+    <row r="999">
+      <c r="H999" s="24"/>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/PythonPlayground/PreliminaryExperimentResults.xlsx
+++ b/PythonPlayground/PreliminaryExperimentResults.xlsx
@@ -5,9 +5,8 @@
   <sheets>
     <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
     <sheet state="visible" name="Sheet2" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="Sheet3" sheetId="3" r:id="rId6"/>
-    <sheet state="visible" name="Sheet4" sheetId="4" r:id="rId7"/>
-    <sheet state="visible" name="DSIFT" sheetId="5" r:id="rId8"/>
+    <sheet state="visible" name="Exp3" sheetId="3" r:id="rId6"/>
+    <sheet state="visible" name="Exp3_Flattened" sheetId="4" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -15,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="46">
   <si>
     <t>Experiment1</t>
   </si>
@@ -116,12 +115,6 @@
     <t>NearBias</t>
   </si>
   <si>
-    <t>WD</t>
-  </si>
-  <si>
-    <t>Photos</t>
-  </si>
-  <si>
     <t>SIFT</t>
   </si>
   <si>
@@ -131,31 +124,34 @@
     <t>SIFT+DSIFT</t>
   </si>
   <si>
-    <t>Comments</t>
+    <t>WD</t>
+  </si>
+  <si>
+    <t>Photos</t>
+  </si>
+  <si>
+    <t>Tilt</t>
   </si>
   <si>
     <t>OffViews</t>
   </si>
   <si>
-    <t>Radius of SfM showed a large radius</t>
+    <t>Comments</t>
   </si>
   <si>
-    <t>SpiralFocus</t>
+    <t>Radius of SfM showed a large radius</t>
   </si>
   <si>
     <t>Very litle of the surrounding scene was captured</t>
   </si>
   <si>
-    <t>CircularFocus</t>
-  </si>
-  <si>
-    <t>Tilt</t>
-  </si>
-  <si>
     <t>SIFT had a pretty large Std. Dev</t>
   </si>
   <si>
-    <t>Photos #</t>
+    <t>Extractor</t>
+  </si>
+  <si>
+    <t>SIFT_DSIFT</t>
   </si>
 </sst>
 </file>
@@ -211,8 +207,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB7B7B7"/>
-        <bgColor rgb="FFB7B7B7"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -222,25 +218,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="4">
     <border/>
     <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
-    </border>
-    <border>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
     </border>
     <border>
       <bottom style="medium">
@@ -251,15 +234,12 @@
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="19">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -292,11 +272,11 @@
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -304,29 +284,11 @@
     <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
     <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="0"/>
-    </xf>
+    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -516,11 +478,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="1791946864"/>
-        <c:axId val="2081689551"/>
+        <c:axId val="1212031083"/>
+        <c:axId val="535411316"/>
       </c:bar3DChart>
       <c:catAx>
-        <c:axId val="1791946864"/>
+        <c:axId val="1212031083"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -572,10 +534,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2081689551"/>
+        <c:crossAx val="535411316"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="2081689551"/>
+        <c:axId val="535411316"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -650,7 +612,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1791946864"/>
+        <c:crossAx val="1212031083"/>
         <c:crosses val="max"/>
       </c:valAx>
     </c:plotArea>
@@ -869,11 +831,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="1750696618"/>
-        <c:axId val="50005776"/>
+        <c:axId val="990851348"/>
+        <c:axId val="162536040"/>
       </c:bar3DChart>
       <c:catAx>
-        <c:axId val="1750696618"/>
+        <c:axId val="990851348"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -925,10 +887,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="50005776"/>
+        <c:crossAx val="162536040"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="50005776"/>
+        <c:axId val="162536040"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1005,7 +967,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1750696618"/>
+        <c:crossAx val="990851348"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -1237,11 +1199,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="1089295186"/>
-        <c:axId val="879454078"/>
+        <c:axId val="1922235277"/>
+        <c:axId val="653645541"/>
       </c:bar3DChart>
       <c:catAx>
-        <c:axId val="1089295186"/>
+        <c:axId val="1922235277"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1293,10 +1255,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="879454078"/>
+        <c:crossAx val="653645541"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="879454078"/>
+        <c:axId val="653645541"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1373,7 +1335,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1089295186"/>
+        <c:crossAx val="1922235277"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -1489,10 +1451,6 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -11678,724 +11636,785 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <cols>
-    <col customWidth="1" min="2" max="2" width="6.25"/>
-    <col customWidth="1" min="3" max="3" width="6.63"/>
-    <col customWidth="1" min="4" max="4" width="8.13"/>
-    <col customWidth="1" min="5" max="5" width="8.88"/>
-    <col customWidth="1" min="6" max="6" width="8.5"/>
-    <col customWidth="1" min="7" max="7" width="8.13"/>
-    <col customWidth="1" min="8" max="8" width="8.88"/>
-    <col customWidth="1" min="9" max="9" width="8.5"/>
-    <col customWidth="1" min="10" max="10" width="10.38"/>
-    <col customWidth="1" min="11" max="11" width="8.88"/>
-    <col customWidth="1" min="12" max="12" width="8.5"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="s">
+      <c r="E1" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="13" t="s">
+      <c r="B2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="C2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="M1" s="14" t="s">
+      <c r="D2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="6"/>
-      <c r="Z1" s="6"/>
-      <c r="AA1" s="6"/>
-      <c r="AB1" s="6"/>
-      <c r="AC1" s="6"/>
-      <c r="AD1" s="6"/>
-      <c r="AE1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="15"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16" t="s">
+      <c r="E2" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="F2" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="G2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="H2" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="I2" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="J2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="16" t="s">
+      <c r="K2" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="K2" s="16" t="s">
+      <c r="L2" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="16" t="s">
+      <c r="M2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="17"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
-      <c r="U2" s="6"/>
-      <c r="V2" s="6"/>
-      <c r="W2" s="6"/>
-      <c r="X2" s="6"/>
-      <c r="Y2" s="6"/>
-      <c r="Z2" s="6"/>
-      <c r="AA2" s="6"/>
-      <c r="AB2" s="6"/>
-      <c r="AC2" s="6"/>
-      <c r="AD2" s="6"/>
-      <c r="AE2" s="6"/>
+      <c r="N2" s="15" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="16">
         <v>1.5</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="16">
         <v>48.0</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="16">
         <v>0.0</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="F3" s="16">
         <v>0.0563419</v>
       </c>
-      <c r="F3" s="7">
+      <c r="G3" s="16">
         <v>-0.003753</v>
       </c>
-      <c r="G3" s="7">
+      <c r="H3" s="16">
         <v>1.0</v>
       </c>
-      <c r="H3" s="7">
+      <c r="I3" s="16">
         <v>0.122002</v>
       </c>
-      <c r="I3" s="7">
+      <c r="J3" s="16">
         <v>-0.045195</v>
       </c>
-      <c r="J3" s="7">
+      <c r="K3" s="16">
         <v>0.0</v>
       </c>
-      <c r="K3" s="7">
+      <c r="L3" s="16">
         <v>0.132857</v>
       </c>
-      <c r="L3" s="7">
+      <c r="M3" s="16">
         <v>-0.022211</v>
       </c>
-      <c r="M3" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="N3" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="O3" s="17"/>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="16">
         <v>1.5</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="16">
         <v>72.0</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="16">
         <v>0.0</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="F4" s="16">
         <v>0.09968</v>
       </c>
-      <c r="F4" s="7">
+      <c r="G4" s="16">
         <v>0.01147</v>
       </c>
-      <c r="G4" s="7">
+      <c r="H4" s="16">
         <v>0.0</v>
       </c>
-      <c r="H4" s="7">
+      <c r="I4" s="16">
         <v>0.3459</v>
       </c>
-      <c r="I4" s="7">
+      <c r="J4" s="16">
         <v>0.152536</v>
       </c>
-      <c r="J4" s="7">
+      <c r="K4" s="16">
         <v>0.0</v>
       </c>
-      <c r="K4" s="7">
+      <c r="L4" s="16">
         <v>0.140796</v>
       </c>
-      <c r="L4" s="7">
+      <c r="M4" s="16">
         <v>0.039724</v>
       </c>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="16">
         <v>2.0</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="16">
         <v>48.0</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="16">
         <v>0.0</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="F5" s="16">
         <v>0.299593</v>
       </c>
-      <c r="F5" s="7">
+      <c r="G5" s="16">
         <v>-0.094855</v>
       </c>
-      <c r="G5" s="7">
+      <c r="H5" s="16">
         <v>0.0</v>
       </c>
-      <c r="H5" s="7">
+      <c r="I5" s="16">
         <v>0.165687</v>
       </c>
-      <c r="I5" s="7">
+      <c r="J5" s="16">
         <v>0.039983</v>
       </c>
-      <c r="J5" s="7">
+      <c r="K5" s="16">
         <v>0.0</v>
       </c>
-      <c r="K5" s="7">
+      <c r="L5" s="16">
         <v>0.166992</v>
       </c>
-      <c r="L5" s="7">
+      <c r="M5" s="16">
         <v>0.040403</v>
       </c>
+      <c r="N5" s="17"/>
+      <c r="O5" s="17"/>
+      <c r="P5" s="18"/>
+      <c r="Q5" s="18"/>
+      <c r="R5" s="18"/>
+      <c r="S5" s="18"/>
+      <c r="T5" s="18"/>
+      <c r="U5" s="18"/>
+      <c r="V5" s="18"/>
+      <c r="W5" s="18"/>
+      <c r="X5" s="18"/>
+      <c r="Y5" s="18"/>
+      <c r="Z5" s="18"/>
+      <c r="AA5" s="18"/>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="16">
         <v>2.0</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="16">
         <v>72.0</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="16">
         <v>0.0</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="F6" s="16">
         <v>0.273452</v>
       </c>
-      <c r="F6" s="7">
+      <c r="G6" s="16">
         <v>0.095401</v>
       </c>
-      <c r="G6" s="7">
+      <c r="H6" s="16">
         <v>7.0</v>
       </c>
-      <c r="H6" s="7">
+      <c r="I6" s="16">
         <v>0.290725</v>
       </c>
-      <c r="I6" s="7">
+      <c r="J6" s="16">
         <v>-0.247398</v>
       </c>
-      <c r="J6" s="7">
+      <c r="K6" s="16">
         <v>1.0</v>
       </c>
-      <c r="K6" s="7">
+      <c r="L6" s="16">
         <v>0.293721</v>
       </c>
-      <c r="L6" s="7">
+      <c r="M6" s="16">
         <v>-0.259891</v>
       </c>
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="16">
         <v>1.5</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="16">
         <v>48.0</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="16">
         <v>0.0</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="F7" s="16">
         <v>0.302278</v>
       </c>
-      <c r="F7" s="7">
+      <c r="G7" s="16">
         <v>0.216884</v>
       </c>
-      <c r="G7" s="7">
+      <c r="H7" s="16">
         <v>0.0</v>
       </c>
-      <c r="H7" s="7">
+      <c r="I7" s="16">
         <v>0.57742</v>
       </c>
-      <c r="I7" s="7">
+      <c r="J7" s="16">
         <v>0.394852</v>
       </c>
-      <c r="J7" s="7">
+      <c r="K7" s="16">
         <v>0.0</v>
       </c>
-      <c r="K7" s="7">
+      <c r="L7" s="16">
         <v>0.581207</v>
       </c>
-      <c r="L7" s="7">
+      <c r="M7" s="16">
         <v>0.448983</v>
       </c>
+      <c r="N7" s="17"/>
+      <c r="O7" s="17"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="16">
         <v>1.5</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="16">
         <v>72.0</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="16">
         <v>0.0</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="F8" s="16">
         <v>0.648478</v>
       </c>
-      <c r="F8" s="7">
+      <c r="G8" s="16">
         <v>0.415064</v>
       </c>
-      <c r="G8" s="7">
+      <c r="H8" s="16">
         <v>0.0</v>
       </c>
-      <c r="H8" s="7">
+      <c r="I8" s="16">
         <v>0.768339</v>
       </c>
-      <c r="I8" s="7">
+      <c r="J8" s="16">
         <v>0.403431</v>
       </c>
-      <c r="J8" s="7">
+      <c r="K8" s="16">
         <v>0.0</v>
       </c>
-      <c r="K8" s="7">
+      <c r="L8" s="16">
         <v>0.720302</v>
       </c>
-      <c r="L8" s="7">
+      <c r="M8" s="16">
         <v>0.461317</v>
       </c>
+      <c r="N8" s="17"/>
+      <c r="O8" s="17"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="16">
         <v>2.0</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="16">
         <v>48.0</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="16">
         <v>0.0</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="F9" s="16">
         <v>0.439882</v>
       </c>
-      <c r="F9" s="7">
+      <c r="G9" s="16">
         <v>0.27209</v>
       </c>
-      <c r="G9" s="7">
+      <c r="H9" s="16">
         <v>0.0</v>
       </c>
-      <c r="H9" s="7">
+      <c r="I9" s="16">
         <v>0.0798324</v>
       </c>
-      <c r="I9" s="7">
+      <c r="J9" s="16">
         <v>5.31E-4</v>
       </c>
-      <c r="J9" s="7">
+      <c r="K9" s="16">
         <v>0.0</v>
       </c>
-      <c r="K9" s="7">
+      <c r="L9" s="16">
         <v>0.0996823</v>
       </c>
-      <c r="L9" s="7">
+      <c r="M9" s="16">
         <v>-0.017615</v>
       </c>
+      <c r="N9" s="17"/>
+      <c r="O9" s="17"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="16">
         <v>2.0</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="16">
         <v>72.0</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="16">
         <v>0.0</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="F10" s="16">
         <v>0.188511</v>
       </c>
-      <c r="F10" s="7">
+      <c r="G10" s="16">
         <v>0.091326</v>
       </c>
-      <c r="G10" s="7">
+      <c r="H10" s="16">
         <v>0.0</v>
       </c>
-      <c r="H10" s="7">
+      <c r="I10" s="16">
         <v>0.205691</v>
       </c>
-      <c r="I10" s="7">
+      <c r="J10" s="16">
         <v>0.106242</v>
       </c>
-      <c r="J10" s="7">
+      <c r="K10" s="16">
         <v>0.0</v>
       </c>
-      <c r="K10" s="7">
+      <c r="L10" s="16">
         <v>0.166254</v>
       </c>
-      <c r="L10" s="7">
+      <c r="M10" s="16">
         <v>0.151412</v>
       </c>
+      <c r="N10" s="17"/>
+      <c r="O10" s="17"/>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="B11" s="18">
+      <c r="A11" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="16">
         <v>1.5</v>
       </c>
-      <c r="C11" s="18">
+      <c r="C11" s="16">
         <v>48.0</v>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="16">
+        <v>1.0</v>
+      </c>
+      <c r="E11" s="16">
         <v>0.0</v>
       </c>
-      <c r="E11" s="18">
+      <c r="F11" s="16">
         <v>0.0782306</v>
       </c>
-      <c r="F11" s="18">
+      <c r="G11" s="16">
         <v>-0.021749</v>
       </c>
-      <c r="G11" s="18">
+      <c r="H11" s="16">
         <v>0.0</v>
       </c>
-      <c r="H11" s="18">
+      <c r="I11" s="16">
         <v>0.0829006</v>
       </c>
-      <c r="I11" s="18">
+      <c r="J11" s="16">
         <v>-0.026013</v>
       </c>
-      <c r="J11" s="18">
+      <c r="K11" s="16">
         <v>0.0</v>
       </c>
-      <c r="K11" s="18">
+      <c r="L11" s="16">
         <v>0.0471715</v>
       </c>
-      <c r="L11" s="18">
+      <c r="M11" s="16">
         <v>-0.006232</v>
       </c>
-      <c r="M11" s="18" t="s">
+      <c r="N11" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="N11" s="19"/>
-      <c r="O11" s="19"/>
-      <c r="P11" s="19"/>
-      <c r="Q11" s="19"/>
-      <c r="R11" s="19"/>
-      <c r="S11" s="19"/>
-      <c r="T11" s="19"/>
-      <c r="U11" s="19"/>
-      <c r="V11" s="19"/>
-      <c r="W11" s="19"/>
-      <c r="X11" s="19"/>
-      <c r="Y11" s="19"/>
-      <c r="Z11" s="19"/>
-      <c r="AA11" s="19"/>
-      <c r="AB11" s="19"/>
-      <c r="AC11" s="19"/>
-      <c r="AD11" s="19"/>
-      <c r="AE11" s="19"/>
+      <c r="O11" s="17"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="7">
+      <c r="A12" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="16">
         <v>1.5</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="16">
         <v>72.0</v>
       </c>
-      <c r="G12" s="7">
+      <c r="D12" s="16">
+        <v>1.0</v>
+      </c>
+      <c r="E12" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="F12" s="16">
+        <v>0.0454423</v>
+      </c>
+      <c r="G12" s="16">
+        <v>-0.00203</v>
+      </c>
+      <c r="H12" s="16">
         <v>9.0</v>
       </c>
-      <c r="H12" s="7">
+      <c r="I12" s="16">
         <v>0.0990531</v>
       </c>
-      <c r="I12" s="7">
+      <c r="J12" s="16">
         <v>0.019526</v>
       </c>
+      <c r="K12" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="L12" s="16">
+        <v>0.0933383</v>
+      </c>
+      <c r="M12" s="16">
+        <v>-0.003156</v>
+      </c>
+      <c r="N12" s="17"/>
+      <c r="O12" s="17"/>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13" s="18">
+      <c r="A13" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="16">
         <v>2.0</v>
       </c>
-      <c r="C13" s="18">
+      <c r="C13" s="16">
         <v>48.0</v>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="16">
+        <v>1.0</v>
+      </c>
+      <c r="E13" s="16">
         <v>0.0</v>
       </c>
-      <c r="E13" s="18">
+      <c r="F13" s="16">
         <v>0.404484</v>
       </c>
-      <c r="F13" s="18">
+      <c r="G13" s="16">
         <v>-0.251714</v>
       </c>
-      <c r="G13" s="18">
+      <c r="H13" s="16">
         <v>2.0</v>
       </c>
-      <c r="H13" s="18">
+      <c r="I13" s="16">
         <v>0.339539</v>
       </c>
-      <c r="I13" s="18">
+      <c r="J13" s="16">
         <v>-0.264361</v>
       </c>
-      <c r="J13" s="18">
+      <c r="K13" s="16">
         <v>4.0</v>
       </c>
-      <c r="K13" s="18">
+      <c r="L13" s="16">
         <v>0.31387</v>
       </c>
-      <c r="L13" s="18">
+      <c r="M13" s="16">
         <v>-0.09202</v>
       </c>
-      <c r="M13" s="19"/>
-      <c r="N13" s="19"/>
-      <c r="O13" s="19"/>
-      <c r="P13" s="19"/>
-      <c r="Q13" s="19"/>
-      <c r="R13" s="19"/>
-      <c r="S13" s="19"/>
-      <c r="T13" s="19"/>
-      <c r="U13" s="19"/>
-      <c r="V13" s="19"/>
-      <c r="W13" s="19"/>
-      <c r="X13" s="19"/>
-      <c r="Y13" s="19"/>
-      <c r="Z13" s="19"/>
-      <c r="AA13" s="19"/>
-      <c r="AB13" s="19"/>
-      <c r="AC13" s="19"/>
-      <c r="AD13" s="19"/>
-      <c r="AE13" s="19"/>
+      <c r="N13" s="17"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="18"/>
+      <c r="Q13" s="18"/>
+      <c r="R13" s="18"/>
+      <c r="S13" s="18"/>
+      <c r="T13" s="18"/>
+      <c r="U13" s="18"/>
+      <c r="V13" s="18"/>
+      <c r="W13" s="18"/>
+      <c r="X13" s="18"/>
+      <c r="Y13" s="18"/>
+      <c r="Z13" s="18"/>
+      <c r="AA13" s="18"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B14" s="7">
+      <c r="A14" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="16">
         <v>2.0</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="16">
         <v>72.0</v>
       </c>
-      <c r="G14" s="7">
+      <c r="D14" s="16">
+        <v>1.0</v>
+      </c>
+      <c r="E14" s="16">
         <v>0.0</v>
       </c>
-      <c r="H14" s="7">
-        <v>0.76562</v>
-      </c>
-      <c r="I14" s="7">
-        <v>0.359441</v>
-      </c>
+      <c r="F14" s="16">
+        <v>0.687837</v>
+      </c>
+      <c r="G14" s="16">
+        <v>0.145153</v>
+      </c>
+      <c r="H14" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="I14" s="16">
+        <v>0.758792</v>
+      </c>
+      <c r="J14" s="16">
+        <v>0.186581</v>
+      </c>
+      <c r="K14" s="16">
+        <v>1.0</v>
+      </c>
+      <c r="L14" s="16">
+        <v>0.12286</v>
+      </c>
+      <c r="M14" s="16">
+        <v>0.02199</v>
+      </c>
+      <c r="N14" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="O14" s="17"/>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="7">
+      <c r="A15" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="16">
         <v>1.5</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="16">
         <v>48.0</v>
       </c>
-      <c r="G15" s="7">
+      <c r="D15" s="16">
+        <v>1.0</v>
+      </c>
+      <c r="E15" s="16">
         <v>0.0</v>
       </c>
-      <c r="H15" s="7">
+      <c r="F15" s="16">
+        <v>0.0369905</v>
+      </c>
+      <c r="G15" s="16">
+        <v>2.28E-4</v>
+      </c>
+      <c r="H15" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="I15" s="16">
         <v>0.0379268</v>
       </c>
-      <c r="I15" s="7">
+      <c r="J15" s="16">
         <v>0.001728</v>
       </c>
+      <c r="K15" s="16">
+        <v>2.0</v>
+      </c>
+      <c r="L15" s="16">
+        <v>0.0358674</v>
+      </c>
+      <c r="M15" s="16">
+        <v>0.00137</v>
+      </c>
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" s="7">
+      <c r="A16" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="16">
         <v>1.5</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="16">
         <v>72.0</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="16">
+        <v>1.0</v>
+      </c>
+      <c r="E16" s="16">
         <v>9.0</v>
       </c>
-      <c r="E16" s="7">
+      <c r="F16" s="16">
         <v>0.153509</v>
       </c>
-      <c r="F16" s="7">
+      <c r="G16" s="16">
         <v>0.072291</v>
       </c>
-      <c r="G16" s="7">
+      <c r="H16" s="16">
         <v>0.0</v>
       </c>
-      <c r="H16" s="7">
+      <c r="I16" s="16">
         <v>0.188314</v>
       </c>
-      <c r="I16" s="7">
+      <c r="J16" s="16">
         <v>-0.056644</v>
       </c>
-      <c r="J16" s="7">
+      <c r="K16" s="16">
         <v>7.0</v>
       </c>
-      <c r="K16" s="7">
+      <c r="L16" s="16">
         <v>0.128848</v>
       </c>
-      <c r="L16" s="7">
+      <c r="M16" s="16">
         <v>0.195241</v>
       </c>
+      <c r="N16" s="17"/>
+      <c r="O16" s="17"/>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B17" s="7">
+      <c r="A17" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="16">
         <v>2.0</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="16">
         <v>48.0</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="16">
+        <v>1.0</v>
+      </c>
+      <c r="E17" s="16">
         <v>0.0</v>
       </c>
-      <c r="E17" s="7">
+      <c r="F17" s="16">
         <v>0.275252</v>
       </c>
-      <c r="F17" s="7">
+      <c r="G17" s="16">
         <v>0.144195</v>
       </c>
-      <c r="G17" s="7">
+      <c r="H17" s="16">
         <v>0.0</v>
       </c>
-      <c r="H17" s="7">
+      <c r="I17" s="16">
         <v>0.528085</v>
       </c>
-      <c r="I17" s="7">
+      <c r="J17" s="16">
         <v>0.110889</v>
       </c>
+      <c r="K17" s="16">
+        <v>6.0</v>
+      </c>
+      <c r="L17" s="16">
+        <v>0.692386</v>
+      </c>
+      <c r="M17" s="16">
+        <v>0.616835</v>
+      </c>
+      <c r="N17" s="17"/>
+      <c r="O17" s="17"/>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="B18" s="18">
+      <c r="A18" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="16">
         <v>2.0</v>
       </c>
-      <c r="C18" s="18">
+      <c r="C18" s="16">
         <v>72.0</v>
       </c>
-      <c r="D18" s="18">
+      <c r="D18" s="16">
+        <v>1.0</v>
+      </c>
+      <c r="E18" s="16">
         <v>0.0</v>
       </c>
-      <c r="E18" s="18">
+      <c r="F18" s="16">
         <v>0.285772</v>
       </c>
-      <c r="F18" s="18">
+      <c r="G18" s="16">
         <v>0.206562</v>
       </c>
-      <c r="G18" s="18">
+      <c r="H18" s="16">
         <v>3.0</v>
       </c>
-      <c r="H18" s="18">
+      <c r="I18" s="16">
         <v>0.143423</v>
       </c>
-      <c r="I18" s="18">
+      <c r="J18" s="16">
         <v>-0.054014</v>
       </c>
-      <c r="J18" s="18">
+      <c r="K18" s="16">
         <v>0.0</v>
       </c>
-      <c r="K18" s="18">
+      <c r="L18" s="16">
         <v>0.273543</v>
       </c>
-      <c r="L18" s="18">
+      <c r="M18" s="16">
         <v>0.159298</v>
       </c>
-      <c r="M18" s="19"/>
-      <c r="N18" s="19"/>
-      <c r="O18" s="19"/>
-      <c r="P18" s="19"/>
-      <c r="Q18" s="19"/>
-      <c r="R18" s="19"/>
-      <c r="S18" s="19"/>
-      <c r="T18" s="19"/>
-      <c r="U18" s="19"/>
-      <c r="V18" s="19"/>
-      <c r="W18" s="19"/>
-      <c r="X18" s="19"/>
-      <c r="Y18" s="19"/>
-      <c r="Z18" s="19"/>
-      <c r="AA18" s="19"/>
-      <c r="AB18" s="19"/>
-      <c r="AC18" s="19"/>
-      <c r="AD18" s="19"/>
-      <c r="AE18" s="19"/>
+      <c r="N18" s="17"/>
+      <c r="O18" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:M1"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -12409,4102 +12428,1343 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
-      <c r="E1" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="H1" s="13" t="s">
+      <c r="A1" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="C1" s="3" t="s">
         <v>37</v>
       </c>
+      <c r="D1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="15" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="A2" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="16">
+        <v>1.5</v>
+      </c>
+      <c r="C2" s="16">
+        <v>48.0</v>
+      </c>
+      <c r="D2" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="E2" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="F2" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="G2" s="16">
+        <v>0.0563419</v>
+      </c>
+      <c r="H2" s="16">
+        <v>-0.003753</v>
+      </c>
+      <c r="I2" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="J2" s="17"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="16">
+        <v>1.5</v>
+      </c>
+      <c r="C3" s="16">
+        <v>72.0</v>
+      </c>
+      <c r="D3" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="G3" s="16">
+        <v>0.09968</v>
+      </c>
+      <c r="H3" s="16">
+        <v>0.01147</v>
+      </c>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="16">
+        <v>2.0</v>
+      </c>
+      <c r="C4" s="16">
+        <v>48.0</v>
+      </c>
+      <c r="D4" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="G4" s="16">
+        <v>0.299593</v>
+      </c>
+      <c r="H4" s="16">
+        <v>-0.094855</v>
+      </c>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="18"/>
+      <c r="N4" s="18"/>
+      <c r="O4" s="18"/>
+      <c r="P4" s="18"/>
+      <c r="Q4" s="18"/>
+      <c r="R4" s="18"/>
+      <c r="S4" s="18"/>
+      <c r="T4" s="18"/>
+      <c r="U4" s="18"/>
+      <c r="V4" s="18"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="16">
+        <v>2.0</v>
+      </c>
+      <c r="C5" s="16">
+        <v>72.0</v>
+      </c>
+      <c r="D5" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="G5" s="16">
+        <v>0.273452</v>
+      </c>
+      <c r="H5" s="16">
+        <v>0.095401</v>
+      </c>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="16">
+        <v>1.5</v>
+      </c>
+      <c r="C6" s="16">
+        <v>48.0</v>
+      </c>
+      <c r="D6" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="G6" s="16">
+        <v>0.302278</v>
+      </c>
+      <c r="H6" s="16">
+        <v>0.216884</v>
+      </c>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="16">
+        <v>1.5</v>
+      </c>
+      <c r="C7" s="16">
+        <v>72.0</v>
+      </c>
+      <c r="D7" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="G7" s="16">
+        <v>0.648478</v>
+      </c>
+      <c r="H7" s="16">
+        <v>0.415064</v>
+      </c>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="16">
+        <v>2.0</v>
+      </c>
+      <c r="C8" s="16">
+        <v>48.0</v>
+      </c>
+      <c r="D8" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="G8" s="16">
+        <v>0.439882</v>
+      </c>
+      <c r="H8" s="16">
+        <v>0.27209</v>
+      </c>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="16">
+        <v>2.0</v>
+      </c>
+      <c r="C9" s="16">
+        <v>72.0</v>
+      </c>
+      <c r="D9" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="G9" s="16">
+        <v>0.188511</v>
+      </c>
+      <c r="H9" s="16">
+        <v>0.091326</v>
+      </c>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="16">
+        <v>1.5</v>
+      </c>
+      <c r="C10" s="16">
+        <v>48.0</v>
+      </c>
+      <c r="D10" s="16">
+        <v>1.0</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="G10" s="16">
+        <v>0.0782306</v>
+      </c>
+      <c r="H10" s="16">
+        <v>-0.021749</v>
+      </c>
+      <c r="I10" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="J10" s="17"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="16">
+        <v>1.5</v>
+      </c>
+      <c r="C11" s="16">
+        <v>72.0</v>
+      </c>
+      <c r="D11" s="16">
+        <v>1.0</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="G11" s="16">
+        <v>0.0454423</v>
+      </c>
+      <c r="H11" s="16">
+        <v>-0.00203</v>
+      </c>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="16">
+        <v>2.0</v>
+      </c>
+      <c r="C12" s="16">
+        <v>48.0</v>
+      </c>
+      <c r="D12" s="16">
+        <v>1.0</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="G12" s="16">
+        <v>0.404484</v>
+      </c>
+      <c r="H12" s="16">
+        <v>-0.251714</v>
+      </c>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="18"/>
+      <c r="L12" s="18"/>
+      <c r="M12" s="18"/>
+      <c r="N12" s="18"/>
+      <c r="O12" s="18"/>
+      <c r="P12" s="18"/>
+      <c r="Q12" s="18"/>
+      <c r="R12" s="18"/>
+      <c r="S12" s="18"/>
+      <c r="T12" s="18"/>
+      <c r="U12" s="18"/>
+      <c r="V12" s="18"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="16">
+        <v>2.0</v>
+      </c>
+      <c r="C13" s="16">
+        <v>72.0</v>
+      </c>
+      <c r="D13" s="16">
+        <v>1.0</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="G13" s="16">
+        <v>0.687837</v>
+      </c>
+      <c r="H13" s="16">
+        <v>0.145153</v>
+      </c>
+      <c r="I13" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="J13" s="17"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="16">
+        <v>1.5</v>
+      </c>
+      <c r="C14" s="16">
+        <v>48.0</v>
+      </c>
+      <c r="D14" s="16">
+        <v>1.0</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="G14" s="16">
+        <v>0.0369905</v>
+      </c>
+      <c r="H14" s="16">
+        <v>2.28E-4</v>
+      </c>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="16">
+        <v>1.5</v>
+      </c>
+      <c r="C15" s="16">
+        <v>72.0</v>
+      </c>
+      <c r="D15" s="16">
+        <v>1.0</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F15" s="16">
+        <v>9.0</v>
+      </c>
+      <c r="G15" s="16">
+        <v>0.153509</v>
+      </c>
+      <c r="H15" s="16">
+        <v>0.072291</v>
+      </c>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="16">
+        <v>2.0</v>
+      </c>
+      <c r="C16" s="16">
+        <v>48.0</v>
+      </c>
+      <c r="D16" s="16">
+        <v>1.0</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="G16" s="16">
+        <v>0.275252</v>
+      </c>
+      <c r="H16" s="16">
+        <v>0.144195</v>
+      </c>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="16">
+        <v>2.0</v>
+      </c>
+      <c r="C17" s="16">
+        <v>72.0</v>
+      </c>
+      <c r="D17" s="16">
+        <v>1.0</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="G17" s="16">
+        <v>0.285772</v>
+      </c>
+      <c r="H17" s="16">
+        <v>0.206562</v>
+      </c>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="16">
+        <v>1.5</v>
+      </c>
+      <c r="C18" s="16">
+        <v>48.0</v>
+      </c>
+      <c r="D18" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="E18" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E2" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="F2" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="I2" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="L2" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="M2" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="N2" s="14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="7" t="s">
+      <c r="F18" s="16">
+        <v>1.0</v>
+      </c>
+      <c r="G18" s="16">
+        <v>0.122002</v>
+      </c>
+      <c r="H18" s="16">
+        <v>-0.045195</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B19" s="16">
         <v>1.5</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C19" s="16">
+        <v>72.0</v>
+      </c>
+      <c r="D19" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F19" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="G19" s="16">
+        <v>0.3459</v>
+      </c>
+      <c r="H19" s="16">
+        <v>0.152536</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="16">
+        <v>2.0</v>
+      </c>
+      <c r="C20" s="16">
         <v>48.0</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D20" s="16">
         <v>0.0</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E20" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F20" s="16">
         <v>0.0</v>
       </c>
-      <c r="F3" s="7">
-        <v>0.0563419</v>
-      </c>
-      <c r="G3" s="7">
-        <v>-0.003753</v>
-      </c>
-      <c r="H3" s="7">
+      <c r="G20" s="16">
+        <v>0.165687</v>
+      </c>
+      <c r="H20" s="16">
+        <v>0.039983</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" s="16">
+        <v>2.0</v>
+      </c>
+      <c r="C21" s="16">
+        <v>72.0</v>
+      </c>
+      <c r="D21" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F21" s="16">
+        <v>7.0</v>
+      </c>
+      <c r="G21" s="16">
+        <v>0.290725</v>
+      </c>
+      <c r="H21" s="16">
+        <v>-0.247398</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="16">
+        <v>1.5</v>
+      </c>
+      <c r="C22" s="16">
+        <v>48.0</v>
+      </c>
+      <c r="D22" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F22" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="G22" s="16">
+        <v>0.57742</v>
+      </c>
+      <c r="H22" s="16">
+        <v>0.394852</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="16">
+        <v>1.5</v>
+      </c>
+      <c r="C23" s="16">
+        <v>72.0</v>
+      </c>
+      <c r="D23" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F23" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="G23" s="16">
+        <v>0.768339</v>
+      </c>
+      <c r="H23" s="16">
+        <v>0.403431</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" s="16">
+        <v>2.0</v>
+      </c>
+      <c r="C24" s="16">
+        <v>48.0</v>
+      </c>
+      <c r="D24" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F24" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="G24" s="16">
+        <v>0.0798324</v>
+      </c>
+      <c r="H24" s="16">
+        <v>5.31E-4</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" s="16">
+        <v>2.0</v>
+      </c>
+      <c r="C25" s="16">
+        <v>72.0</v>
+      </c>
+      <c r="D25" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="E25" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F25" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="G25" s="16">
+        <v>0.205691</v>
+      </c>
+      <c r="H25" s="16">
+        <v>0.106242</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26" s="16">
+        <v>1.5</v>
+      </c>
+      <c r="C26" s="16">
+        <v>48.0</v>
+      </c>
+      <c r="D26" s="16">
         <v>1.0</v>
       </c>
-      <c r="I3" s="7">
-        <v>0.122002</v>
-      </c>
-      <c r="J3" s="7">
-        <v>-0.045195</v>
-      </c>
-      <c r="K3" s="7">
+      <c r="E26" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F26" s="16">
         <v>0.0</v>
       </c>
-      <c r="L3" s="7">
+      <c r="G26" s="16">
+        <v>0.0829006</v>
+      </c>
+      <c r="H26" s="16">
+        <v>-0.026013</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" s="16">
+        <v>1.5</v>
+      </c>
+      <c r="C27" s="16">
+        <v>72.0</v>
+      </c>
+      <c r="D27" s="16">
+        <v>1.0</v>
+      </c>
+      <c r="E27" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F27" s="16">
+        <v>9.0</v>
+      </c>
+      <c r="G27" s="16">
+        <v>0.0990531</v>
+      </c>
+      <c r="H27" s="16">
+        <v>0.019526</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B28" s="16">
+        <v>2.0</v>
+      </c>
+      <c r="C28" s="16">
+        <v>48.0</v>
+      </c>
+      <c r="D28" s="16">
+        <v>1.0</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F28" s="16">
+        <v>2.0</v>
+      </c>
+      <c r="G28" s="16">
+        <v>0.339539</v>
+      </c>
+      <c r="H28" s="16">
+        <v>-0.264361</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B29" s="16">
+        <v>2.0</v>
+      </c>
+      <c r="C29" s="16">
+        <v>72.0</v>
+      </c>
+      <c r="D29" s="16">
+        <v>1.0</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F29" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="G29" s="16">
+        <v>0.758792</v>
+      </c>
+      <c r="H29" s="16">
+        <v>0.186581</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B30" s="16">
+        <v>1.5</v>
+      </c>
+      <c r="C30" s="16">
+        <v>48.0</v>
+      </c>
+      <c r="D30" s="16">
+        <v>1.0</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F30" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="G30" s="16">
+        <v>0.0379268</v>
+      </c>
+      <c r="H30" s="16">
+        <v>0.001728</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B31" s="16">
+        <v>1.5</v>
+      </c>
+      <c r="C31" s="16">
+        <v>72.0</v>
+      </c>
+      <c r="D31" s="16">
+        <v>1.0</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F31" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="G31" s="16">
+        <v>0.188314</v>
+      </c>
+      <c r="H31" s="16">
+        <v>-0.056644</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B32" s="16">
+        <v>2.0</v>
+      </c>
+      <c r="C32" s="16">
+        <v>48.0</v>
+      </c>
+      <c r="D32" s="16">
+        <v>1.0</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F32" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="G32" s="16">
+        <v>0.528085</v>
+      </c>
+      <c r="H32" s="16">
+        <v>0.110889</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B33" s="16">
+        <v>2.0</v>
+      </c>
+      <c r="C33" s="16">
+        <v>72.0</v>
+      </c>
+      <c r="D33" s="16">
+        <v>1.0</v>
+      </c>
+      <c r="E33" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F33" s="16">
+        <v>3.0</v>
+      </c>
+      <c r="G33" s="16">
+        <v>0.143423</v>
+      </c>
+      <c r="H33" s="16">
+        <v>-0.054014</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B34" s="16">
+        <v>1.5</v>
+      </c>
+      <c r="C34" s="16">
+        <v>48.0</v>
+      </c>
+      <c r="D34" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="E34" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F34" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="G34" s="16">
         <v>0.132857</v>
       </c>
-      <c r="M3" s="7">
+      <c r="H34" s="16">
         <v>-0.022211</v>
       </c>
-      <c r="N3" s="7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="s">
+    </row>
+    <row r="35">
+      <c r="A35" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B35" s="16">
         <v>1.5</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C35" s="16">
         <v>72.0</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D35" s="16">
         <v>0.0</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E35" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F35" s="16">
         <v>0.0</v>
       </c>
-      <c r="F4" s="7">
-        <v>0.09968</v>
-      </c>
-      <c r="G4" s="7">
-        <v>0.01147</v>
-      </c>
-      <c r="H4" s="7">
+      <c r="G35" s="16">
+        <v>0.140796</v>
+      </c>
+      <c r="H35" s="16">
+        <v>0.039724</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B36" s="16">
+        <v>2.0</v>
+      </c>
+      <c r="C36" s="16">
+        <v>48.0</v>
+      </c>
+      <c r="D36" s="16">
         <v>0.0</v>
       </c>
-      <c r="I4" s="7">
-        <v>0.3459</v>
-      </c>
-      <c r="J4" s="7">
-        <v>0.152536</v>
-      </c>
-      <c r="K4" s="7">
+      <c r="E36" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F36" s="16">
         <v>0.0</v>
       </c>
-      <c r="L4" s="7">
-        <v>0.140796</v>
-      </c>
-      <c r="M4" s="7">
-        <v>0.039724</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="20" t="s">
+      <c r="G36" s="16">
+        <v>0.166992</v>
+      </c>
+      <c r="H36" s="16">
+        <v>0.040403</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B37" s="16">
         <v>2.0</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C37" s="16">
+        <v>72.0</v>
+      </c>
+      <c r="D37" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="E37" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F37" s="16">
+        <v>1.0</v>
+      </c>
+      <c r="G37" s="16">
+        <v>0.293721</v>
+      </c>
+      <c r="H37" s="16">
+        <v>-0.259891</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B38" s="16">
+        <v>1.5</v>
+      </c>
+      <c r="C38" s="16">
         <v>48.0</v>
       </c>
-      <c r="D5" s="20">
+      <c r="D38" s="16">
         <v>0.0</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E38" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F38" s="16">
         <v>0.0</v>
       </c>
-      <c r="F5" s="7">
-        <v>0.299593</v>
-      </c>
-      <c r="G5" s="7">
-        <v>-0.094855</v>
-      </c>
-      <c r="H5" s="7">
+      <c r="G38" s="16">
+        <v>0.581207</v>
+      </c>
+      <c r="H38" s="16">
+        <v>0.448983</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B39" s="16">
+        <v>1.5</v>
+      </c>
+      <c r="C39" s="16">
+        <v>72.0</v>
+      </c>
+      <c r="D39" s="16">
         <v>0.0</v>
       </c>
-      <c r="I5" s="7">
-        <v>0.165687</v>
-      </c>
-      <c r="J5" s="7">
-        <v>0.039983</v>
-      </c>
-      <c r="K5" s="7">
+      <c r="E39" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F39" s="16">
         <v>0.0</v>
       </c>
-      <c r="L5" s="7">
-        <v>0.166992</v>
-      </c>
-      <c r="M5" s="7">
-        <v>0.040403</v>
-      </c>
-      <c r="O5" s="21"/>
-      <c r="P5" s="21"/>
-      <c r="Q5" s="21"/>
-      <c r="R5" s="21"/>
-      <c r="S5" s="21"/>
-      <c r="T5" s="21"/>
-      <c r="U5" s="21"/>
-      <c r="V5" s="21"/>
-      <c r="W5" s="21"/>
-      <c r="X5" s="21"/>
-      <c r="Y5" s="21"/>
-      <c r="Z5" s="21"/>
-      <c r="AA5" s="21"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="s">
+      <c r="G39" s="16">
+        <v>0.720302</v>
+      </c>
+      <c r="H39" s="16">
+        <v>0.461317</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B40" s="16">
+        <v>2.0</v>
+      </c>
+      <c r="C40" s="16">
+        <v>48.0</v>
+      </c>
+      <c r="D40" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="E40" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F40" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="G40" s="16">
+        <v>0.0996823</v>
+      </c>
+      <c r="H40" s="16">
+        <v>-0.017615</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B41" s="16">
+        <v>2.0</v>
+      </c>
+      <c r="C41" s="16">
+        <v>72.0</v>
+      </c>
+      <c r="D41" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="E41" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F41" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="G41" s="16">
+        <v>0.166254</v>
+      </c>
+      <c r="H41" s="16">
+        <v>0.151412</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B42" s="16">
+        <v>1.5</v>
+      </c>
+      <c r="C42" s="16">
+        <v>48.0</v>
+      </c>
+      <c r="D42" s="16">
+        <v>1.0</v>
+      </c>
+      <c r="E42" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F42" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="G42" s="16">
+        <v>0.0471715</v>
+      </c>
+      <c r="H42" s="16">
+        <v>-0.006232</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B43" s="16">
+        <v>1.5</v>
+      </c>
+      <c r="C43" s="16">
+        <v>72.0</v>
+      </c>
+      <c r="D43" s="16">
+        <v>1.0</v>
+      </c>
+      <c r="E43" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F43" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="G43" s="16">
+        <v>0.0933383</v>
+      </c>
+      <c r="H43" s="16">
+        <v>-0.003156</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B44" s="16">
         <v>2.0</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C44" s="16">
+        <v>48.0</v>
+      </c>
+      <c r="D44" s="16">
+        <v>1.0</v>
+      </c>
+      <c r="E44" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F44" s="16">
+        <v>4.0</v>
+      </c>
+      <c r="G44" s="16">
+        <v>0.31387</v>
+      </c>
+      <c r="H44" s="16">
+        <v>-0.09202</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B45" s="16">
+        <v>2.0</v>
+      </c>
+      <c r="C45" s="16">
         <v>72.0</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D45" s="16">
+        <v>1.0</v>
+      </c>
+      <c r="E45" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F45" s="16">
+        <v>1.0</v>
+      </c>
+      <c r="G45" s="16">
+        <v>0.12286</v>
+      </c>
+      <c r="H45" s="16">
+        <v>0.02199</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B46" s="16">
+        <v>1.5</v>
+      </c>
+      <c r="C46" s="16">
+        <v>48.0</v>
+      </c>
+      <c r="D46" s="16">
+        <v>1.0</v>
+      </c>
+      <c r="E46" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F46" s="16">
+        <v>2.0</v>
+      </c>
+      <c r="G46" s="16">
+        <v>0.0358674</v>
+      </c>
+      <c r="H46" s="16">
+        <v>0.00137</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B47" s="16">
+        <v>1.5</v>
+      </c>
+      <c r="C47" s="16">
+        <v>72.0</v>
+      </c>
+      <c r="D47" s="16">
+        <v>1.0</v>
+      </c>
+      <c r="E47" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F47" s="16">
+        <v>7.0</v>
+      </c>
+      <c r="G47" s="16">
+        <v>0.128848</v>
+      </c>
+      <c r="H47" s="16">
+        <v>0.195241</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B48" s="16">
+        <v>2.0</v>
+      </c>
+      <c r="C48" s="16">
+        <v>48.0</v>
+      </c>
+      <c r="D48" s="16">
+        <v>1.0</v>
+      </c>
+      <c r="E48" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F48" s="16">
+        <v>6.0</v>
+      </c>
+      <c r="G48" s="16">
+        <v>0.692386</v>
+      </c>
+      <c r="H48" s="16">
+        <v>0.616835</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B49" s="16">
+        <v>2.0</v>
+      </c>
+      <c r="C49" s="16">
+        <v>72.0</v>
+      </c>
+      <c r="D49" s="16">
+        <v>1.0</v>
+      </c>
+      <c r="E49" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F49" s="16">
         <v>0.0</v>
       </c>
-      <c r="E6" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="F6" s="7">
-        <v>0.273452</v>
-      </c>
-      <c r="G6" s="7">
-        <v>0.095401</v>
-      </c>
-      <c r="H6" s="7">
-        <v>7.0</v>
-      </c>
-      <c r="I6" s="7">
-        <v>0.290725</v>
-      </c>
-      <c r="J6" s="7">
-        <v>-0.247398</v>
-      </c>
-      <c r="K6" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="L6" s="7">
-        <v>0.293721</v>
-      </c>
-      <c r="M6" s="7">
-        <v>-0.259891</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="7">
-        <v>1.5</v>
-      </c>
-      <c r="C7" s="7">
-        <v>48.0</v>
-      </c>
-      <c r="D7" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="E7" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="F7" s="7">
-        <v>0.302278</v>
-      </c>
-      <c r="G7" s="7">
-        <v>0.216884</v>
-      </c>
-      <c r="H7" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="I7" s="7">
-        <v>0.57742</v>
-      </c>
-      <c r="J7" s="7">
-        <v>0.394852</v>
-      </c>
-      <c r="K7" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="L7" s="7">
-        <v>0.581207</v>
-      </c>
-      <c r="M7" s="7">
-        <v>0.448983</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="7">
-        <v>1.5</v>
-      </c>
-      <c r="C8" s="7">
-        <v>72.0</v>
-      </c>
-      <c r="D8" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="E8" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="F8" s="7">
-        <v>0.648478</v>
-      </c>
-      <c r="G8" s="7">
-        <v>0.415064</v>
-      </c>
-      <c r="H8" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="I8" s="7">
-        <v>0.768339</v>
-      </c>
-      <c r="J8" s="7">
-        <v>0.403431</v>
-      </c>
-      <c r="K8" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="L8" s="7">
-        <v>0.720302</v>
-      </c>
-      <c r="M8" s="7">
-        <v>0.461317</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="C9" s="7">
-        <v>48.0</v>
-      </c>
-      <c r="D9" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="E9" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="F9" s="7">
-        <v>0.439882</v>
-      </c>
-      <c r="G9" s="7">
-        <v>0.27209</v>
-      </c>
-      <c r="H9" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="I9" s="7">
-        <v>0.0798324</v>
-      </c>
-      <c r="J9" s="7">
-        <v>5.31E-4</v>
-      </c>
-      <c r="K9" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="L9" s="7">
-        <v>0.0996823</v>
-      </c>
-      <c r="M9" s="7">
-        <v>-0.017615</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="C10" s="7">
-        <v>72.0</v>
-      </c>
-      <c r="D10" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="E10" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="F10" s="7">
-        <v>0.188511</v>
-      </c>
-      <c r="G10" s="7">
-        <v>0.091326</v>
-      </c>
-      <c r="H10" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="I10" s="7">
-        <v>0.205691</v>
-      </c>
-      <c r="J10" s="7">
-        <v>0.106242</v>
-      </c>
-      <c r="K10" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="L10" s="7">
-        <v>0.166254</v>
-      </c>
-      <c r="M10" s="7">
-        <v>0.151412</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="18">
-        <v>1.5</v>
-      </c>
-      <c r="C11" s="18">
-        <v>48.0</v>
-      </c>
-      <c r="D11" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="E11" s="18">
-        <v>0.0</v>
-      </c>
-      <c r="F11" s="18">
-        <v>0.0782306</v>
-      </c>
-      <c r="G11" s="18">
-        <v>-0.021749</v>
-      </c>
-      <c r="H11" s="18">
-        <v>0.0</v>
-      </c>
-      <c r="I11" s="18">
-        <v>0.0829006</v>
-      </c>
-      <c r="J11" s="18">
-        <v>-0.026013</v>
-      </c>
-      <c r="K11" s="18">
-        <v>0.0</v>
-      </c>
-      <c r="L11" s="18">
-        <v>0.0471715</v>
-      </c>
-      <c r="M11" s="18">
-        <v>-0.006232</v>
-      </c>
-      <c r="N11" s="18" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="7">
-        <v>1.5</v>
-      </c>
-      <c r="C12" s="7">
-        <v>72.0</v>
-      </c>
-      <c r="D12" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="H12" s="7">
-        <v>9.0</v>
-      </c>
-      <c r="I12" s="7">
-        <v>0.0990531</v>
-      </c>
-      <c r="J12" s="7">
-        <v>0.019526</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="18">
-        <v>2.0</v>
-      </c>
-      <c r="C13" s="18">
-        <v>48.0</v>
-      </c>
-      <c r="D13" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="E13" s="18">
-        <v>0.0</v>
-      </c>
-      <c r="F13" s="18">
-        <v>0.404484</v>
-      </c>
-      <c r="G13" s="18">
-        <v>-0.251714</v>
-      </c>
-      <c r="H13" s="18">
-        <v>2.0</v>
-      </c>
-      <c r="I13" s="18">
-        <v>0.339539</v>
-      </c>
-      <c r="J13" s="18">
-        <v>-0.264361</v>
-      </c>
-      <c r="K13" s="18">
-        <v>4.0</v>
-      </c>
-      <c r="L13" s="18">
-        <v>0.31387</v>
-      </c>
-      <c r="M13" s="18">
-        <v>-0.09202</v>
-      </c>
-      <c r="N13" s="19"/>
-      <c r="O13" s="21"/>
-      <c r="P13" s="21"/>
-      <c r="Q13" s="21"/>
-      <c r="R13" s="21"/>
-      <c r="S13" s="21"/>
-      <c r="T13" s="21"/>
-      <c r="U13" s="21"/>
-      <c r="V13" s="21"/>
-      <c r="W13" s="21"/>
-      <c r="X13" s="21"/>
-      <c r="Y13" s="21"/>
-      <c r="Z13" s="21"/>
-      <c r="AA13" s="21"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="C14" s="7">
-        <v>72.0</v>
-      </c>
-      <c r="D14" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="E14" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="F14" s="7">
-        <v>0.687837</v>
-      </c>
-      <c r="G14" s="7">
-        <v>0.145153</v>
-      </c>
-      <c r="H14" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="I14" s="7">
-        <v>0.758792</v>
-      </c>
-      <c r="J14" s="7">
-        <v>0.186581</v>
-      </c>
-      <c r="K14" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="L14" s="7">
-        <v>0.12286</v>
-      </c>
-      <c r="M14" s="7">
-        <v>0.02199</v>
-      </c>
-      <c r="N14" s="7" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="7">
-        <v>1.5</v>
-      </c>
-      <c r="C15" s="7">
-        <v>48.0</v>
-      </c>
-      <c r="D15" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="H15" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="I15" s="7">
-        <v>0.0379268</v>
-      </c>
-      <c r="J15" s="7">
-        <v>0.001728</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="7">
-        <v>1.5</v>
-      </c>
-      <c r="C16" s="7">
-        <v>72.0</v>
-      </c>
-      <c r="D16" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="E16" s="7">
-        <v>9.0</v>
-      </c>
-      <c r="F16" s="7">
-        <v>0.153509</v>
-      </c>
-      <c r="G16" s="7">
-        <v>0.072291</v>
-      </c>
-      <c r="H16" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="I16" s="7">
-        <v>0.188314</v>
-      </c>
-      <c r="J16" s="7">
-        <v>-0.056644</v>
-      </c>
-      <c r="K16" s="7">
-        <v>7.0</v>
-      </c>
-      <c r="L16" s="7">
-        <v>0.128848</v>
-      </c>
-      <c r="M16" s="7">
-        <v>0.195241</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="C17" s="7">
-        <v>48.0</v>
-      </c>
-      <c r="D17" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="E17" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="F17" s="7">
-        <v>0.275252</v>
-      </c>
-      <c r="G17" s="7">
-        <v>0.144195</v>
-      </c>
-      <c r="H17" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="I17" s="7">
-        <v>0.528085</v>
-      </c>
-      <c r="J17" s="7">
-        <v>0.110889</v>
-      </c>
-      <c r="K17" s="7">
-        <v>6.0</v>
-      </c>
-      <c r="L17" s="7">
-        <v>0.692386</v>
-      </c>
-      <c r="M17" s="7">
-        <v>0.616835</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="18">
-        <v>2.0</v>
-      </c>
-      <c r="C18" s="18">
-        <v>72.0</v>
-      </c>
-      <c r="D18" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="E18" s="18">
-        <v>0.0</v>
-      </c>
-      <c r="F18" s="18">
-        <v>0.285772</v>
-      </c>
-      <c r="G18" s="18">
-        <v>0.206562</v>
-      </c>
-      <c r="H18" s="18">
-        <v>3.0</v>
-      </c>
-      <c r="I18" s="18">
-        <v>0.143423</v>
-      </c>
-      <c r="J18" s="18">
-        <v>-0.054014</v>
-      </c>
-      <c r="K18" s="18">
-        <v>0.0</v>
-      </c>
-      <c r="L18" s="18">
+      <c r="G49" s="16">
         <v>0.273543</v>
       </c>
-      <c r="M18" s="18">
+      <c r="H49" s="16">
         <v>0.159298</v>
       </c>
-      <c r="N18" s="19"/>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="H1:J1"/>
-    <mergeCell ref="K1:M1"/>
-  </mergeCells>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <cols>
-    <col customWidth="1" min="1" max="1" width="10.25"/>
-    <col customWidth="1" min="2" max="2" width="8.25"/>
-    <col customWidth="1" min="3" max="3" width="9.13"/>
-    <col customWidth="1" min="4" max="4" width="6.25"/>
-    <col customWidth="1" min="5" max="5" width="8.13"/>
-    <col customWidth="1" min="6" max="6" width="14.63"/>
-    <col customWidth="1" min="8" max="8" width="15.75"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E1" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="F1" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="H1" s="22" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="7">
-        <v>1.5</v>
-      </c>
-      <c r="C2" s="7">
-        <v>48.0</v>
-      </c>
-      <c r="D2" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="E2" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="F2" s="7">
-        <v>0.122002</v>
-      </c>
-      <c r="G2" s="7">
-        <v>-0.045195</v>
-      </c>
-      <c r="H2" s="23" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="7">
-        <v>1.5</v>
-      </c>
-      <c r="C3" s="7">
-        <v>72.0</v>
-      </c>
-      <c r="D3" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="E3" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="F3" s="7">
-        <v>0.3459</v>
-      </c>
-      <c r="G3" s="7">
-        <v>0.152536</v>
-      </c>
-      <c r="H3" s="24"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="C4" s="7">
-        <v>48.0</v>
-      </c>
-      <c r="D4" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="E4" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="F4" s="7">
-        <v>0.165687</v>
-      </c>
-      <c r="G4" s="7">
-        <v>0.039983</v>
-      </c>
-      <c r="H4" s="24"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="C5" s="7">
-        <v>72.0</v>
-      </c>
-      <c r="D5" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="E5" s="7">
-        <v>7.0</v>
-      </c>
-      <c r="F5" s="7">
-        <v>0.290725</v>
-      </c>
-      <c r="G5" s="7">
-        <v>-0.247398</v>
-      </c>
-      <c r="H5" s="24"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1.5</v>
-      </c>
-      <c r="C6" s="7">
-        <v>48.0</v>
-      </c>
-      <c r="D6" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="E6" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="F6" s="7">
-        <v>0.57742</v>
-      </c>
-      <c r="G6" s="7">
-        <v>0.394852</v>
-      </c>
-      <c r="H6" s="24"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="7">
-        <v>1.5</v>
-      </c>
-      <c r="C7" s="7">
-        <v>72.0</v>
-      </c>
-      <c r="D7" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="E7" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="F7" s="7">
-        <v>0.768339</v>
-      </c>
-      <c r="G7" s="7">
-        <v>0.403431</v>
-      </c>
-      <c r="H7" s="24"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="C8" s="7">
-        <v>48.0</v>
-      </c>
-      <c r="D8" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="E8" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="F8" s="7">
-        <v>0.0798324</v>
-      </c>
-      <c r="G8" s="7">
-        <v>5.31E-4</v>
-      </c>
-      <c r="H8" s="24"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="C9" s="7">
-        <v>72.0</v>
-      </c>
-      <c r="D9" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="E9" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="F9" s="7">
-        <v>0.205691</v>
-      </c>
-      <c r="G9" s="7">
-        <v>0.106242</v>
-      </c>
-      <c r="H9" s="24"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="7">
-        <v>1.5</v>
-      </c>
-      <c r="C10" s="7">
-        <v>48.0</v>
-      </c>
-      <c r="D10" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="E10" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="F10" s="7">
-        <v>0.0829006</v>
-      </c>
-      <c r="G10" s="7">
-        <v>-0.026013</v>
-      </c>
-      <c r="H10" s="23" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="7">
-        <v>1.5</v>
-      </c>
-      <c r="C11" s="7">
-        <v>72.0</v>
-      </c>
-      <c r="D11" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="E11" s="7">
-        <v>9.0</v>
-      </c>
-      <c r="F11" s="7">
-        <v>0.0990531</v>
-      </c>
-      <c r="G11" s="7">
-        <v>0.019526</v>
-      </c>
-      <c r="H11" s="24"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="C12" s="7">
-        <v>48.0</v>
-      </c>
-      <c r="D12" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="E12" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="F12" s="7">
-        <v>0.339539</v>
-      </c>
-      <c r="G12" s="7">
-        <v>-0.264361</v>
-      </c>
-      <c r="H12" s="24"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="C13" s="7">
-        <v>72.0</v>
-      </c>
-      <c r="D13" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="E13" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="F13" s="7">
-        <v>0.76562</v>
-      </c>
-      <c r="G13" s="7">
-        <v>0.359441</v>
-      </c>
-      <c r="H13" s="24"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="7">
-        <v>1.5</v>
-      </c>
-      <c r="C14" s="7">
-        <v>48.0</v>
-      </c>
-      <c r="D14" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="E14" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="F14" s="7">
-        <v>0.0379268</v>
-      </c>
-      <c r="G14" s="7">
-        <v>0.001728</v>
-      </c>
-      <c r="H14" s="24"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="7">
-        <v>1.5</v>
-      </c>
-      <c r="C15" s="7">
-        <v>72.0</v>
-      </c>
-      <c r="D15" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="E15" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="F15" s="7">
-        <v>0.188314</v>
-      </c>
-      <c r="G15" s="7">
-        <v>-0.056644</v>
-      </c>
-      <c r="H15" s="24"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="C16" s="7">
-        <v>48.0</v>
-      </c>
-      <c r="D16" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="E16" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="F16" s="7">
-        <v>0.528085</v>
-      </c>
-      <c r="G16" s="7">
-        <v>0.110889</v>
-      </c>
-      <c r="H16" s="24"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="C17" s="7">
-        <v>72.0</v>
-      </c>
-      <c r="D17" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="E17" s="7">
-        <v>3.0</v>
-      </c>
-      <c r="F17" s="7">
-        <v>0.143423</v>
-      </c>
-      <c r="G17" s="7">
-        <v>-0.054014</v>
-      </c>
-      <c r="H17" s="24"/>
-    </row>
-    <row r="18">
-      <c r="H18" s="24"/>
-    </row>
-    <row r="19">
-      <c r="H19" s="24"/>
-    </row>
-    <row r="20">
-      <c r="H20" s="24"/>
-    </row>
-    <row r="21">
-      <c r="H21" s="24"/>
-    </row>
-    <row r="22">
-      <c r="H22" s="24"/>
-    </row>
-    <row r="23">
-      <c r="H23" s="24"/>
-    </row>
-    <row r="24">
-      <c r="H24" s="24"/>
-    </row>
-    <row r="25">
-      <c r="H25" s="24"/>
-    </row>
-    <row r="26">
-      <c r="H26" s="24"/>
-    </row>
-    <row r="27">
-      <c r="H27" s="24"/>
-    </row>
-    <row r="28">
-      <c r="H28" s="24"/>
-    </row>
-    <row r="29">
-      <c r="H29" s="24"/>
-    </row>
-    <row r="30">
-      <c r="H30" s="24"/>
-    </row>
-    <row r="31">
-      <c r="H31" s="24"/>
-    </row>
-    <row r="32">
-      <c r="H32" s="24"/>
-    </row>
-    <row r="33">
-      <c r="H33" s="24"/>
-    </row>
-    <row r="34">
-      <c r="H34" s="24"/>
-    </row>
-    <row r="35">
-      <c r="H35" s="24"/>
-    </row>
-    <row r="36">
-      <c r="H36" s="24"/>
-    </row>
-    <row r="37">
-      <c r="H37" s="24"/>
-    </row>
-    <row r="38">
-      <c r="H38" s="24"/>
-    </row>
-    <row r="39">
-      <c r="H39" s="24"/>
-    </row>
-    <row r="40">
-      <c r="H40" s="24"/>
-    </row>
-    <row r="41">
-      <c r="H41" s="24"/>
-    </row>
-    <row r="42">
-      <c r="H42" s="24"/>
-    </row>
-    <row r="43">
-      <c r="H43" s="24"/>
-    </row>
-    <row r="44">
-      <c r="H44" s="24"/>
-    </row>
-    <row r="45">
-      <c r="H45" s="24"/>
-    </row>
-    <row r="46">
-      <c r="H46" s="24"/>
-    </row>
-    <row r="47">
-      <c r="H47" s="24"/>
-    </row>
-    <row r="48">
-      <c r="H48" s="24"/>
-    </row>
-    <row r="49">
-      <c r="H49" s="24"/>
-    </row>
-    <row r="50">
-      <c r="H50" s="24"/>
-    </row>
-    <row r="51">
-      <c r="H51" s="24"/>
-    </row>
-    <row r="52">
-      <c r="H52" s="24"/>
-    </row>
-    <row r="53">
-      <c r="H53" s="24"/>
-    </row>
-    <row r="54">
-      <c r="H54" s="24"/>
-    </row>
-    <row r="55">
-      <c r="H55" s="24"/>
-    </row>
-    <row r="56">
-      <c r="H56" s="24"/>
-    </row>
-    <row r="57">
-      <c r="H57" s="24"/>
-    </row>
-    <row r="58">
-      <c r="H58" s="24"/>
-    </row>
-    <row r="59">
-      <c r="H59" s="24"/>
-    </row>
-    <row r="60">
-      <c r="H60" s="24"/>
-    </row>
-    <row r="61">
-      <c r="H61" s="24"/>
-    </row>
-    <row r="62">
-      <c r="H62" s="24"/>
-    </row>
-    <row r="63">
-      <c r="H63" s="24"/>
-    </row>
-    <row r="64">
-      <c r="H64" s="24"/>
-    </row>
-    <row r="65">
-      <c r="H65" s="24"/>
-    </row>
-    <row r="66">
-      <c r="H66" s="24"/>
-    </row>
-    <row r="67">
-      <c r="H67" s="24"/>
-    </row>
-    <row r="68">
-      <c r="H68" s="24"/>
-    </row>
-    <row r="69">
-      <c r="H69" s="24"/>
-    </row>
-    <row r="70">
-      <c r="H70" s="24"/>
-    </row>
-    <row r="71">
-      <c r="H71" s="24"/>
-    </row>
-    <row r="72">
-      <c r="H72" s="24"/>
-    </row>
-    <row r="73">
-      <c r="H73" s="24"/>
-    </row>
-    <row r="74">
-      <c r="H74" s="24"/>
-    </row>
-    <row r="75">
-      <c r="H75" s="24"/>
-    </row>
-    <row r="76">
-      <c r="H76" s="24"/>
-    </row>
-    <row r="77">
-      <c r="H77" s="24"/>
-    </row>
-    <row r="78">
-      <c r="H78" s="24"/>
-    </row>
-    <row r="79">
-      <c r="H79" s="24"/>
-    </row>
-    <row r="80">
-      <c r="H80" s="24"/>
-    </row>
-    <row r="81">
-      <c r="H81" s="24"/>
-    </row>
-    <row r="82">
-      <c r="H82" s="24"/>
-    </row>
-    <row r="83">
-      <c r="H83" s="24"/>
-    </row>
-    <row r="84">
-      <c r="H84" s="24"/>
-    </row>
-    <row r="85">
-      <c r="H85" s="24"/>
-    </row>
-    <row r="86">
-      <c r="H86" s="24"/>
-    </row>
-    <row r="87">
-      <c r="H87" s="24"/>
-    </row>
-    <row r="88">
-      <c r="H88" s="24"/>
-    </row>
-    <row r="89">
-      <c r="H89" s="24"/>
-    </row>
-    <row r="90">
-      <c r="H90" s="24"/>
-    </row>
-    <row r="91">
-      <c r="H91" s="24"/>
-    </row>
-    <row r="92">
-      <c r="H92" s="24"/>
-    </row>
-    <row r="93">
-      <c r="H93" s="24"/>
-    </row>
-    <row r="94">
-      <c r="H94" s="24"/>
-    </row>
-    <row r="95">
-      <c r="H95" s="24"/>
-    </row>
-    <row r="96">
-      <c r="H96" s="24"/>
-    </row>
-    <row r="97">
-      <c r="H97" s="24"/>
-    </row>
-    <row r="98">
-      <c r="H98" s="24"/>
-    </row>
-    <row r="99">
-      <c r="H99" s="24"/>
-    </row>
-    <row r="100">
-      <c r="H100" s="24"/>
-    </row>
-    <row r="101">
-      <c r="H101" s="24"/>
-    </row>
-    <row r="102">
-      <c r="H102" s="24"/>
-    </row>
-    <row r="103">
-      <c r="H103" s="24"/>
-    </row>
-    <row r="104">
-      <c r="H104" s="24"/>
-    </row>
-    <row r="105">
-      <c r="H105" s="24"/>
-    </row>
-    <row r="106">
-      <c r="H106" s="24"/>
-    </row>
-    <row r="107">
-      <c r="H107" s="24"/>
-    </row>
-    <row r="108">
-      <c r="H108" s="24"/>
-    </row>
-    <row r="109">
-      <c r="H109" s="24"/>
-    </row>
-    <row r="110">
-      <c r="H110" s="24"/>
-    </row>
-    <row r="111">
-      <c r="H111" s="24"/>
-    </row>
-    <row r="112">
-      <c r="H112" s="24"/>
-    </row>
-    <row r="113">
-      <c r="H113" s="24"/>
-    </row>
-    <row r="114">
-      <c r="H114" s="24"/>
-    </row>
-    <row r="115">
-      <c r="H115" s="24"/>
-    </row>
-    <row r="116">
-      <c r="H116" s="24"/>
-    </row>
-    <row r="117">
-      <c r="H117" s="24"/>
-    </row>
-    <row r="118">
-      <c r="H118" s="24"/>
-    </row>
-    <row r="119">
-      <c r="H119" s="24"/>
-    </row>
-    <row r="120">
-      <c r="H120" s="24"/>
-    </row>
-    <row r="121">
-      <c r="H121" s="24"/>
-    </row>
-    <row r="122">
-      <c r="H122" s="24"/>
-    </row>
-    <row r="123">
-      <c r="H123" s="24"/>
-    </row>
-    <row r="124">
-      <c r="H124" s="24"/>
-    </row>
-    <row r="125">
-      <c r="H125" s="24"/>
-    </row>
-    <row r="126">
-      <c r="H126" s="24"/>
-    </row>
-    <row r="127">
-      <c r="H127" s="24"/>
-    </row>
-    <row r="128">
-      <c r="H128" s="24"/>
-    </row>
-    <row r="129">
-      <c r="H129" s="24"/>
-    </row>
-    <row r="130">
-      <c r="H130" s="24"/>
-    </row>
-    <row r="131">
-      <c r="H131" s="24"/>
-    </row>
-    <row r="132">
-      <c r="H132" s="24"/>
-    </row>
-    <row r="133">
-      <c r="H133" s="24"/>
-    </row>
-    <row r="134">
-      <c r="H134" s="24"/>
-    </row>
-    <row r="135">
-      <c r="H135" s="24"/>
-    </row>
-    <row r="136">
-      <c r="H136" s="24"/>
-    </row>
-    <row r="137">
-      <c r="H137" s="24"/>
-    </row>
-    <row r="138">
-      <c r="H138" s="24"/>
-    </row>
-    <row r="139">
-      <c r="H139" s="24"/>
-    </row>
-    <row r="140">
-      <c r="H140" s="24"/>
-    </row>
-    <row r="141">
-      <c r="H141" s="24"/>
-    </row>
-    <row r="142">
-      <c r="H142" s="24"/>
-    </row>
-    <row r="143">
-      <c r="H143" s="24"/>
-    </row>
-    <row r="144">
-      <c r="H144" s="24"/>
-    </row>
-    <row r="145">
-      <c r="H145" s="24"/>
-    </row>
-    <row r="146">
-      <c r="H146" s="24"/>
-    </row>
-    <row r="147">
-      <c r="H147" s="24"/>
-    </row>
-    <row r="148">
-      <c r="H148" s="24"/>
-    </row>
-    <row r="149">
-      <c r="H149" s="24"/>
-    </row>
-    <row r="150">
-      <c r="H150" s="24"/>
-    </row>
-    <row r="151">
-      <c r="H151" s="24"/>
-    </row>
-    <row r="152">
-      <c r="H152" s="24"/>
-    </row>
-    <row r="153">
-      <c r="H153" s="24"/>
-    </row>
-    <row r="154">
-      <c r="H154" s="24"/>
-    </row>
-    <row r="155">
-      <c r="H155" s="24"/>
-    </row>
-    <row r="156">
-      <c r="H156" s="24"/>
-    </row>
-    <row r="157">
-      <c r="H157" s="24"/>
-    </row>
-    <row r="158">
-      <c r="H158" s="24"/>
-    </row>
-    <row r="159">
-      <c r="H159" s="24"/>
-    </row>
-    <row r="160">
-      <c r="H160" s="24"/>
-    </row>
-    <row r="161">
-      <c r="H161" s="24"/>
-    </row>
-    <row r="162">
-      <c r="H162" s="24"/>
-    </row>
-    <row r="163">
-      <c r="H163" s="24"/>
-    </row>
-    <row r="164">
-      <c r="H164" s="24"/>
-    </row>
-    <row r="165">
-      <c r="H165" s="24"/>
-    </row>
-    <row r="166">
-      <c r="H166" s="24"/>
-    </row>
-    <row r="167">
-      <c r="H167" s="24"/>
-    </row>
-    <row r="168">
-      <c r="H168" s="24"/>
-    </row>
-    <row r="169">
-      <c r="H169" s="24"/>
-    </row>
-    <row r="170">
-      <c r="H170" s="24"/>
-    </row>
-    <row r="171">
-      <c r="H171" s="24"/>
-    </row>
-    <row r="172">
-      <c r="H172" s="24"/>
-    </row>
-    <row r="173">
-      <c r="H173" s="24"/>
-    </row>
-    <row r="174">
-      <c r="H174" s="24"/>
-    </row>
-    <row r="175">
-      <c r="H175" s="24"/>
-    </row>
-    <row r="176">
-      <c r="H176" s="24"/>
-    </row>
-    <row r="177">
-      <c r="H177" s="24"/>
-    </row>
-    <row r="178">
-      <c r="H178" s="24"/>
-    </row>
-    <row r="179">
-      <c r="H179" s="24"/>
-    </row>
-    <row r="180">
-      <c r="H180" s="24"/>
-    </row>
-    <row r="181">
-      <c r="H181" s="24"/>
-    </row>
-    <row r="182">
-      <c r="H182" s="24"/>
-    </row>
-    <row r="183">
-      <c r="H183" s="24"/>
-    </row>
-    <row r="184">
-      <c r="H184" s="24"/>
-    </row>
-    <row r="185">
-      <c r="H185" s="24"/>
-    </row>
-    <row r="186">
-      <c r="H186" s="24"/>
-    </row>
-    <row r="187">
-      <c r="H187" s="24"/>
-    </row>
-    <row r="188">
-      <c r="H188" s="24"/>
-    </row>
-    <row r="189">
-      <c r="H189" s="24"/>
-    </row>
-    <row r="190">
-      <c r="H190" s="24"/>
-    </row>
-    <row r="191">
-      <c r="H191" s="24"/>
-    </row>
-    <row r="192">
-      <c r="H192" s="24"/>
-    </row>
-    <row r="193">
-      <c r="H193" s="24"/>
-    </row>
-    <row r="194">
-      <c r="H194" s="24"/>
-    </row>
-    <row r="195">
-      <c r="H195" s="24"/>
-    </row>
-    <row r="196">
-      <c r="H196" s="24"/>
-    </row>
-    <row r="197">
-      <c r="H197" s="24"/>
-    </row>
-    <row r="198">
-      <c r="H198" s="24"/>
-    </row>
-    <row r="199">
-      <c r="H199" s="24"/>
-    </row>
-    <row r="200">
-      <c r="H200" s="24"/>
-    </row>
-    <row r="201">
-      <c r="H201" s="24"/>
-    </row>
-    <row r="202">
-      <c r="H202" s="24"/>
-    </row>
-    <row r="203">
-      <c r="H203" s="24"/>
-    </row>
-    <row r="204">
-      <c r="H204" s="24"/>
-    </row>
-    <row r="205">
-      <c r="H205" s="24"/>
-    </row>
-    <row r="206">
-      <c r="H206" s="24"/>
-    </row>
-    <row r="207">
-      <c r="H207" s="24"/>
-    </row>
-    <row r="208">
-      <c r="H208" s="24"/>
-    </row>
-    <row r="209">
-      <c r="H209" s="24"/>
-    </row>
-    <row r="210">
-      <c r="H210" s="24"/>
-    </row>
-    <row r="211">
-      <c r="H211" s="24"/>
-    </row>
-    <row r="212">
-      <c r="H212" s="24"/>
-    </row>
-    <row r="213">
-      <c r="H213" s="24"/>
-    </row>
-    <row r="214">
-      <c r="H214" s="24"/>
-    </row>
-    <row r="215">
-      <c r="H215" s="24"/>
-    </row>
-    <row r="216">
-      <c r="H216" s="24"/>
-    </row>
-    <row r="217">
-      <c r="H217" s="24"/>
-    </row>
-    <row r="218">
-      <c r="H218" s="24"/>
-    </row>
-    <row r="219">
-      <c r="H219" s="24"/>
-    </row>
-    <row r="220">
-      <c r="H220" s="24"/>
-    </row>
-    <row r="221">
-      <c r="H221" s="24"/>
-    </row>
-    <row r="222">
-      <c r="H222" s="24"/>
-    </row>
-    <row r="223">
-      <c r="H223" s="24"/>
-    </row>
-    <row r="224">
-      <c r="H224" s="24"/>
-    </row>
-    <row r="225">
-      <c r="H225" s="24"/>
-    </row>
-    <row r="226">
-      <c r="H226" s="24"/>
-    </row>
-    <row r="227">
-      <c r="H227" s="24"/>
-    </row>
-    <row r="228">
-      <c r="H228" s="24"/>
-    </row>
-    <row r="229">
-      <c r="H229" s="24"/>
-    </row>
-    <row r="230">
-      <c r="H230" s="24"/>
-    </row>
-    <row r="231">
-      <c r="H231" s="24"/>
-    </row>
-    <row r="232">
-      <c r="H232" s="24"/>
-    </row>
-    <row r="233">
-      <c r="H233" s="24"/>
-    </row>
-    <row r="234">
-      <c r="H234" s="24"/>
-    </row>
-    <row r="235">
-      <c r="H235" s="24"/>
-    </row>
-    <row r="236">
-      <c r="H236" s="24"/>
-    </row>
-    <row r="237">
-      <c r="H237" s="24"/>
-    </row>
-    <row r="238">
-      <c r="H238" s="24"/>
-    </row>
-    <row r="239">
-      <c r="H239" s="24"/>
-    </row>
-    <row r="240">
-      <c r="H240" s="24"/>
-    </row>
-    <row r="241">
-      <c r="H241" s="24"/>
-    </row>
-    <row r="242">
-      <c r="H242" s="24"/>
-    </row>
-    <row r="243">
-      <c r="H243" s="24"/>
-    </row>
-    <row r="244">
-      <c r="H244" s="24"/>
-    </row>
-    <row r="245">
-      <c r="H245" s="24"/>
-    </row>
-    <row r="246">
-      <c r="H246" s="24"/>
-    </row>
-    <row r="247">
-      <c r="H247" s="24"/>
-    </row>
-    <row r="248">
-      <c r="H248" s="24"/>
-    </row>
-    <row r="249">
-      <c r="H249" s="24"/>
-    </row>
-    <row r="250">
-      <c r="H250" s="24"/>
-    </row>
-    <row r="251">
-      <c r="H251" s="24"/>
-    </row>
-    <row r="252">
-      <c r="H252" s="24"/>
-    </row>
-    <row r="253">
-      <c r="H253" s="24"/>
-    </row>
-    <row r="254">
-      <c r="H254" s="24"/>
-    </row>
-    <row r="255">
-      <c r="H255" s="24"/>
-    </row>
-    <row r="256">
-      <c r="H256" s="24"/>
-    </row>
-    <row r="257">
-      <c r="H257" s="24"/>
-    </row>
-    <row r="258">
-      <c r="H258" s="24"/>
-    </row>
-    <row r="259">
-      <c r="H259" s="24"/>
-    </row>
-    <row r="260">
-      <c r="H260" s="24"/>
-    </row>
-    <row r="261">
-      <c r="H261" s="24"/>
-    </row>
-    <row r="262">
-      <c r="H262" s="24"/>
-    </row>
-    <row r="263">
-      <c r="H263" s="24"/>
-    </row>
-    <row r="264">
-      <c r="H264" s="24"/>
-    </row>
-    <row r="265">
-      <c r="H265" s="24"/>
-    </row>
-    <row r="266">
-      <c r="H266" s="24"/>
-    </row>
-    <row r="267">
-      <c r="H267" s="24"/>
-    </row>
-    <row r="268">
-      <c r="H268" s="24"/>
-    </row>
-    <row r="269">
-      <c r="H269" s="24"/>
-    </row>
-    <row r="270">
-      <c r="H270" s="24"/>
-    </row>
-    <row r="271">
-      <c r="H271" s="24"/>
-    </row>
-    <row r="272">
-      <c r="H272" s="24"/>
-    </row>
-    <row r="273">
-      <c r="H273" s="24"/>
-    </row>
-    <row r="274">
-      <c r="H274" s="24"/>
-    </row>
-    <row r="275">
-      <c r="H275" s="24"/>
-    </row>
-    <row r="276">
-      <c r="H276" s="24"/>
-    </row>
-    <row r="277">
-      <c r="H277" s="24"/>
-    </row>
-    <row r="278">
-      <c r="H278" s="24"/>
-    </row>
-    <row r="279">
-      <c r="H279" s="24"/>
-    </row>
-    <row r="280">
-      <c r="H280" s="24"/>
-    </row>
-    <row r="281">
-      <c r="H281" s="24"/>
-    </row>
-    <row r="282">
-      <c r="H282" s="24"/>
-    </row>
-    <row r="283">
-      <c r="H283" s="24"/>
-    </row>
-    <row r="284">
-      <c r="H284" s="24"/>
-    </row>
-    <row r="285">
-      <c r="H285" s="24"/>
-    </row>
-    <row r="286">
-      <c r="H286" s="24"/>
-    </row>
-    <row r="287">
-      <c r="H287" s="24"/>
-    </row>
-    <row r="288">
-      <c r="H288" s="24"/>
-    </row>
-    <row r="289">
-      <c r="H289" s="24"/>
-    </row>
-    <row r="290">
-      <c r="H290" s="24"/>
-    </row>
-    <row r="291">
-      <c r="H291" s="24"/>
-    </row>
-    <row r="292">
-      <c r="H292" s="24"/>
-    </row>
-    <row r="293">
-      <c r="H293" s="24"/>
-    </row>
-    <row r="294">
-      <c r="H294" s="24"/>
-    </row>
-    <row r="295">
-      <c r="H295" s="24"/>
-    </row>
-    <row r="296">
-      <c r="H296" s="24"/>
-    </row>
-    <row r="297">
-      <c r="H297" s="24"/>
-    </row>
-    <row r="298">
-      <c r="H298" s="24"/>
-    </row>
-    <row r="299">
-      <c r="H299" s="24"/>
-    </row>
-    <row r="300">
-      <c r="H300" s="24"/>
-    </row>
-    <row r="301">
-      <c r="H301" s="24"/>
-    </row>
-    <row r="302">
-      <c r="H302" s="24"/>
-    </row>
-    <row r="303">
-      <c r="H303" s="24"/>
-    </row>
-    <row r="304">
-      <c r="H304" s="24"/>
-    </row>
-    <row r="305">
-      <c r="H305" s="24"/>
-    </row>
-    <row r="306">
-      <c r="H306" s="24"/>
-    </row>
-    <row r="307">
-      <c r="H307" s="24"/>
-    </row>
-    <row r="308">
-      <c r="H308" s="24"/>
-    </row>
-    <row r="309">
-      <c r="H309" s="24"/>
-    </row>
-    <row r="310">
-      <c r="H310" s="24"/>
-    </row>
-    <row r="311">
-      <c r="H311" s="24"/>
-    </row>
-    <row r="312">
-      <c r="H312" s="24"/>
-    </row>
-    <row r="313">
-      <c r="H313" s="24"/>
-    </row>
-    <row r="314">
-      <c r="H314" s="24"/>
-    </row>
-    <row r="315">
-      <c r="H315" s="24"/>
-    </row>
-    <row r="316">
-      <c r="H316" s="24"/>
-    </row>
-    <row r="317">
-      <c r="H317" s="24"/>
-    </row>
-    <row r="318">
-      <c r="H318" s="24"/>
-    </row>
-    <row r="319">
-      <c r="H319" s="24"/>
-    </row>
-    <row r="320">
-      <c r="H320" s="24"/>
-    </row>
-    <row r="321">
-      <c r="H321" s="24"/>
-    </row>
-    <row r="322">
-      <c r="H322" s="24"/>
-    </row>
-    <row r="323">
-      <c r="H323" s="24"/>
-    </row>
-    <row r="324">
-      <c r="H324" s="24"/>
-    </row>
-    <row r="325">
-      <c r="H325" s="24"/>
-    </row>
-    <row r="326">
-      <c r="H326" s="24"/>
-    </row>
-    <row r="327">
-      <c r="H327" s="24"/>
-    </row>
-    <row r="328">
-      <c r="H328" s="24"/>
-    </row>
-    <row r="329">
-      <c r="H329" s="24"/>
-    </row>
-    <row r="330">
-      <c r="H330" s="24"/>
-    </row>
-    <row r="331">
-      <c r="H331" s="24"/>
-    </row>
-    <row r="332">
-      <c r="H332" s="24"/>
-    </row>
-    <row r="333">
-      <c r="H333" s="24"/>
-    </row>
-    <row r="334">
-      <c r="H334" s="24"/>
-    </row>
-    <row r="335">
-      <c r="H335" s="24"/>
-    </row>
-    <row r="336">
-      <c r="H336" s="24"/>
-    </row>
-    <row r="337">
-      <c r="H337" s="24"/>
-    </row>
-    <row r="338">
-      <c r="H338" s="24"/>
-    </row>
-    <row r="339">
-      <c r="H339" s="24"/>
-    </row>
-    <row r="340">
-      <c r="H340" s="24"/>
-    </row>
-    <row r="341">
-      <c r="H341" s="24"/>
-    </row>
-    <row r="342">
-      <c r="H342" s="24"/>
-    </row>
-    <row r="343">
-      <c r="H343" s="24"/>
-    </row>
-    <row r="344">
-      <c r="H344" s="24"/>
-    </row>
-    <row r="345">
-      <c r="H345" s="24"/>
-    </row>
-    <row r="346">
-      <c r="H346" s="24"/>
-    </row>
-    <row r="347">
-      <c r="H347" s="24"/>
-    </row>
-    <row r="348">
-      <c r="H348" s="24"/>
-    </row>
-    <row r="349">
-      <c r="H349" s="24"/>
-    </row>
-    <row r="350">
-      <c r="H350" s="24"/>
-    </row>
-    <row r="351">
-      <c r="H351" s="24"/>
-    </row>
-    <row r="352">
-      <c r="H352" s="24"/>
-    </row>
-    <row r="353">
-      <c r="H353" s="24"/>
-    </row>
-    <row r="354">
-      <c r="H354" s="24"/>
-    </row>
-    <row r="355">
-      <c r="H355" s="24"/>
-    </row>
-    <row r="356">
-      <c r="H356" s="24"/>
-    </row>
-    <row r="357">
-      <c r="H357" s="24"/>
-    </row>
-    <row r="358">
-      <c r="H358" s="24"/>
-    </row>
-    <row r="359">
-      <c r="H359" s="24"/>
-    </row>
-    <row r="360">
-      <c r="H360" s="24"/>
-    </row>
-    <row r="361">
-      <c r="H361" s="24"/>
-    </row>
-    <row r="362">
-      <c r="H362" s="24"/>
-    </row>
-    <row r="363">
-      <c r="H363" s="24"/>
-    </row>
-    <row r="364">
-      <c r="H364" s="24"/>
-    </row>
-    <row r="365">
-      <c r="H365" s="24"/>
-    </row>
-    <row r="366">
-      <c r="H366" s="24"/>
-    </row>
-    <row r="367">
-      <c r="H367" s="24"/>
-    </row>
-    <row r="368">
-      <c r="H368" s="24"/>
-    </row>
-    <row r="369">
-      <c r="H369" s="24"/>
-    </row>
-    <row r="370">
-      <c r="H370" s="24"/>
-    </row>
-    <row r="371">
-      <c r="H371" s="24"/>
-    </row>
-    <row r="372">
-      <c r="H372" s="24"/>
-    </row>
-    <row r="373">
-      <c r="H373" s="24"/>
-    </row>
-    <row r="374">
-      <c r="H374" s="24"/>
-    </row>
-    <row r="375">
-      <c r="H375" s="24"/>
-    </row>
-    <row r="376">
-      <c r="H376" s="24"/>
-    </row>
-    <row r="377">
-      <c r="H377" s="24"/>
-    </row>
-    <row r="378">
-      <c r="H378" s="24"/>
-    </row>
-    <row r="379">
-      <c r="H379" s="24"/>
-    </row>
-    <row r="380">
-      <c r="H380" s="24"/>
-    </row>
-    <row r="381">
-      <c r="H381" s="24"/>
-    </row>
-    <row r="382">
-      <c r="H382" s="24"/>
-    </row>
-    <row r="383">
-      <c r="H383" s="24"/>
-    </row>
-    <row r="384">
-      <c r="H384" s="24"/>
-    </row>
-    <row r="385">
-      <c r="H385" s="24"/>
-    </row>
-    <row r="386">
-      <c r="H386" s="24"/>
-    </row>
-    <row r="387">
-      <c r="H387" s="24"/>
-    </row>
-    <row r="388">
-      <c r="H388" s="24"/>
-    </row>
-    <row r="389">
-      <c r="H389" s="24"/>
-    </row>
-    <row r="390">
-      <c r="H390" s="24"/>
-    </row>
-    <row r="391">
-      <c r="H391" s="24"/>
-    </row>
-    <row r="392">
-      <c r="H392" s="24"/>
-    </row>
-    <row r="393">
-      <c r="H393" s="24"/>
-    </row>
-    <row r="394">
-      <c r="H394" s="24"/>
-    </row>
-    <row r="395">
-      <c r="H395" s="24"/>
-    </row>
-    <row r="396">
-      <c r="H396" s="24"/>
-    </row>
-    <row r="397">
-      <c r="H397" s="24"/>
-    </row>
-    <row r="398">
-      <c r="H398" s="24"/>
-    </row>
-    <row r="399">
-      <c r="H399" s="24"/>
-    </row>
-    <row r="400">
-      <c r="H400" s="24"/>
-    </row>
-    <row r="401">
-      <c r="H401" s="24"/>
-    </row>
-    <row r="402">
-      <c r="H402" s="24"/>
-    </row>
-    <row r="403">
-      <c r="H403" s="24"/>
-    </row>
-    <row r="404">
-      <c r="H404" s="24"/>
-    </row>
-    <row r="405">
-      <c r="H405" s="24"/>
-    </row>
-    <row r="406">
-      <c r="H406" s="24"/>
-    </row>
-    <row r="407">
-      <c r="H407" s="24"/>
-    </row>
-    <row r="408">
-      <c r="H408" s="24"/>
-    </row>
-    <row r="409">
-      <c r="H409" s="24"/>
-    </row>
-    <row r="410">
-      <c r="H410" s="24"/>
-    </row>
-    <row r="411">
-      <c r="H411" s="24"/>
-    </row>
-    <row r="412">
-      <c r="H412" s="24"/>
-    </row>
-    <row r="413">
-      <c r="H413" s="24"/>
-    </row>
-    <row r="414">
-      <c r="H414" s="24"/>
-    </row>
-    <row r="415">
-      <c r="H415" s="24"/>
-    </row>
-    <row r="416">
-      <c r="H416" s="24"/>
-    </row>
-    <row r="417">
-      <c r="H417" s="24"/>
-    </row>
-    <row r="418">
-      <c r="H418" s="24"/>
-    </row>
-    <row r="419">
-      <c r="H419" s="24"/>
-    </row>
-    <row r="420">
-      <c r="H420" s="24"/>
-    </row>
-    <row r="421">
-      <c r="H421" s="24"/>
-    </row>
-    <row r="422">
-      <c r="H422" s="24"/>
-    </row>
-    <row r="423">
-      <c r="H423" s="24"/>
-    </row>
-    <row r="424">
-      <c r="H424" s="24"/>
-    </row>
-    <row r="425">
-      <c r="H425" s="24"/>
-    </row>
-    <row r="426">
-      <c r="H426" s="24"/>
-    </row>
-    <row r="427">
-      <c r="H427" s="24"/>
-    </row>
-    <row r="428">
-      <c r="H428" s="24"/>
-    </row>
-    <row r="429">
-      <c r="H429" s="24"/>
-    </row>
-    <row r="430">
-      <c r="H430" s="24"/>
-    </row>
-    <row r="431">
-      <c r="H431" s="24"/>
-    </row>
-    <row r="432">
-      <c r="H432" s="24"/>
-    </row>
-    <row r="433">
-      <c r="H433" s="24"/>
-    </row>
-    <row r="434">
-      <c r="H434" s="24"/>
-    </row>
-    <row r="435">
-      <c r="H435" s="24"/>
-    </row>
-    <row r="436">
-      <c r="H436" s="24"/>
-    </row>
-    <row r="437">
-      <c r="H437" s="24"/>
-    </row>
-    <row r="438">
-      <c r="H438" s="24"/>
-    </row>
-    <row r="439">
-      <c r="H439" s="24"/>
-    </row>
-    <row r="440">
-      <c r="H440" s="24"/>
-    </row>
-    <row r="441">
-      <c r="H441" s="24"/>
-    </row>
-    <row r="442">
-      <c r="H442" s="24"/>
-    </row>
-    <row r="443">
-      <c r="H443" s="24"/>
-    </row>
-    <row r="444">
-      <c r="H444" s="24"/>
-    </row>
-    <row r="445">
-      <c r="H445" s="24"/>
-    </row>
-    <row r="446">
-      <c r="H446" s="24"/>
-    </row>
-    <row r="447">
-      <c r="H447" s="24"/>
-    </row>
-    <row r="448">
-      <c r="H448" s="24"/>
-    </row>
-    <row r="449">
-      <c r="H449" s="24"/>
-    </row>
-    <row r="450">
-      <c r="H450" s="24"/>
-    </row>
-    <row r="451">
-      <c r="H451" s="24"/>
-    </row>
-    <row r="452">
-      <c r="H452" s="24"/>
-    </row>
-    <row r="453">
-      <c r="H453" s="24"/>
-    </row>
-    <row r="454">
-      <c r="H454" s="24"/>
-    </row>
-    <row r="455">
-      <c r="H455" s="24"/>
-    </row>
-    <row r="456">
-      <c r="H456" s="24"/>
-    </row>
-    <row r="457">
-      <c r="H457" s="24"/>
-    </row>
-    <row r="458">
-      <c r="H458" s="24"/>
-    </row>
-    <row r="459">
-      <c r="H459" s="24"/>
-    </row>
-    <row r="460">
-      <c r="H460" s="24"/>
-    </row>
-    <row r="461">
-      <c r="H461" s="24"/>
-    </row>
-    <row r="462">
-      <c r="H462" s="24"/>
-    </row>
-    <row r="463">
-      <c r="H463" s="24"/>
-    </row>
-    <row r="464">
-      <c r="H464" s="24"/>
-    </row>
-    <row r="465">
-      <c r="H465" s="24"/>
-    </row>
-    <row r="466">
-      <c r="H466" s="24"/>
-    </row>
-    <row r="467">
-      <c r="H467" s="24"/>
-    </row>
-    <row r="468">
-      <c r="H468" s="24"/>
-    </row>
-    <row r="469">
-      <c r="H469" s="24"/>
-    </row>
-    <row r="470">
-      <c r="H470" s="24"/>
-    </row>
-    <row r="471">
-      <c r="H471" s="24"/>
-    </row>
-    <row r="472">
-      <c r="H472" s="24"/>
-    </row>
-    <row r="473">
-      <c r="H473" s="24"/>
-    </row>
-    <row r="474">
-      <c r="H474" s="24"/>
-    </row>
-    <row r="475">
-      <c r="H475" s="24"/>
-    </row>
-    <row r="476">
-      <c r="H476" s="24"/>
-    </row>
-    <row r="477">
-      <c r="H477" s="24"/>
-    </row>
-    <row r="478">
-      <c r="H478" s="24"/>
-    </row>
-    <row r="479">
-      <c r="H479" s="24"/>
-    </row>
-    <row r="480">
-      <c r="H480" s="24"/>
-    </row>
-    <row r="481">
-      <c r="H481" s="24"/>
-    </row>
-    <row r="482">
-      <c r="H482" s="24"/>
-    </row>
-    <row r="483">
-      <c r="H483" s="24"/>
-    </row>
-    <row r="484">
-      <c r="H484" s="24"/>
-    </row>
-    <row r="485">
-      <c r="H485" s="24"/>
-    </row>
-    <row r="486">
-      <c r="H486" s="24"/>
-    </row>
-    <row r="487">
-      <c r="H487" s="24"/>
-    </row>
-    <row r="488">
-      <c r="H488" s="24"/>
-    </row>
-    <row r="489">
-      <c r="H489" s="24"/>
-    </row>
-    <row r="490">
-      <c r="H490" s="24"/>
-    </row>
-    <row r="491">
-      <c r="H491" s="24"/>
-    </row>
-    <row r="492">
-      <c r="H492" s="24"/>
-    </row>
-    <row r="493">
-      <c r="H493" s="24"/>
-    </row>
-    <row r="494">
-      <c r="H494" s="24"/>
-    </row>
-    <row r="495">
-      <c r="H495" s="24"/>
-    </row>
-    <row r="496">
-      <c r="H496" s="24"/>
-    </row>
-    <row r="497">
-      <c r="H497" s="24"/>
-    </row>
-    <row r="498">
-      <c r="H498" s="24"/>
-    </row>
-    <row r="499">
-      <c r="H499" s="24"/>
-    </row>
-    <row r="500">
-      <c r="H500" s="24"/>
-    </row>
-    <row r="501">
-      <c r="H501" s="24"/>
-    </row>
-    <row r="502">
-      <c r="H502" s="24"/>
-    </row>
-    <row r="503">
-      <c r="H503" s="24"/>
-    </row>
-    <row r="504">
-      <c r="H504" s="24"/>
-    </row>
-    <row r="505">
-      <c r="H505" s="24"/>
-    </row>
-    <row r="506">
-      <c r="H506" s="24"/>
-    </row>
-    <row r="507">
-      <c r="H507" s="24"/>
-    </row>
-    <row r="508">
-      <c r="H508" s="24"/>
-    </row>
-    <row r="509">
-      <c r="H509" s="24"/>
-    </row>
-    <row r="510">
-      <c r="H510" s="24"/>
-    </row>
-    <row r="511">
-      <c r="H511" s="24"/>
-    </row>
-    <row r="512">
-      <c r="H512" s="24"/>
-    </row>
-    <row r="513">
-      <c r="H513" s="24"/>
-    </row>
-    <row r="514">
-      <c r="H514" s="24"/>
-    </row>
-    <row r="515">
-      <c r="H515" s="24"/>
-    </row>
-    <row r="516">
-      <c r="H516" s="24"/>
-    </row>
-    <row r="517">
-      <c r="H517" s="24"/>
-    </row>
-    <row r="518">
-      <c r="H518" s="24"/>
-    </row>
-    <row r="519">
-      <c r="H519" s="24"/>
-    </row>
-    <row r="520">
-      <c r="H520" s="24"/>
-    </row>
-    <row r="521">
-      <c r="H521" s="24"/>
-    </row>
-    <row r="522">
-      <c r="H522" s="24"/>
-    </row>
-    <row r="523">
-      <c r="H523" s="24"/>
-    </row>
-    <row r="524">
-      <c r="H524" s="24"/>
-    </row>
-    <row r="525">
-      <c r="H525" s="24"/>
-    </row>
-    <row r="526">
-      <c r="H526" s="24"/>
-    </row>
-    <row r="527">
-      <c r="H527" s="24"/>
-    </row>
-    <row r="528">
-      <c r="H528" s="24"/>
-    </row>
-    <row r="529">
-      <c r="H529" s="24"/>
-    </row>
-    <row r="530">
-      <c r="H530" s="24"/>
-    </row>
-    <row r="531">
-      <c r="H531" s="24"/>
-    </row>
-    <row r="532">
-      <c r="H532" s="24"/>
-    </row>
-    <row r="533">
-      <c r="H533" s="24"/>
-    </row>
-    <row r="534">
-      <c r="H534" s="24"/>
-    </row>
-    <row r="535">
-      <c r="H535" s="24"/>
-    </row>
-    <row r="536">
-      <c r="H536" s="24"/>
-    </row>
-    <row r="537">
-      <c r="H537" s="24"/>
-    </row>
-    <row r="538">
-      <c r="H538" s="24"/>
-    </row>
-    <row r="539">
-      <c r="H539" s="24"/>
-    </row>
-    <row r="540">
-      <c r="H540" s="24"/>
-    </row>
-    <row r="541">
-      <c r="H541" s="24"/>
-    </row>
-    <row r="542">
-      <c r="H542" s="24"/>
-    </row>
-    <row r="543">
-      <c r="H543" s="24"/>
-    </row>
-    <row r="544">
-      <c r="H544" s="24"/>
-    </row>
-    <row r="545">
-      <c r="H545" s="24"/>
-    </row>
-    <row r="546">
-      <c r="H546" s="24"/>
-    </row>
-    <row r="547">
-      <c r="H547" s="24"/>
-    </row>
-    <row r="548">
-      <c r="H548" s="24"/>
-    </row>
-    <row r="549">
-      <c r="H549" s="24"/>
-    </row>
-    <row r="550">
-      <c r="H550" s="24"/>
-    </row>
-    <row r="551">
-      <c r="H551" s="24"/>
-    </row>
-    <row r="552">
-      <c r="H552" s="24"/>
-    </row>
-    <row r="553">
-      <c r="H553" s="24"/>
-    </row>
-    <row r="554">
-      <c r="H554" s="24"/>
-    </row>
-    <row r="555">
-      <c r="H555" s="24"/>
-    </row>
-    <row r="556">
-      <c r="H556" s="24"/>
-    </row>
-    <row r="557">
-      <c r="H557" s="24"/>
-    </row>
-    <row r="558">
-      <c r="H558" s="24"/>
-    </row>
-    <row r="559">
-      <c r="H559" s="24"/>
-    </row>
-    <row r="560">
-      <c r="H560" s="24"/>
-    </row>
-    <row r="561">
-      <c r="H561" s="24"/>
-    </row>
-    <row r="562">
-      <c r="H562" s="24"/>
-    </row>
-    <row r="563">
-      <c r="H563" s="24"/>
-    </row>
-    <row r="564">
-      <c r="H564" s="24"/>
-    </row>
-    <row r="565">
-      <c r="H565" s="24"/>
-    </row>
-    <row r="566">
-      <c r="H566" s="24"/>
-    </row>
-    <row r="567">
-      <c r="H567" s="24"/>
-    </row>
-    <row r="568">
-      <c r="H568" s="24"/>
-    </row>
-    <row r="569">
-      <c r="H569" s="24"/>
-    </row>
-    <row r="570">
-      <c r="H570" s="24"/>
-    </row>
-    <row r="571">
-      <c r="H571" s="24"/>
-    </row>
-    <row r="572">
-      <c r="H572" s="24"/>
-    </row>
-    <row r="573">
-      <c r="H573" s="24"/>
-    </row>
-    <row r="574">
-      <c r="H574" s="24"/>
-    </row>
-    <row r="575">
-      <c r="H575" s="24"/>
-    </row>
-    <row r="576">
-      <c r="H576" s="24"/>
-    </row>
-    <row r="577">
-      <c r="H577" s="24"/>
-    </row>
-    <row r="578">
-      <c r="H578" s="24"/>
-    </row>
-    <row r="579">
-      <c r="H579" s="24"/>
-    </row>
-    <row r="580">
-      <c r="H580" s="24"/>
-    </row>
-    <row r="581">
-      <c r="H581" s="24"/>
-    </row>
-    <row r="582">
-      <c r="H582" s="24"/>
-    </row>
-    <row r="583">
-      <c r="H583" s="24"/>
-    </row>
-    <row r="584">
-      <c r="H584" s="24"/>
-    </row>
-    <row r="585">
-      <c r="H585" s="24"/>
-    </row>
-    <row r="586">
-      <c r="H586" s="24"/>
-    </row>
-    <row r="587">
-      <c r="H587" s="24"/>
-    </row>
-    <row r="588">
-      <c r="H588" s="24"/>
-    </row>
-    <row r="589">
-      <c r="H589" s="24"/>
-    </row>
-    <row r="590">
-      <c r="H590" s="24"/>
-    </row>
-    <row r="591">
-      <c r="H591" s="24"/>
-    </row>
-    <row r="592">
-      <c r="H592" s="24"/>
-    </row>
-    <row r="593">
-      <c r="H593" s="24"/>
-    </row>
-    <row r="594">
-      <c r="H594" s="24"/>
-    </row>
-    <row r="595">
-      <c r="H595" s="24"/>
-    </row>
-    <row r="596">
-      <c r="H596" s="24"/>
-    </row>
-    <row r="597">
-      <c r="H597" s="24"/>
-    </row>
-    <row r="598">
-      <c r="H598" s="24"/>
-    </row>
-    <row r="599">
-      <c r="H599" s="24"/>
-    </row>
-    <row r="600">
-      <c r="H600" s="24"/>
-    </row>
-    <row r="601">
-      <c r="H601" s="24"/>
-    </row>
-    <row r="602">
-      <c r="H602" s="24"/>
-    </row>
-    <row r="603">
-      <c r="H603" s="24"/>
-    </row>
-    <row r="604">
-      <c r="H604" s="24"/>
-    </row>
-    <row r="605">
-      <c r="H605" s="24"/>
-    </row>
-    <row r="606">
-      <c r="H606" s="24"/>
-    </row>
-    <row r="607">
-      <c r="H607" s="24"/>
-    </row>
-    <row r="608">
-      <c r="H608" s="24"/>
-    </row>
-    <row r="609">
-      <c r="H609" s="24"/>
-    </row>
-    <row r="610">
-      <c r="H610" s="24"/>
-    </row>
-    <row r="611">
-      <c r="H611" s="24"/>
-    </row>
-    <row r="612">
-      <c r="H612" s="24"/>
-    </row>
-    <row r="613">
-      <c r="H613" s="24"/>
-    </row>
-    <row r="614">
-      <c r="H614" s="24"/>
-    </row>
-    <row r="615">
-      <c r="H615" s="24"/>
-    </row>
-    <row r="616">
-      <c r="H616" s="24"/>
-    </row>
-    <row r="617">
-      <c r="H617" s="24"/>
-    </row>
-    <row r="618">
-      <c r="H618" s="24"/>
-    </row>
-    <row r="619">
-      <c r="H619" s="24"/>
-    </row>
-    <row r="620">
-      <c r="H620" s="24"/>
-    </row>
-    <row r="621">
-      <c r="H621" s="24"/>
-    </row>
-    <row r="622">
-      <c r="H622" s="24"/>
-    </row>
-    <row r="623">
-      <c r="H623" s="24"/>
-    </row>
-    <row r="624">
-      <c r="H624" s="24"/>
-    </row>
-    <row r="625">
-      <c r="H625" s="24"/>
-    </row>
-    <row r="626">
-      <c r="H626" s="24"/>
-    </row>
-    <row r="627">
-      <c r="H627" s="24"/>
-    </row>
-    <row r="628">
-      <c r="H628" s="24"/>
-    </row>
-    <row r="629">
-      <c r="H629" s="24"/>
-    </row>
-    <row r="630">
-      <c r="H630" s="24"/>
-    </row>
-    <row r="631">
-      <c r="H631" s="24"/>
-    </row>
-    <row r="632">
-      <c r="H632" s="24"/>
-    </row>
-    <row r="633">
-      <c r="H633" s="24"/>
-    </row>
-    <row r="634">
-      <c r="H634" s="24"/>
-    </row>
-    <row r="635">
-      <c r="H635" s="24"/>
-    </row>
-    <row r="636">
-      <c r="H636" s="24"/>
-    </row>
-    <row r="637">
-      <c r="H637" s="24"/>
-    </row>
-    <row r="638">
-      <c r="H638" s="24"/>
-    </row>
-    <row r="639">
-      <c r="H639" s="24"/>
-    </row>
-    <row r="640">
-      <c r="H640" s="24"/>
-    </row>
-    <row r="641">
-      <c r="H641" s="24"/>
-    </row>
-    <row r="642">
-      <c r="H642" s="24"/>
-    </row>
-    <row r="643">
-      <c r="H643" s="24"/>
-    </row>
-    <row r="644">
-      <c r="H644" s="24"/>
-    </row>
-    <row r="645">
-      <c r="H645" s="24"/>
-    </row>
-    <row r="646">
-      <c r="H646" s="24"/>
-    </row>
-    <row r="647">
-      <c r="H647" s="24"/>
-    </row>
-    <row r="648">
-      <c r="H648" s="24"/>
-    </row>
-    <row r="649">
-      <c r="H649" s="24"/>
-    </row>
-    <row r="650">
-      <c r="H650" s="24"/>
-    </row>
-    <row r="651">
-      <c r="H651" s="24"/>
-    </row>
-    <row r="652">
-      <c r="H652" s="24"/>
-    </row>
-    <row r="653">
-      <c r="H653" s="24"/>
-    </row>
-    <row r="654">
-      <c r="H654" s="24"/>
-    </row>
-    <row r="655">
-      <c r="H655" s="24"/>
-    </row>
-    <row r="656">
-      <c r="H656" s="24"/>
-    </row>
-    <row r="657">
-      <c r="H657" s="24"/>
-    </row>
-    <row r="658">
-      <c r="H658" s="24"/>
-    </row>
-    <row r="659">
-      <c r="H659" s="24"/>
-    </row>
-    <row r="660">
-      <c r="H660" s="24"/>
-    </row>
-    <row r="661">
-      <c r="H661" s="24"/>
-    </row>
-    <row r="662">
-      <c r="H662" s="24"/>
-    </row>
-    <row r="663">
-      <c r="H663" s="24"/>
-    </row>
-    <row r="664">
-      <c r="H664" s="24"/>
-    </row>
-    <row r="665">
-      <c r="H665" s="24"/>
-    </row>
-    <row r="666">
-      <c r="H666" s="24"/>
-    </row>
-    <row r="667">
-      <c r="H667" s="24"/>
-    </row>
-    <row r="668">
-      <c r="H668" s="24"/>
-    </row>
-    <row r="669">
-      <c r="H669" s="24"/>
-    </row>
-    <row r="670">
-      <c r="H670" s="24"/>
-    </row>
-    <row r="671">
-      <c r="H671" s="24"/>
-    </row>
-    <row r="672">
-      <c r="H672" s="24"/>
-    </row>
-    <row r="673">
-      <c r="H673" s="24"/>
-    </row>
-    <row r="674">
-      <c r="H674" s="24"/>
-    </row>
-    <row r="675">
-      <c r="H675" s="24"/>
-    </row>
-    <row r="676">
-      <c r="H676" s="24"/>
-    </row>
-    <row r="677">
-      <c r="H677" s="24"/>
-    </row>
-    <row r="678">
-      <c r="H678" s="24"/>
-    </row>
-    <row r="679">
-      <c r="H679" s="24"/>
-    </row>
-    <row r="680">
-      <c r="H680" s="24"/>
-    </row>
-    <row r="681">
-      <c r="H681" s="24"/>
-    </row>
-    <row r="682">
-      <c r="H682" s="24"/>
-    </row>
-    <row r="683">
-      <c r="H683" s="24"/>
-    </row>
-    <row r="684">
-      <c r="H684" s="24"/>
-    </row>
-    <row r="685">
-      <c r="H685" s="24"/>
-    </row>
-    <row r="686">
-      <c r="H686" s="24"/>
-    </row>
-    <row r="687">
-      <c r="H687" s="24"/>
-    </row>
-    <row r="688">
-      <c r="H688" s="24"/>
-    </row>
-    <row r="689">
-      <c r="H689" s="24"/>
-    </row>
-    <row r="690">
-      <c r="H690" s="24"/>
-    </row>
-    <row r="691">
-      <c r="H691" s="24"/>
-    </row>
-    <row r="692">
-      <c r="H692" s="24"/>
-    </row>
-    <row r="693">
-      <c r="H693" s="24"/>
-    </row>
-    <row r="694">
-      <c r="H694" s="24"/>
-    </row>
-    <row r="695">
-      <c r="H695" s="24"/>
-    </row>
-    <row r="696">
-      <c r="H696" s="24"/>
-    </row>
-    <row r="697">
-      <c r="H697" s="24"/>
-    </row>
-    <row r="698">
-      <c r="H698" s="24"/>
-    </row>
-    <row r="699">
-      <c r="H699" s="24"/>
-    </row>
-    <row r="700">
-      <c r="H700" s="24"/>
-    </row>
-    <row r="701">
-      <c r="H701" s="24"/>
-    </row>
-    <row r="702">
-      <c r="H702" s="24"/>
-    </row>
-    <row r="703">
-      <c r="H703" s="24"/>
-    </row>
-    <row r="704">
-      <c r="H704" s="24"/>
-    </row>
-    <row r="705">
-      <c r="H705" s="24"/>
-    </row>
-    <row r="706">
-      <c r="H706" s="24"/>
-    </row>
-    <row r="707">
-      <c r="H707" s="24"/>
-    </row>
-    <row r="708">
-      <c r="H708" s="24"/>
-    </row>
-    <row r="709">
-      <c r="H709" s="24"/>
-    </row>
-    <row r="710">
-      <c r="H710" s="24"/>
-    </row>
-    <row r="711">
-      <c r="H711" s="24"/>
-    </row>
-    <row r="712">
-      <c r="H712" s="24"/>
-    </row>
-    <row r="713">
-      <c r="H713" s="24"/>
-    </row>
-    <row r="714">
-      <c r="H714" s="24"/>
-    </row>
-    <row r="715">
-      <c r="H715" s="24"/>
-    </row>
-    <row r="716">
-      <c r="H716" s="24"/>
-    </row>
-    <row r="717">
-      <c r="H717" s="24"/>
-    </row>
-    <row r="718">
-      <c r="H718" s="24"/>
-    </row>
-    <row r="719">
-      <c r="H719" s="24"/>
-    </row>
-    <row r="720">
-      <c r="H720" s="24"/>
-    </row>
-    <row r="721">
-      <c r="H721" s="24"/>
-    </row>
-    <row r="722">
-      <c r="H722" s="24"/>
-    </row>
-    <row r="723">
-      <c r="H723" s="24"/>
-    </row>
-    <row r="724">
-      <c r="H724" s="24"/>
-    </row>
-    <row r="725">
-      <c r="H725" s="24"/>
-    </row>
-    <row r="726">
-      <c r="H726" s="24"/>
-    </row>
-    <row r="727">
-      <c r="H727" s="24"/>
-    </row>
-    <row r="728">
-      <c r="H728" s="24"/>
-    </row>
-    <row r="729">
-      <c r="H729" s="24"/>
-    </row>
-    <row r="730">
-      <c r="H730" s="24"/>
-    </row>
-    <row r="731">
-      <c r="H731" s="24"/>
-    </row>
-    <row r="732">
-      <c r="H732" s="24"/>
-    </row>
-    <row r="733">
-      <c r="H733" s="24"/>
-    </row>
-    <row r="734">
-      <c r="H734" s="24"/>
-    </row>
-    <row r="735">
-      <c r="H735" s="24"/>
-    </row>
-    <row r="736">
-      <c r="H736" s="24"/>
-    </row>
-    <row r="737">
-      <c r="H737" s="24"/>
-    </row>
-    <row r="738">
-      <c r="H738" s="24"/>
-    </row>
-    <row r="739">
-      <c r="H739" s="24"/>
-    </row>
-    <row r="740">
-      <c r="H740" s="24"/>
-    </row>
-    <row r="741">
-      <c r="H741" s="24"/>
-    </row>
-    <row r="742">
-      <c r="H742" s="24"/>
-    </row>
-    <row r="743">
-      <c r="H743" s="24"/>
-    </row>
-    <row r="744">
-      <c r="H744" s="24"/>
-    </row>
-    <row r="745">
-      <c r="H745" s="24"/>
-    </row>
-    <row r="746">
-      <c r="H746" s="24"/>
-    </row>
-    <row r="747">
-      <c r="H747" s="24"/>
-    </row>
-    <row r="748">
-      <c r="H748" s="24"/>
-    </row>
-    <row r="749">
-      <c r="H749" s="24"/>
-    </row>
-    <row r="750">
-      <c r="H750" s="24"/>
-    </row>
-    <row r="751">
-      <c r="H751" s="24"/>
-    </row>
-    <row r="752">
-      <c r="H752" s="24"/>
-    </row>
-    <row r="753">
-      <c r="H753" s="24"/>
-    </row>
-    <row r="754">
-      <c r="H754" s="24"/>
-    </row>
-    <row r="755">
-      <c r="H755" s="24"/>
-    </row>
-    <row r="756">
-      <c r="H756" s="24"/>
-    </row>
-    <row r="757">
-      <c r="H757" s="24"/>
-    </row>
-    <row r="758">
-      <c r="H758" s="24"/>
-    </row>
-    <row r="759">
-      <c r="H759" s="24"/>
-    </row>
-    <row r="760">
-      <c r="H760" s="24"/>
-    </row>
-    <row r="761">
-      <c r="H761" s="24"/>
-    </row>
-    <row r="762">
-      <c r="H762" s="24"/>
-    </row>
-    <row r="763">
-      <c r="H763" s="24"/>
-    </row>
-    <row r="764">
-      <c r="H764" s="24"/>
-    </row>
-    <row r="765">
-      <c r="H765" s="24"/>
-    </row>
-    <row r="766">
-      <c r="H766" s="24"/>
-    </row>
-    <row r="767">
-      <c r="H767" s="24"/>
-    </row>
-    <row r="768">
-      <c r="H768" s="24"/>
-    </row>
-    <row r="769">
-      <c r="H769" s="24"/>
-    </row>
-    <row r="770">
-      <c r="H770" s="24"/>
-    </row>
-    <row r="771">
-      <c r="H771" s="24"/>
-    </row>
-    <row r="772">
-      <c r="H772" s="24"/>
-    </row>
-    <row r="773">
-      <c r="H773" s="24"/>
-    </row>
-    <row r="774">
-      <c r="H774" s="24"/>
-    </row>
-    <row r="775">
-      <c r="H775" s="24"/>
-    </row>
-    <row r="776">
-      <c r="H776" s="24"/>
-    </row>
-    <row r="777">
-      <c r="H777" s="24"/>
-    </row>
-    <row r="778">
-      <c r="H778" s="24"/>
-    </row>
-    <row r="779">
-      <c r="H779" s="24"/>
-    </row>
-    <row r="780">
-      <c r="H780" s="24"/>
-    </row>
-    <row r="781">
-      <c r="H781" s="24"/>
-    </row>
-    <row r="782">
-      <c r="H782" s="24"/>
-    </row>
-    <row r="783">
-      <c r="H783" s="24"/>
-    </row>
-    <row r="784">
-      <c r="H784" s="24"/>
-    </row>
-    <row r="785">
-      <c r="H785" s="24"/>
-    </row>
-    <row r="786">
-      <c r="H786" s="24"/>
-    </row>
-    <row r="787">
-      <c r="H787" s="24"/>
-    </row>
-    <row r="788">
-      <c r="H788" s="24"/>
-    </row>
-    <row r="789">
-      <c r="H789" s="24"/>
-    </row>
-    <row r="790">
-      <c r="H790" s="24"/>
-    </row>
-    <row r="791">
-      <c r="H791" s="24"/>
-    </row>
-    <row r="792">
-      <c r="H792" s="24"/>
-    </row>
-    <row r="793">
-      <c r="H793" s="24"/>
-    </row>
-    <row r="794">
-      <c r="H794" s="24"/>
-    </row>
-    <row r="795">
-      <c r="H795" s="24"/>
-    </row>
-    <row r="796">
-      <c r="H796" s="24"/>
-    </row>
-    <row r="797">
-      <c r="H797" s="24"/>
-    </row>
-    <row r="798">
-      <c r="H798" s="24"/>
-    </row>
-    <row r="799">
-      <c r="H799" s="24"/>
-    </row>
-    <row r="800">
-      <c r="H800" s="24"/>
-    </row>
-    <row r="801">
-      <c r="H801" s="24"/>
-    </row>
-    <row r="802">
-      <c r="H802" s="24"/>
-    </row>
-    <row r="803">
-      <c r="H803" s="24"/>
-    </row>
-    <row r="804">
-      <c r="H804" s="24"/>
-    </row>
-    <row r="805">
-      <c r="H805" s="24"/>
-    </row>
-    <row r="806">
-      <c r="H806" s="24"/>
-    </row>
-    <row r="807">
-      <c r="H807" s="24"/>
-    </row>
-    <row r="808">
-      <c r="H808" s="24"/>
-    </row>
-    <row r="809">
-      <c r="H809" s="24"/>
-    </row>
-    <row r="810">
-      <c r="H810" s="24"/>
-    </row>
-    <row r="811">
-      <c r="H811" s="24"/>
-    </row>
-    <row r="812">
-      <c r="H812" s="24"/>
-    </row>
-    <row r="813">
-      <c r="H813" s="24"/>
-    </row>
-    <row r="814">
-      <c r="H814" s="24"/>
-    </row>
-    <row r="815">
-      <c r="H815" s="24"/>
-    </row>
-    <row r="816">
-      <c r="H816" s="24"/>
-    </row>
-    <row r="817">
-      <c r="H817" s="24"/>
-    </row>
-    <row r="818">
-      <c r="H818" s="24"/>
-    </row>
-    <row r="819">
-      <c r="H819" s="24"/>
-    </row>
-    <row r="820">
-      <c r="H820" s="24"/>
-    </row>
-    <row r="821">
-      <c r="H821" s="24"/>
-    </row>
-    <row r="822">
-      <c r="H822" s="24"/>
-    </row>
-    <row r="823">
-      <c r="H823" s="24"/>
-    </row>
-    <row r="824">
-      <c r="H824" s="24"/>
-    </row>
-    <row r="825">
-      <c r="H825" s="24"/>
-    </row>
-    <row r="826">
-      <c r="H826" s="24"/>
-    </row>
-    <row r="827">
-      <c r="H827" s="24"/>
-    </row>
-    <row r="828">
-      <c r="H828" s="24"/>
-    </row>
-    <row r="829">
-      <c r="H829" s="24"/>
-    </row>
-    <row r="830">
-      <c r="H830" s="24"/>
-    </row>
-    <row r="831">
-      <c r="H831" s="24"/>
-    </row>
-    <row r="832">
-      <c r="H832" s="24"/>
-    </row>
-    <row r="833">
-      <c r="H833" s="24"/>
-    </row>
-    <row r="834">
-      <c r="H834" s="24"/>
-    </row>
-    <row r="835">
-      <c r="H835" s="24"/>
-    </row>
-    <row r="836">
-      <c r="H836" s="24"/>
-    </row>
-    <row r="837">
-      <c r="H837" s="24"/>
-    </row>
-    <row r="838">
-      <c r="H838" s="24"/>
-    </row>
-    <row r="839">
-      <c r="H839" s="24"/>
-    </row>
-    <row r="840">
-      <c r="H840" s="24"/>
-    </row>
-    <row r="841">
-      <c r="H841" s="24"/>
-    </row>
-    <row r="842">
-      <c r="H842" s="24"/>
-    </row>
-    <row r="843">
-      <c r="H843" s="24"/>
-    </row>
-    <row r="844">
-      <c r="H844" s="24"/>
-    </row>
-    <row r="845">
-      <c r="H845" s="24"/>
-    </row>
-    <row r="846">
-      <c r="H846" s="24"/>
-    </row>
-    <row r="847">
-      <c r="H847" s="24"/>
-    </row>
-    <row r="848">
-      <c r="H848" s="24"/>
-    </row>
-    <row r="849">
-      <c r="H849" s="24"/>
-    </row>
-    <row r="850">
-      <c r="H850" s="24"/>
-    </row>
-    <row r="851">
-      <c r="H851" s="24"/>
-    </row>
-    <row r="852">
-      <c r="H852" s="24"/>
-    </row>
-    <row r="853">
-      <c r="H853" s="24"/>
-    </row>
-    <row r="854">
-      <c r="H854" s="24"/>
-    </row>
-    <row r="855">
-      <c r="H855" s="24"/>
-    </row>
-    <row r="856">
-      <c r="H856" s="24"/>
-    </row>
-    <row r="857">
-      <c r="H857" s="24"/>
-    </row>
-    <row r="858">
-      <c r="H858" s="24"/>
-    </row>
-    <row r="859">
-      <c r="H859" s="24"/>
-    </row>
-    <row r="860">
-      <c r="H860" s="24"/>
-    </row>
-    <row r="861">
-      <c r="H861" s="24"/>
-    </row>
-    <row r="862">
-      <c r="H862" s="24"/>
-    </row>
-    <row r="863">
-      <c r="H863" s="24"/>
-    </row>
-    <row r="864">
-      <c r="H864" s="24"/>
-    </row>
-    <row r="865">
-      <c r="H865" s="24"/>
-    </row>
-    <row r="866">
-      <c r="H866" s="24"/>
-    </row>
-    <row r="867">
-      <c r="H867" s="24"/>
-    </row>
-    <row r="868">
-      <c r="H868" s="24"/>
-    </row>
-    <row r="869">
-      <c r="H869" s="24"/>
-    </row>
-    <row r="870">
-      <c r="H870" s="24"/>
-    </row>
-    <row r="871">
-      <c r="H871" s="24"/>
-    </row>
-    <row r="872">
-      <c r="H872" s="24"/>
-    </row>
-    <row r="873">
-      <c r="H873" s="24"/>
-    </row>
-    <row r="874">
-      <c r="H874" s="24"/>
-    </row>
-    <row r="875">
-      <c r="H875" s="24"/>
-    </row>
-    <row r="876">
-      <c r="H876" s="24"/>
-    </row>
-    <row r="877">
-      <c r="H877" s="24"/>
-    </row>
-    <row r="878">
-      <c r="H878" s="24"/>
-    </row>
-    <row r="879">
-      <c r="H879" s="24"/>
-    </row>
-    <row r="880">
-      <c r="H880" s="24"/>
-    </row>
-    <row r="881">
-      <c r="H881" s="24"/>
-    </row>
-    <row r="882">
-      <c r="H882" s="24"/>
-    </row>
-    <row r="883">
-      <c r="H883" s="24"/>
-    </row>
-    <row r="884">
-      <c r="H884" s="24"/>
-    </row>
-    <row r="885">
-      <c r="H885" s="24"/>
-    </row>
-    <row r="886">
-      <c r="H886" s="24"/>
-    </row>
-    <row r="887">
-      <c r="H887" s="24"/>
-    </row>
-    <row r="888">
-      <c r="H888" s="24"/>
-    </row>
-    <row r="889">
-      <c r="H889" s="24"/>
-    </row>
-    <row r="890">
-      <c r="H890" s="24"/>
-    </row>
-    <row r="891">
-      <c r="H891" s="24"/>
-    </row>
-    <row r="892">
-      <c r="H892" s="24"/>
-    </row>
-    <row r="893">
-      <c r="H893" s="24"/>
-    </row>
-    <row r="894">
-      <c r="H894" s="24"/>
-    </row>
-    <row r="895">
-      <c r="H895" s="24"/>
-    </row>
-    <row r="896">
-      <c r="H896" s="24"/>
-    </row>
-    <row r="897">
-      <c r="H897" s="24"/>
-    </row>
-    <row r="898">
-      <c r="H898" s="24"/>
-    </row>
-    <row r="899">
-      <c r="H899" s="24"/>
-    </row>
-    <row r="900">
-      <c r="H900" s="24"/>
-    </row>
-    <row r="901">
-      <c r="H901" s="24"/>
-    </row>
-    <row r="902">
-      <c r="H902" s="24"/>
-    </row>
-    <row r="903">
-      <c r="H903" s="24"/>
-    </row>
-    <row r="904">
-      <c r="H904" s="24"/>
-    </row>
-    <row r="905">
-      <c r="H905" s="24"/>
-    </row>
-    <row r="906">
-      <c r="H906" s="24"/>
-    </row>
-    <row r="907">
-      <c r="H907" s="24"/>
-    </row>
-    <row r="908">
-      <c r="H908" s="24"/>
-    </row>
-    <row r="909">
-      <c r="H909" s="24"/>
-    </row>
-    <row r="910">
-      <c r="H910" s="24"/>
-    </row>
-    <row r="911">
-      <c r="H911" s="24"/>
-    </row>
-    <row r="912">
-      <c r="H912" s="24"/>
-    </row>
-    <row r="913">
-      <c r="H913" s="24"/>
-    </row>
-    <row r="914">
-      <c r="H914" s="24"/>
-    </row>
-    <row r="915">
-      <c r="H915" s="24"/>
-    </row>
-    <row r="916">
-      <c r="H916" s="24"/>
-    </row>
-    <row r="917">
-      <c r="H917" s="24"/>
-    </row>
-    <row r="918">
-      <c r="H918" s="24"/>
-    </row>
-    <row r="919">
-      <c r="H919" s="24"/>
-    </row>
-    <row r="920">
-      <c r="H920" s="24"/>
-    </row>
-    <row r="921">
-      <c r="H921" s="24"/>
-    </row>
-    <row r="922">
-      <c r="H922" s="24"/>
-    </row>
-    <row r="923">
-      <c r="H923" s="24"/>
-    </row>
-    <row r="924">
-      <c r="H924" s="24"/>
-    </row>
-    <row r="925">
-      <c r="H925" s="24"/>
-    </row>
-    <row r="926">
-      <c r="H926" s="24"/>
-    </row>
-    <row r="927">
-      <c r="H927" s="24"/>
-    </row>
-    <row r="928">
-      <c r="H928" s="24"/>
-    </row>
-    <row r="929">
-      <c r="H929" s="24"/>
-    </row>
-    <row r="930">
-      <c r="H930" s="24"/>
-    </row>
-    <row r="931">
-      <c r="H931" s="24"/>
-    </row>
-    <row r="932">
-      <c r="H932" s="24"/>
-    </row>
-    <row r="933">
-      <c r="H933" s="24"/>
-    </row>
-    <row r="934">
-      <c r="H934" s="24"/>
-    </row>
-    <row r="935">
-      <c r="H935" s="24"/>
-    </row>
-    <row r="936">
-      <c r="H936" s="24"/>
-    </row>
-    <row r="937">
-      <c r="H937" s="24"/>
-    </row>
-    <row r="938">
-      <c r="H938" s="24"/>
-    </row>
-    <row r="939">
-      <c r="H939" s="24"/>
-    </row>
-    <row r="940">
-      <c r="H940" s="24"/>
-    </row>
-    <row r="941">
-      <c r="H941" s="24"/>
-    </row>
-    <row r="942">
-      <c r="H942" s="24"/>
-    </row>
-    <row r="943">
-      <c r="H943" s="24"/>
-    </row>
-    <row r="944">
-      <c r="H944" s="24"/>
-    </row>
-    <row r="945">
-      <c r="H945" s="24"/>
-    </row>
-    <row r="946">
-      <c r="H946" s="24"/>
-    </row>
-    <row r="947">
-      <c r="H947" s="24"/>
-    </row>
-    <row r="948">
-      <c r="H948" s="24"/>
-    </row>
-    <row r="949">
-      <c r="H949" s="24"/>
-    </row>
-    <row r="950">
-      <c r="H950" s="24"/>
-    </row>
-    <row r="951">
-      <c r="H951" s="24"/>
-    </row>
-    <row r="952">
-      <c r="H952" s="24"/>
-    </row>
-    <row r="953">
-      <c r="H953" s="24"/>
-    </row>
-    <row r="954">
-      <c r="H954" s="24"/>
-    </row>
-    <row r="955">
-      <c r="H955" s="24"/>
-    </row>
-    <row r="956">
-      <c r="H956" s="24"/>
-    </row>
-    <row r="957">
-      <c r="H957" s="24"/>
-    </row>
-    <row r="958">
-      <c r="H958" s="24"/>
-    </row>
-    <row r="959">
-      <c r="H959" s="24"/>
-    </row>
-    <row r="960">
-      <c r="H960" s="24"/>
-    </row>
-    <row r="961">
-      <c r="H961" s="24"/>
-    </row>
-    <row r="962">
-      <c r="H962" s="24"/>
-    </row>
-    <row r="963">
-      <c r="H963" s="24"/>
-    </row>
-    <row r="964">
-      <c r="H964" s="24"/>
-    </row>
-    <row r="965">
-      <c r="H965" s="24"/>
-    </row>
-    <row r="966">
-      <c r="H966" s="24"/>
-    </row>
-    <row r="967">
-      <c r="H967" s="24"/>
-    </row>
-    <row r="968">
-      <c r="H968" s="24"/>
-    </row>
-    <row r="969">
-      <c r="H969" s="24"/>
-    </row>
-    <row r="970">
-      <c r="H970" s="24"/>
-    </row>
-    <row r="971">
-      <c r="H971" s="24"/>
-    </row>
-    <row r="972">
-      <c r="H972" s="24"/>
-    </row>
-    <row r="973">
-      <c r="H973" s="24"/>
-    </row>
-    <row r="974">
-      <c r="H974" s="24"/>
-    </row>
-    <row r="975">
-      <c r="H975" s="24"/>
-    </row>
-    <row r="976">
-      <c r="H976" s="24"/>
-    </row>
-    <row r="977">
-      <c r="H977" s="24"/>
-    </row>
-    <row r="978">
-      <c r="H978" s="24"/>
-    </row>
-    <row r="979">
-      <c r="H979" s="24"/>
-    </row>
-    <row r="980">
-      <c r="H980" s="24"/>
-    </row>
-    <row r="981">
-      <c r="H981" s="24"/>
-    </row>
-    <row r="982">
-      <c r="H982" s="24"/>
-    </row>
-    <row r="983">
-      <c r="H983" s="24"/>
-    </row>
-    <row r="984">
-      <c r="H984" s="24"/>
-    </row>
-    <row r="985">
-      <c r="H985" s="24"/>
-    </row>
-    <row r="986">
-      <c r="H986" s="24"/>
-    </row>
-    <row r="987">
-      <c r="H987" s="24"/>
-    </row>
-    <row r="988">
-      <c r="H988" s="24"/>
-    </row>
-    <row r="989">
-      <c r="H989" s="24"/>
-    </row>
-    <row r="990">
-      <c r="H990" s="24"/>
-    </row>
-    <row r="991">
-      <c r="H991" s="24"/>
-    </row>
-    <row r="992">
-      <c r="H992" s="24"/>
-    </row>
-    <row r="993">
-      <c r="H993" s="24"/>
-    </row>
-    <row r="994">
-      <c r="H994" s="24"/>
-    </row>
-    <row r="995">
-      <c r="H995" s="24"/>
-    </row>
-    <row r="996">
-      <c r="H996" s="24"/>
-    </row>
-    <row r="997">
-      <c r="H997" s="24"/>
-    </row>
-    <row r="998">
-      <c r="H998" s="24"/>
-    </row>
-    <row r="999">
-      <c r="H999" s="24"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
